--- a/Time_series_data.xlsx
+++ b/Time_series_data.xlsx
@@ -5,10 +5,10 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64aae3e7249de19e/Documents/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64aae3e7249de19e/Documents/DATA309-Housing-Affordability/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="8_{337E3E88-031D-4C18-A848-C403A45C26FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{6824D946-1EDC-4004-9EE1-2325B2BCF9D5}"/>
+  <xr:revisionPtr revIDLastSave="11" documentId="8_{337E3E88-031D-4C18-A848-C403A45C26FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94B8BB00-21B0-4497-8636-5EF38D0DF776}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="28" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="29" uniqueCount="28">
   <si>
     <t>Date</t>
   </si>
@@ -102,6 +102,9 @@
   </si>
   <si>
     <t>Mean NZ house price</t>
+  </si>
+  <si>
+    <t>Median Sale Price</t>
   </si>
 </sst>
 </file>
@@ -466,13 +469,13 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:Z142"/>
+  <dimension ref="A1:AA142"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="26" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:26" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:27" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -551,8 +554,11 @@
       <c r="Z1" s="1" t="s">
         <v>19</v>
       </c>
-    </row>
-    <row r="2" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA1" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="2" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>42005</v>
       </c>
@@ -595,8 +601,11 @@
       <c r="Z2" s="3">
         <v>402000</v>
       </c>
-    </row>
-    <row r="3" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA2">
+        <v>425000</v>
+      </c>
+    </row>
+    <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>42036</v>
       </c>
@@ -639,8 +648,11 @@
       <c r="Z3" s="3">
         <v>410000</v>
       </c>
-    </row>
-    <row r="4" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA3">
+        <v>430000</v>
+      </c>
+    </row>
+    <row r="4" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>42064</v>
       </c>
@@ -717,8 +729,11 @@
       <c r="Z4" s="3">
         <v>415000</v>
       </c>
-    </row>
-    <row r="5" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA4">
+        <v>475000</v>
+      </c>
+    </row>
+    <row r="5" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>42095</v>
       </c>
@@ -761,8 +776,11 @@
       <c r="Z5" s="3">
         <v>425000</v>
       </c>
-    </row>
-    <row r="6" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA5">
+        <v>455000</v>
+      </c>
+    </row>
+    <row r="6" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>42125</v>
       </c>
@@ -805,8 +823,11 @@
       <c r="Z6" s="3">
         <v>407000</v>
       </c>
-    </row>
-    <row r="7" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA6">
+        <v>460000</v>
+      </c>
+    </row>
+    <row r="7" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>42156</v>
       </c>
@@ -863,8 +884,11 @@
       <c r="Z7" s="3">
         <v>422000</v>
       </c>
-    </row>
-    <row r="8" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA7">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>42186</v>
       </c>
@@ -907,8 +931,11 @@
       <c r="Z8" s="3">
         <v>420000</v>
       </c>
-    </row>
-    <row r="9" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA8">
+        <v>464000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>42217</v>
       </c>
@@ -951,8 +978,11 @@
       <c r="Z9" s="3">
         <v>415000</v>
       </c>
-    </row>
-    <row r="10" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA9">
+        <v>465000</v>
+      </c>
+    </row>
+    <row r="10" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>42248</v>
       </c>
@@ -1009,8 +1039,11 @@
       <c r="Z10" s="3">
         <v>425000</v>
       </c>
-    </row>
-    <row r="11" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA10">
+        <v>482000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>42278</v>
       </c>
@@ -1053,8 +1086,11 @@
       <c r="Z11" s="3">
         <v>421000</v>
       </c>
-    </row>
-    <row r="12" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA11">
+        <v>458000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>42309</v>
       </c>
@@ -1097,8 +1133,11 @@
       <c r="Z12" s="3">
         <v>425000</v>
       </c>
-    </row>
-    <row r="13" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA12">
+        <v>457000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>42339</v>
       </c>
@@ -1155,8 +1194,11 @@
       <c r="Z13" s="3">
         <v>425000</v>
       </c>
-    </row>
-    <row r="14" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA13">
+        <v>462300</v>
+      </c>
+    </row>
+    <row r="14" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>42370</v>
       </c>
@@ -1199,8 +1241,11 @@
       <c r="Z14" s="3">
         <v>425000</v>
       </c>
-    </row>
-    <row r="15" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA14">
+        <v>448000</v>
+      </c>
+    </row>
+    <row r="15" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>42401</v>
       </c>
@@ -1243,8 +1288,11 @@
       <c r="Z15" s="3">
         <v>424000</v>
       </c>
-    </row>
-    <row r="16" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA15">
+        <v>450000</v>
+      </c>
+    </row>
+    <row r="16" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>42430</v>
       </c>
@@ -1323,8 +1371,11 @@
       <c r="Z16" s="3">
         <v>430000</v>
       </c>
-    </row>
-    <row r="17" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA16">
+        <v>494000</v>
+      </c>
+    </row>
+    <row r="17" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>42461</v>
       </c>
@@ -1367,8 +1418,11 @@
       <c r="Z17" s="3">
         <v>430000</v>
       </c>
-    </row>
-    <row r="18" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA17">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="18" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>42491</v>
       </c>
@@ -1411,8 +1465,11 @@
       <c r="Z18" s="3">
         <v>440000</v>
       </c>
-    </row>
-    <row r="19" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA18">
+        <v>508000</v>
+      </c>
+    </row>
+    <row r="19" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>42522</v>
       </c>
@@ -1469,8 +1526,11 @@
       <c r="Z19" s="3">
         <v>431000</v>
       </c>
-    </row>
-    <row r="20" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA19">
+        <v>500000</v>
+      </c>
+    </row>
+    <row r="20" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>42552</v>
       </c>
@@ -1513,8 +1573,11 @@
       <c r="Z20" s="3">
         <v>430000</v>
       </c>
-    </row>
-    <row r="21" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA20">
+        <v>501000</v>
+      </c>
+    </row>
+    <row r="21" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>42583</v>
       </c>
@@ -1557,8 +1620,11 @@
       <c r="Z21" s="3">
         <v>422500</v>
       </c>
-    </row>
-    <row r="22" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA21">
+        <v>490000</v>
+      </c>
+    </row>
+    <row r="22" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>42614</v>
       </c>
@@ -1615,8 +1681,11 @@
       <c r="Z22" s="3">
         <v>440000</v>
       </c>
-    </row>
-    <row r="23" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA22">
+        <v>519000</v>
+      </c>
+    </row>
+    <row r="23" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>42644</v>
       </c>
@@ -1659,8 +1728,11 @@
       <c r="Z23" s="3">
         <v>430927</v>
       </c>
-    </row>
-    <row r="24" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA23">
+        <v>510000</v>
+      </c>
+    </row>
+    <row r="24" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>42675</v>
       </c>
@@ -1703,8 +1775,11 @@
       <c r="Z24" s="3">
         <v>445000</v>
       </c>
-    </row>
-    <row r="25" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA24">
+        <v>520000</v>
+      </c>
+    </row>
+    <row r="25" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>42705</v>
       </c>
@@ -1761,8 +1836,11 @@
       <c r="Z25" s="3">
         <v>442000</v>
       </c>
-    </row>
-    <row r="26" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA25">
+        <v>520000</v>
+      </c>
+    </row>
+    <row r="26" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>42736</v>
       </c>
@@ -1805,8 +1883,11 @@
       <c r="Z26" s="3">
         <v>425000</v>
       </c>
-    </row>
-    <row r="27" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA26">
+        <v>485500</v>
+      </c>
+    </row>
+    <row r="27" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>42767</v>
       </c>
@@ -1849,8 +1930,11 @@
       <c r="Z27" s="3">
         <v>430000</v>
       </c>
-    </row>
-    <row r="28" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA27">
+        <v>496000</v>
+      </c>
+    </row>
+    <row r="28" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>42795</v>
       </c>
@@ -1929,8 +2013,11 @@
       <c r="Z28" s="3">
         <v>449000</v>
       </c>
-    </row>
-    <row r="29" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA28">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="29" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>42826</v>
       </c>
@@ -1973,8 +2060,11 @@
       <c r="Z29" s="3">
         <v>445000</v>
       </c>
-    </row>
-    <row r="30" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA29">
+        <v>540000</v>
+      </c>
+    </row>
+    <row r="30" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>42856</v>
       </c>
@@ -2017,8 +2107,11 @@
       <c r="Z30" s="3">
         <v>435000</v>
       </c>
-    </row>
-    <row r="31" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA30">
+        <v>535000</v>
+      </c>
+    </row>
+    <row r="31" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>42887</v>
       </c>
@@ -2075,8 +2168,11 @@
       <c r="Z31" s="3">
         <v>435000</v>
       </c>
-    </row>
-    <row r="32" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA31">
+        <v>530000</v>
+      </c>
+    </row>
+    <row r="32" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>42917</v>
       </c>
@@ -2119,8 +2215,11 @@
       <c r="Z32" s="3">
         <v>420000</v>
       </c>
-    </row>
-    <row r="33" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA32">
+        <v>518000</v>
+      </c>
+    </row>
+    <row r="33" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>42948</v>
       </c>
@@ -2163,8 +2262,11 @@
       <c r="Z33" s="3">
         <v>427000</v>
       </c>
-    </row>
-    <row r="34" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA33">
+        <v>530000</v>
+      </c>
+    </row>
+    <row r="34" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>42979</v>
       </c>
@@ -2221,8 +2323,11 @@
       <c r="Z34" s="3">
         <v>431500</v>
       </c>
-    </row>
-    <row r="35" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA34">
+        <v>525000</v>
+      </c>
+    </row>
+    <row r="35" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>43009</v>
       </c>
@@ -2265,8 +2370,11 @@
       <c r="Z35" s="3">
         <v>450000</v>
       </c>
-    </row>
-    <row r="36" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA35">
+        <v>530000</v>
+      </c>
+    </row>
+    <row r="36" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>43040</v>
       </c>
@@ -2309,8 +2417,11 @@
       <c r="Z36" s="3">
         <v>460000</v>
       </c>
-    </row>
-    <row r="37" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA36">
+        <v>540000</v>
+      </c>
+    </row>
+    <row r="37" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>43070</v>
       </c>
@@ -2367,8 +2478,11 @@
       <c r="Z37" s="3">
         <v>435000</v>
       </c>
-    </row>
-    <row r="38" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA37">
+        <v>551750</v>
+      </c>
+    </row>
+    <row r="38" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>43101</v>
       </c>
@@ -2411,8 +2525,11 @@
       <c r="Z38" s="3">
         <v>435000</v>
       </c>
-    </row>
-    <row r="39" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA38">
+        <v>520000</v>
+      </c>
+    </row>
+    <row r="39" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>43132</v>
       </c>
@@ -2455,8 +2572,11 @@
       <c r="Z39" s="3">
         <v>445000</v>
       </c>
-    </row>
-    <row r="40" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA39">
+        <v>530000</v>
+      </c>
+    </row>
+    <row r="40" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>43160</v>
       </c>
@@ -2535,8 +2655,11 @@
       <c r="Z40" s="3">
         <v>450000</v>
       </c>
-    </row>
-    <row r="41" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA40">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="41" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>43191</v>
       </c>
@@ -2579,8 +2702,11 @@
       <c r="Z41" s="3">
         <v>441000</v>
       </c>
-    </row>
-    <row r="42" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA41">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="42" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>43221</v>
       </c>
@@ -2623,8 +2749,11 @@
       <c r="Z42" s="3">
         <v>445000</v>
       </c>
-    </row>
-    <row r="43" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA42">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="43" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>43252</v>
       </c>
@@ -2681,8 +2810,11 @@
       <c r="Z43" s="3">
         <v>432500</v>
       </c>
-    </row>
-    <row r="44" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA43">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="44" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43282</v>
       </c>
@@ -2725,8 +2857,11 @@
       <c r="Z44" s="3">
         <v>430000</v>
       </c>
-    </row>
-    <row r="45" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA44">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="45" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>43313</v>
       </c>
@@ -2769,8 +2904,11 @@
       <c r="Z45" s="3">
         <v>425000</v>
       </c>
-    </row>
-    <row r="46" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA45">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="46" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>43344</v>
       </c>
@@ -2827,8 +2965,11 @@
       <c r="Z46" s="3">
         <v>447500</v>
       </c>
-    </row>
-    <row r="47" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA46">
+        <v>559000</v>
+      </c>
+    </row>
+    <row r="47" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>43374</v>
       </c>
@@ -2871,8 +3012,11 @@
       <c r="Z47" s="3">
         <v>465000</v>
       </c>
-    </row>
-    <row r="48" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA47">
+        <v>561500</v>
+      </c>
+    </row>
+    <row r="48" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>43405</v>
       </c>
@@ -2915,8 +3059,11 @@
       <c r="Z48" s="3">
         <v>445000</v>
       </c>
-    </row>
-    <row r="49" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA48">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="49" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>43435</v>
       </c>
@@ -2973,8 +3120,11 @@
       <c r="Z49" s="3">
         <v>455000</v>
       </c>
-    </row>
-    <row r="50" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA49">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="50" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>43466</v>
       </c>
@@ -3017,8 +3167,11 @@
       <c r="Z50" s="3">
         <v>430000</v>
       </c>
-    </row>
-    <row r="51" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA50">
+        <v>550000</v>
+      </c>
+    </row>
+    <row r="51" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>43497</v>
       </c>
@@ -3061,8 +3214,11 @@
       <c r="Z51" s="3">
         <v>455000</v>
       </c>
-    </row>
-    <row r="52" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA51">
+        <v>560000</v>
+      </c>
+    </row>
+    <row r="52" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>43525</v>
       </c>
@@ -3141,8 +3297,11 @@
       <c r="Z52" s="3">
         <v>459000</v>
       </c>
-    </row>
-    <row r="53" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA52">
+        <v>585000</v>
+      </c>
+    </row>
+    <row r="53" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>43556</v>
       </c>
@@ -3185,8 +3344,11 @@
       <c r="Z53" s="3">
         <v>450000</v>
       </c>
-    </row>
-    <row r="54" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA53">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="54" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>43586</v>
       </c>
@@ -3229,8 +3391,11 @@
       <c r="Z54" s="3">
         <v>445000</v>
       </c>
-    </row>
-    <row r="55" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA54">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="55" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>43617</v>
       </c>
@@ -3287,8 +3452,11 @@
       <c r="Z55" s="3">
         <v>445000</v>
       </c>
-    </row>
-    <row r="56" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA55">
+        <v>585000</v>
+      </c>
+    </row>
+    <row r="56" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>43647</v>
       </c>
@@ -3331,8 +3499,11 @@
       <c r="Z56" s="3">
         <v>446000</v>
       </c>
-    </row>
-    <row r="57" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA56">
+        <v>575000</v>
+      </c>
+    </row>
+    <row r="57" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>43678</v>
       </c>
@@ -3375,8 +3546,11 @@
       <c r="Z57" s="3">
         <v>440000</v>
       </c>
-    </row>
-    <row r="58" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA57">
+        <v>580000</v>
+      </c>
+    </row>
+    <row r="58" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>43709</v>
       </c>
@@ -3433,8 +3607,11 @@
       <c r="Z58" s="3">
         <v>450000</v>
       </c>
-    </row>
-    <row r="59" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA58">
+        <v>596956</v>
+      </c>
+    </row>
+    <row r="59" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>43739</v>
       </c>
@@ -3477,8 +3654,11 @@
       <c r="Z59" s="3">
         <v>465000</v>
       </c>
-    </row>
-    <row r="60" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA59">
+        <v>605000</v>
+      </c>
+    </row>
+    <row r="60" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>43770</v>
       </c>
@@ -3521,8 +3701,11 @@
       <c r="Z60" s="3">
         <v>465000</v>
       </c>
-    </row>
-    <row r="61" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA60">
+        <v>632000</v>
+      </c>
+    </row>
+    <row r="61" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>43800</v>
       </c>
@@ -3579,8 +3762,11 @@
       <c r="Z61" s="3">
         <v>460000</v>
       </c>
-    </row>
-    <row r="62" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA61">
+        <v>628000</v>
+      </c>
+    </row>
+    <row r="62" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>43831</v>
       </c>
@@ -3623,8 +3809,11 @@
       <c r="Z62" s="3">
         <v>465000</v>
       </c>
-    </row>
-    <row r="63" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA62">
+        <v>612000</v>
+      </c>
+    </row>
+    <row r="63" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>43862</v>
       </c>
@@ -3667,8 +3856,11 @@
       <c r="Z63" s="3">
         <v>474000</v>
       </c>
-    </row>
-    <row r="64" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA63">
+        <v>635000</v>
+      </c>
+    </row>
+    <row r="64" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>43891</v>
       </c>
@@ -3747,8 +3939,11 @@
       <c r="Z64" s="3">
         <v>488000</v>
       </c>
-    </row>
-    <row r="65" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA64">
+        <v>665000</v>
+      </c>
+    </row>
+    <row r="65" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>43922</v>
       </c>
@@ -3791,8 +3986,11 @@
       <c r="Z65" s="3">
         <v>464000</v>
       </c>
-    </row>
-    <row r="66" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA65">
+        <v>680000</v>
+      </c>
+    </row>
+    <row r="66" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>43952</v>
       </c>
@@ -3835,8 +4033,11 @@
       <c r="Z66" s="3">
         <v>460000</v>
       </c>
-    </row>
-    <row r="67" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA66">
+        <v>620000</v>
+      </c>
+    </row>
+    <row r="67" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>43983</v>
       </c>
@@ -3893,8 +4094,11 @@
       <c r="Z67" s="3">
         <v>470000</v>
       </c>
-    </row>
-    <row r="68" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA67">
+        <v>637000</v>
+      </c>
+    </row>
+    <row r="68" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>44013</v>
       </c>
@@ -3937,8 +4141,11 @@
       <c r="Z68" s="3">
         <v>477000</v>
       </c>
-    </row>
-    <row r="69" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA68">
+        <v>659500</v>
+      </c>
+    </row>
+    <row r="69" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>44044</v>
       </c>
@@ -3981,8 +4188,11 @@
       <c r="Z69" s="3">
         <v>498000</v>
       </c>
-    </row>
-    <row r="70" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA69">
+        <v>677400</v>
+      </c>
+    </row>
+    <row r="70" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>44075</v>
       </c>
@@ -4039,8 +4249,11 @@
       <c r="Z70" s="3">
         <v>504000</v>
       </c>
-    </row>
-    <row r="71" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA70">
+        <v>689000</v>
+      </c>
+    </row>
+    <row r="71" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>44105</v>
       </c>
@@ -4083,8 +4296,11 @@
       <c r="Z71" s="3">
         <v>510000</v>
       </c>
-    </row>
-    <row r="72" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA71">
+        <v>725000</v>
+      </c>
+    </row>
+    <row r="72" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>44136</v>
       </c>
@@ -4127,8 +4343,11 @@
       <c r="Z72" s="3">
         <v>525000</v>
       </c>
-    </row>
-    <row r="73" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA72">
+        <v>747000</v>
+      </c>
+    </row>
+    <row r="73" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>44166</v>
       </c>
@@ -4185,8 +4404,11 @@
       <c r="Z73" s="3">
         <v>540000</v>
       </c>
-    </row>
-    <row r="74" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA73">
+        <v>745000</v>
+      </c>
+    </row>
+    <row r="74" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>44197</v>
       </c>
@@ -4229,8 +4451,11 @@
       <c r="Z74" s="3">
         <v>507500</v>
       </c>
-    </row>
-    <row r="75" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA74">
+        <v>730300</v>
+      </c>
+    </row>
+    <row r="75" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>44228</v>
       </c>
@@ -4273,8 +4498,11 @@
       <c r="Z75" s="3">
         <v>560000</v>
       </c>
-    </row>
-    <row r="76" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA75">
+        <v>780000</v>
+      </c>
+    </row>
+    <row r="76" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>44256</v>
       </c>
@@ -4353,8 +4581,11 @@
       <c r="Z76" s="3">
         <v>575000</v>
       </c>
-    </row>
-    <row r="77" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA76">
+        <v>825000</v>
+      </c>
+    </row>
+    <row r="77" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>44287</v>
       </c>
@@ -4397,8 +4628,11 @@
       <c r="Z77" s="3">
         <v>566000</v>
       </c>
-    </row>
-    <row r="78" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA77">
+        <v>804362</v>
+      </c>
+    </row>
+    <row r="78" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>44317</v>
       </c>
@@ -4441,8 +4675,11 @@
       <c r="Z78" s="3">
         <v>580000</v>
       </c>
-    </row>
-    <row r="79" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA78">
+        <v>820000</v>
+      </c>
+    </row>
+    <row r="79" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>44348</v>
       </c>
@@ -4499,8 +4736,11 @@
       <c r="Z79" s="3">
         <v>565000</v>
       </c>
-    </row>
-    <row r="80" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA79">
+        <v>816000</v>
+      </c>
+    </row>
+    <row r="80" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>44378</v>
       </c>
@@ -4543,8 +4783,11 @@
       <c r="Z80" s="3">
         <v>597000</v>
       </c>
-    </row>
-    <row r="81" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA80">
+        <v>825000</v>
+      </c>
+    </row>
+    <row r="81" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>44409</v>
       </c>
@@ -4587,8 +4830,11 @@
       <c r="Z81" s="3">
         <v>620000</v>
       </c>
-    </row>
-    <row r="82" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA81">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="82" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>44440</v>
       </c>
@@ -4645,8 +4891,11 @@
       <c r="Z82" s="3">
         <v>657500</v>
       </c>
-    </row>
-    <row r="83" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA82">
+        <v>795000</v>
+      </c>
+    </row>
+    <row r="83" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>44470</v>
       </c>
@@ -4689,8 +4938,11 @@
       <c r="Z83" s="3">
         <v>665000</v>
       </c>
-    </row>
-    <row r="84" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA83">
+        <v>892000</v>
+      </c>
+    </row>
+    <row r="84" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>44501</v>
       </c>
@@ -4733,8 +4985,11 @@
       <c r="Z84" s="3">
         <v>690000</v>
       </c>
-    </row>
-    <row r="85" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA84">
+        <v>925000</v>
+      </c>
+    </row>
+    <row r="85" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>44531</v>
       </c>
@@ -4791,8 +5046,11 @@
       <c r="Z85" s="3">
         <v>680000</v>
       </c>
-    </row>
-    <row r="86" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA85">
+        <v>900000</v>
+      </c>
+    </row>
+    <row r="86" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>44562</v>
       </c>
@@ -4835,8 +5093,11 @@
       <c r="Z86" s="3">
         <v>650000</v>
       </c>
-    </row>
-    <row r="87" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA86">
+        <v>879000</v>
+      </c>
+    </row>
+    <row r="87" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>44593</v>
       </c>
@@ -4879,8 +5140,11 @@
       <c r="Z87" s="3">
         <v>717830</v>
       </c>
-    </row>
-    <row r="88" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA87">
+        <v>885000</v>
+      </c>
+    </row>
+    <row r="88" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>44621</v>
       </c>
@@ -4959,8 +5223,11 @@
       <c r="Z88" s="3">
         <v>700000</v>
       </c>
-    </row>
-    <row r="89" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA88">
+        <v>890000</v>
+      </c>
+    </row>
+    <row r="89" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>44652</v>
       </c>
@@ -5003,8 +5270,11 @@
       <c r="Z89" s="3">
         <v>680000</v>
       </c>
-    </row>
-    <row r="90" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA89">
+        <v>875000</v>
+      </c>
+    </row>
+    <row r="90" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>44682</v>
       </c>
@@ -5047,8 +5317,11 @@
       <c r="Z90" s="3">
         <v>687000</v>
       </c>
-    </row>
-    <row r="91" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA90">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="91" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>44713</v>
       </c>
@@ -5105,8 +5378,11 @@
       <c r="Z91" s="3">
         <v>685000</v>
       </c>
-    </row>
-    <row r="92" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA91">
+        <v>850000</v>
+      </c>
+    </row>
+    <row r="92" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>44743</v>
       </c>
@@ -5149,8 +5425,11 @@
       <c r="Z92" s="3">
         <v>675000</v>
       </c>
-    </row>
-    <row r="93" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA92">
+        <v>810000</v>
+      </c>
+    </row>
+    <row r="93" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>44774</v>
       </c>
@@ -5193,8 +5472,11 @@
       <c r="Z93" s="3">
         <v>650000</v>
       </c>
-    </row>
-    <row r="94" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA93">
+        <v>800000</v>
+      </c>
+    </row>
+    <row r="94" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>44805</v>
       </c>
@@ -5251,8 +5533,11 @@
       <c r="Z94" s="3">
         <v>675000</v>
       </c>
-    </row>
-    <row r="95" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA94">
+        <v>810000</v>
+      </c>
+    </row>
+    <row r="95" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>44835</v>
       </c>
@@ -5295,8 +5580,11 @@
       <c r="Z95" s="3">
         <v>659000</v>
       </c>
-    </row>
-    <row r="96" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA95">
+        <v>818000</v>
+      </c>
+    </row>
+    <row r="96" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>44866</v>
       </c>
@@ -5339,8 +5627,11 @@
       <c r="Z96" s="3">
         <v>665000</v>
       </c>
-    </row>
-    <row r="97" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA96">
+        <v>806000</v>
+      </c>
+    </row>
+    <row r="97" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>44896</v>
       </c>
@@ -5397,8 +5688,11 @@
       <c r="Z97" s="3">
         <v>651000</v>
       </c>
-    </row>
-    <row r="98" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA97">
+        <v>785000</v>
+      </c>
+    </row>
+    <row r="98" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>44927</v>
       </c>
@@ -5441,8 +5735,11 @@
       <c r="Z98" s="3">
         <v>642500</v>
       </c>
-    </row>
-    <row r="99" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA98">
+        <v>765000</v>
+      </c>
+    </row>
+    <row r="99" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>44958</v>
       </c>
@@ -5485,8 +5782,11 @@
       <c r="Z99" s="3">
         <v>670000</v>
       </c>
-    </row>
-    <row r="100" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA99">
+        <v>766000</v>
+      </c>
+    </row>
+    <row r="100" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>44986</v>
       </c>
@@ -5565,8 +5865,11 @@
       <c r="Z100" s="3">
         <v>680000</v>
       </c>
-    </row>
-    <row r="101" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA100">
+        <v>779000</v>
+      </c>
+    </row>
+    <row r="101" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>45017</v>
       </c>
@@ -5609,8 +5912,11 @@
       <c r="Z101" s="3">
         <v>665000</v>
       </c>
-    </row>
-    <row r="102" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA101">
+        <v>780000</v>
+      </c>
+    </row>
+    <row r="102" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>45047</v>
       </c>
@@ -5653,8 +5959,11 @@
       <c r="Z102" s="3">
         <v>649000</v>
       </c>
-    </row>
-    <row r="103" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA102">
+        <v>780000</v>
+      </c>
+    </row>
+    <row r="103" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>45078</v>
       </c>
@@ -5711,8 +6020,11 @@
       <c r="Z103" s="3">
         <v>657000</v>
       </c>
-    </row>
-    <row r="104" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA103">
+        <v>780000</v>
+      </c>
+    </row>
+    <row r="104" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>45108</v>
       </c>
@@ -5755,8 +6067,11 @@
       <c r="Z104" s="3">
         <v>665000</v>
       </c>
-    </row>
-    <row r="105" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA104">
+        <v>770000</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>45139</v>
       </c>
@@ -5799,8 +6114,11 @@
       <c r="Z105" s="3">
         <v>659000</v>
       </c>
-    </row>
-    <row r="106" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA105">
+        <v>770000</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>45170</v>
       </c>
@@ -5857,8 +6175,11 @@
       <c r="Z106" s="3">
         <v>680000</v>
       </c>
-    </row>
-    <row r="107" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA106">
+        <v>799000</v>
+      </c>
+    </row>
+    <row r="107" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>45200</v>
       </c>
@@ -5901,8 +6222,11 @@
       <c r="Z107" s="3">
         <v>680000</v>
       </c>
-    </row>
-    <row r="108" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA107">
+        <v>789500</v>
+      </c>
+    </row>
+    <row r="108" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>45231</v>
       </c>
@@ -5945,8 +6269,11 @@
       <c r="Z108" s="3">
         <v>700000</v>
       </c>
-    </row>
-    <row r="109" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA108">
+        <v>795000</v>
+      </c>
+    </row>
+    <row r="109" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>45261</v>
       </c>
@@ -6003,8 +6330,11 @@
       <c r="Z109" s="3">
         <v>665000</v>
       </c>
-    </row>
-    <row r="110" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA109">
+        <v>780000</v>
+      </c>
+    </row>
+    <row r="110" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>45292</v>
       </c>
@@ -6047,8 +6377,11 @@
       <c r="Z110" s="3">
         <v>646000</v>
       </c>
-    </row>
-    <row r="111" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA110">
+        <v>763000</v>
+      </c>
+    </row>
+    <row r="111" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>45323</v>
       </c>
@@ -6091,8 +6424,11 @@
       <c r="Z111" s="3">
         <v>705000</v>
       </c>
-    </row>
-    <row r="112" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA111">
+        <v>791000</v>
+      </c>
+    </row>
+    <row r="112" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>45352</v>
       </c>
@@ -6171,8 +6507,11 @@
       <c r="Z112" s="3">
         <v>695000</v>
       </c>
-    </row>
-    <row r="113" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA112">
+        <v>801000</v>
+      </c>
+    </row>
+    <row r="113" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>45383</v>
       </c>
@@ -6215,8 +6554,11 @@
       <c r="Z113" s="3">
         <v>670000</v>
       </c>
-    </row>
-    <row r="114" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA113">
+        <v>790000</v>
+      </c>
+    </row>
+    <row r="114" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>45413</v>
       </c>
@@ -6259,8 +6601,11 @@
       <c r="Z114" s="3">
         <v>680000</v>
       </c>
-    </row>
-    <row r="115" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA114">
+        <v>770000</v>
+      </c>
+    </row>
+    <row r="115" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>45444</v>
       </c>
@@ -6317,8 +6662,11 @@
       <c r="Z115" s="3">
         <v>690000</v>
       </c>
-    </row>
-    <row r="116" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA115">
+        <v>770000</v>
+      </c>
+    </row>
+    <row r="116" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>45474</v>
       </c>
@@ -6361,8 +6709,11 @@
       <c r="Z116" s="3">
         <v>650500</v>
       </c>
-    </row>
-    <row r="117" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA116">
+        <v>754000</v>
+      </c>
+    </row>
+    <row r="117" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>45505</v>
       </c>
@@ -6405,8 +6756,11 @@
       <c r="Z117" s="3">
         <v>662500</v>
       </c>
-    </row>
-    <row r="118" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA117">
+        <v>765000</v>
+      </c>
+    </row>
+    <row r="118" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>45536</v>
       </c>
@@ -6463,8 +6817,11 @@
       <c r="Z118" s="3">
         <v>690000</v>
       </c>
-    </row>
-    <row r="119" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA118">
+        <v>782000</v>
+      </c>
+    </row>
+    <row r="119" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>45566</v>
       </c>
@@ -6507,8 +6864,11 @@
       <c r="Z119" s="3">
         <v>700000</v>
       </c>
-    </row>
-    <row r="120" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA119">
+        <v>795000</v>
+      </c>
+    </row>
+    <row r="120" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>45597</v>
       </c>
@@ -6551,8 +6911,11 @@
       <c r="Z120" s="3">
         <v>699000</v>
       </c>
-    </row>
-    <row r="121" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA120">
+        <v>790000</v>
+      </c>
+    </row>
+    <row r="121" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>45627</v>
       </c>
@@ -6609,8 +6972,11 @@
       <c r="Z121" s="3">
         <v>700000</v>
       </c>
-    </row>
-    <row r="122" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA121">
+        <v>776000</v>
+      </c>
+    </row>
+    <row r="122" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>45658</v>
       </c>
@@ -6653,8 +7019,11 @@
       <c r="Z122" s="3">
         <v>677000</v>
       </c>
-    </row>
-    <row r="123" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA122">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="123" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>45689</v>
       </c>
@@ -6697,8 +7066,11 @@
       <c r="Z123" s="3">
         <v>705000</v>
       </c>
-    </row>
-    <row r="124" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA123">
+        <v>770000</v>
+      </c>
+    </row>
+    <row r="124" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>45717</v>
       </c>
@@ -6775,8 +7147,11 @@
       <c r="Z124" s="3">
         <v>690000</v>
       </c>
-    </row>
-    <row r="125" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA124">
+        <v>790000</v>
+      </c>
+    </row>
+    <row r="125" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>45748</v>
       </c>
@@ -6819,8 +7194,11 @@
       <c r="Z125" s="3">
         <v>695652</v>
       </c>
-    </row>
-    <row r="126" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA125">
+        <v>780000</v>
+      </c>
+    </row>
+    <row r="126" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>45778</v>
       </c>
@@ -6863,8 +7241,11 @@
       <c r="Z126" s="3">
         <v>680000</v>
       </c>
-    </row>
-    <row r="127" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA126">
+        <v>765000</v>
+      </c>
+    </row>
+    <row r="127" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>45809</v>
       </c>
@@ -6919,8 +7300,11 @@
       <c r="Z127" s="3">
         <v>675000</v>
       </c>
-    </row>
-    <row r="128" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA127">
+        <v>765000</v>
+      </c>
+    </row>
+    <row r="128" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>45839</v>
       </c>
@@ -6963,8 +7347,11 @@
       <c r="Z128" s="3">
         <v>677000</v>
       </c>
-    </row>
-    <row r="129" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA128">
+        <v>765000</v>
+      </c>
+    </row>
+    <row r="129" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>45870</v>
       </c>
@@ -7007,8 +7394,11 @@
       <c r="Z129" s="3">
         <v>690000</v>
       </c>
-    </row>
-    <row r="130" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA129">
+        <v>760000</v>
+      </c>
+    </row>
+    <row r="130" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>45901</v>
       </c>
@@ -7063,8 +7453,11 @@
       <c r="Z130" s="3">
         <v>709000</v>
       </c>
-    </row>
-    <row r="131" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA130">
+        <v>773000</v>
+      </c>
+    </row>
+    <row r="131" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>45931</v>
       </c>
@@ -7107,8 +7500,11 @@
       <c r="Z131" s="3">
         <v>708000</v>
       </c>
-    </row>
-    <row r="132" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA131">
+        <v>790000</v>
+      </c>
+    </row>
+    <row r="132" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>45962</v>
       </c>
@@ -7151,8 +7547,11 @@
       <c r="Z132" s="3">
         <v>725000</v>
       </c>
-    </row>
-    <row r="133" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA132">
+        <v>802000</v>
+      </c>
+    </row>
+    <row r="133" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>45992</v>
       </c>
@@ -7207,8 +7606,11 @@
       <c r="Z133" s="3">
         <v>721000</v>
       </c>
-    </row>
-    <row r="134" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA133">
+        <v>790000</v>
+      </c>
+    </row>
+    <row r="134" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>46023</v>
       </c>
@@ -7251,8 +7653,11 @@
       <c r="Z134" s="3">
         <v>700000</v>
       </c>
-    </row>
-    <row r="135" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA134">
+        <v>755000</v>
+      </c>
+    </row>
+    <row r="135" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>46054</v>
       </c>
@@ -7289,8 +7694,11 @@
       <c r="Z135" s="3">
         <v>719000</v>
       </c>
-    </row>
-    <row r="136" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA135">
+        <v>795000</v>
+      </c>
+    </row>
+    <row r="136" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>46082</v>
       </c>
@@ -7349,8 +7757,11 @@
       <c r="Z136" s="3">
         <v>715000</v>
       </c>
-    </row>
-    <row r="137" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA136">
+        <v>790000</v>
+      </c>
+    </row>
+    <row r="137" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>46113</v>
       </c>
@@ -7387,8 +7798,11 @@
       <c r="Z137" s="3">
         <v>705000</v>
       </c>
-    </row>
-    <row r="138" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA137">
+        <v>780000</v>
+      </c>
+    </row>
+    <row r="138" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>46143</v>
       </c>
@@ -7425,8 +7839,11 @@
       <c r="Z138" s="3">
         <v>725000</v>
       </c>
-    </row>
-    <row r="139" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA138">
+        <v>780000</v>
+      </c>
+    </row>
+    <row r="139" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>46174</v>
       </c>
@@ -7467,8 +7884,11 @@
       <c r="Z139" s="3">
         <v>710000</v>
       </c>
-    </row>
-    <row r="140" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA139">
+        <v>775000</v>
+      </c>
+    </row>
+    <row r="140" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>46204</v>
       </c>
@@ -7503,8 +7923,11 @@
         <v>296.10165360000002</v>
       </c>
       <c r="Z140" s="3"/>
-    </row>
-    <row r="141" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA140">
+        <v>760500</v>
+      </c>
+    </row>
+    <row r="141" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>46235</v>
       </c>
@@ -7537,8 +7960,11 @@
         <v>300.83523769999999</v>
       </c>
       <c r="Z141" s="3"/>
-    </row>
-    <row r="142" spans="1:26" x14ac:dyDescent="0.3">
+      <c r="AA141">
+        <v>750000</v>
+      </c>
+    </row>
+    <row r="142" spans="1:27" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>46266</v>
       </c>

--- a/Time_series_data.xlsx
+++ b/Time_series_data.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64aae3e7249de19e/Documents/DATA309-Housing-Affordability/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="11" documentId="8_{337E3E88-031D-4C18-A848-C403A45C26FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{94B8BB00-21B0-4497-8636-5EF38D0DF776}"/>
+  <xr:revisionPtr revIDLastSave="14" documentId="8_{337E3E88-031D-4C18-A848-C403A45C26FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{C88E9B8A-738C-4EEE-98EB-93324E71F67D}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -104,7 +104,7 @@
     <t>Mean NZ house price</t>
   </si>
   <si>
-    <t>Median Sale Price</t>
+    <t>NZ Median sale price</t>
   </si>
 </sst>
 </file>
@@ -554,7 +554,7 @@
       <c r="Z1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="AA1" t="s">
+      <c r="AA1" s="1" t="s">
         <v>27</v>
       </c>
     </row>

--- a/Time_series_data.xlsx
+++ b/Time_series_data.xlsx
@@ -8,20 +8,34 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Documents\DATA309\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD18F50-42D1-4584-9E35-3BF8A0A5C17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{08A933B6-8DB2-4CEA-ACD1-87F9F9FDB0B6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-90" yWindow="0" windowWidth="11460" windowHeight="14410" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Combined" sheetId="1" r:id="rId1"/>
     <sheet name="Week" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <fileRecoveryPr repairLoad="1"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>Date</t>
   </si>
@@ -166,6 +180,12 @@
   <si>
     <t>Floating Mortgage Rate</t>
   </si>
+  <si>
+    <t>Weeks of Inventory</t>
+  </si>
+  <si>
+    <t>Weeks of Inventory Canterbury</t>
+  </si>
 </sst>
 </file>
 
@@ -237,7 +257,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -690,8 +710,12 @@
       <c r="AU1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="6"/>
-      <c r="AW1" s="6"/>
+      <c r="AV1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AW1" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="AX1" s="6"/>
       <c r="AY1" s="6"/>
       <c r="AZ1" s="6"/>
@@ -797,6 +821,12 @@
       <c r="AU2">
         <v>562</v>
       </c>
+      <c r="AV2">
+        <v>22</v>
+      </c>
+      <c r="AW2">
+        <v>18</v>
+      </c>
     </row>
     <row r="3" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
@@ -898,6 +928,12 @@
       <c r="AU3">
         <v>409</v>
       </c>
+      <c r="AV3">
+        <v>24</v>
+      </c>
+      <c r="AW3">
+        <v>22</v>
+      </c>
     </row>
     <row r="4" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
@@ -1040,6 +1076,12 @@
       </c>
       <c r="AU4">
         <v>631</v>
+      </c>
+      <c r="AV4">
+        <v>22</v>
+      </c>
+      <c r="AW4">
+        <v>19</v>
       </c>
     </row>
     <row r="5" spans="1:53" x14ac:dyDescent="0.35">
@@ -1142,6 +1184,12 @@
       <c r="AU5">
         <v>747</v>
       </c>
+      <c r="AV5">
+        <v>20</v>
+      </c>
+      <c r="AW5">
+        <v>19</v>
+      </c>
     </row>
     <row r="6" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
@@ -1243,6 +1291,12 @@
       <c r="AU6">
         <v>584</v>
       </c>
+      <c r="AV6">
+        <v>21</v>
+      </c>
+      <c r="AW6">
+        <v>20</v>
+      </c>
     </row>
     <row r="7" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
@@ -1356,6 +1410,12 @@
       </c>
       <c r="AU7">
         <v>540</v>
+      </c>
+      <c r="AV7">
+        <v>20</v>
+      </c>
+      <c r="AW7">
+        <v>19</v>
       </c>
     </row>
     <row r="8" spans="1:53" x14ac:dyDescent="0.35">
@@ -1458,6 +1518,12 @@
       <c r="AU8">
         <v>1025</v>
       </c>
+      <c r="AV8">
+        <v>18</v>
+      </c>
+      <c r="AW8">
+        <v>18</v>
+      </c>
     </row>
     <row r="9" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
@@ -1559,6 +1625,12 @@
       <c r="AU9">
         <v>674</v>
       </c>
+      <c r="AV9">
+        <v>17</v>
+      </c>
+      <c r="AW9">
+        <v>17</v>
+      </c>
     </row>
     <row r="10" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
@@ -1672,6 +1744,12 @@
       </c>
       <c r="AU10">
         <v>461</v>
+      </c>
+      <c r="AV10">
+        <v>17</v>
+      </c>
+      <c r="AW10">
+        <v>19</v>
       </c>
     </row>
     <row r="11" spans="1:53" x14ac:dyDescent="0.35">
@@ -1774,6 +1852,12 @@
       <c r="AU11">
         <v>617</v>
       </c>
+      <c r="AV11">
+        <v>17</v>
+      </c>
+      <c r="AW11">
+        <v>18</v>
+      </c>
     </row>
     <row r="12" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
@@ -1875,6 +1959,12 @@
       <c r="AU12">
         <v>967</v>
       </c>
+      <c r="AV12">
+        <v>16</v>
+      </c>
+      <c r="AW12">
+        <v>17</v>
+      </c>
     </row>
     <row r="13" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
@@ -1988,6 +2078,12 @@
       </c>
       <c r="AU13">
         <v>877</v>
+      </c>
+      <c r="AV13">
+        <v>16</v>
+      </c>
+      <c r="AW13">
+        <v>17</v>
       </c>
     </row>
     <row r="14" spans="1:53" x14ac:dyDescent="0.35">
@@ -2090,6 +2186,12 @@
       <c r="AU14">
         <v>409</v>
       </c>
+      <c r="AV14">
+        <v>16</v>
+      </c>
+      <c r="AW14">
+        <v>18</v>
+      </c>
     </row>
     <row r="15" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
@@ -2191,6 +2293,12 @@
       <c r="AU15">
         <v>667</v>
       </c>
+      <c r="AV15">
+        <v>16</v>
+      </c>
+      <c r="AW15">
+        <v>18</v>
+      </c>
     </row>
     <row r="16" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
@@ -2334,8 +2442,14 @@
       <c r="AU16">
         <v>500</v>
       </c>
-    </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV16">
+        <v>14</v>
+      </c>
+      <c r="AW16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>42461</v>
       </c>
@@ -2435,8 +2549,14 @@
       <c r="AU17">
         <v>619</v>
       </c>
-    </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV17">
+        <v>13</v>
+      </c>
+      <c r="AW17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>42491</v>
       </c>
@@ -2536,8 +2656,14 @@
       <c r="AU18">
         <v>564</v>
       </c>
-    </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV18">
+        <v>12</v>
+      </c>
+      <c r="AW18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>42522</v>
       </c>
@@ -2650,8 +2776,14 @@
       <c r="AU19">
         <v>889</v>
       </c>
-    </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV19">
+        <v>12</v>
+      </c>
+      <c r="AW19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>42552</v>
       </c>
@@ -2751,8 +2883,14 @@
       <c r="AU20">
         <v>1050</v>
       </c>
-    </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV20">
+        <v>13</v>
+      </c>
+      <c r="AW20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>42583</v>
       </c>
@@ -2852,8 +2990,14 @@
       <c r="AU21">
         <v>819</v>
       </c>
-    </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV21">
+        <v>14</v>
+      </c>
+      <c r="AW21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>42614</v>
       </c>
@@ -2966,8 +3110,14 @@
       <c r="AU22">
         <v>722</v>
       </c>
-    </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV22">
+        <v>14</v>
+      </c>
+      <c r="AW22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>42644</v>
       </c>
@@ -3067,8 +3217,14 @@
       <c r="AU23">
         <v>773</v>
       </c>
-    </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV23">
+        <v>14</v>
+      </c>
+      <c r="AW23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>42675</v>
       </c>
@@ -3168,8 +3324,14 @@
       <c r="AU24">
         <v>1119</v>
       </c>
-    </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV24">
+        <v>15</v>
+      </c>
+      <c r="AW24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>42705</v>
       </c>
@@ -3282,8 +3444,14 @@
       <c r="AU25">
         <v>625</v>
       </c>
-    </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV25">
+        <v>15</v>
+      </c>
+      <c r="AW25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>42736</v>
       </c>
@@ -3383,8 +3551,14 @@
       <c r="AU26">
         <v>499</v>
       </c>
-    </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV26">
+        <v>15</v>
+      </c>
+      <c r="AW26">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>42767</v>
       </c>
@@ -3484,8 +3658,14 @@
       <c r="AU27">
         <v>657</v>
       </c>
-    </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV27">
+        <v>17</v>
+      </c>
+      <c r="AW27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>42795</v>
       </c>
@@ -3627,8 +3807,14 @@
       <c r="AU28">
         <v>856</v>
       </c>
-    </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV28">
+        <v>16</v>
+      </c>
+      <c r="AW28">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>42826</v>
       </c>
@@ -3728,8 +3914,14 @@
       <c r="AU29">
         <v>619</v>
       </c>
-    </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV29">
+        <v>15</v>
+      </c>
+      <c r="AW29">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>42856</v>
       </c>
@@ -3829,8 +4021,14 @@
       <c r="AU30">
         <v>755</v>
       </c>
-    </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV30">
+        <v>16</v>
+      </c>
+      <c r="AW30">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>42887</v>
       </c>
@@ -3943,8 +4141,14 @@
       <c r="AU31">
         <v>869</v>
       </c>
-    </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV31">
+        <v>17</v>
+      </c>
+      <c r="AW31">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>42917</v>
       </c>
@@ -4044,8 +4248,14 @@
       <c r="AU32">
         <v>862</v>
       </c>
-    </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV32">
+        <v>17</v>
+      </c>
+      <c r="AW32">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>42948</v>
       </c>
@@ -4145,8 +4355,14 @@
       <c r="AU33">
         <v>1141</v>
       </c>
-    </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV33">
+        <v>18</v>
+      </c>
+      <c r="AW33">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>42979</v>
       </c>
@@ -4259,8 +4475,14 @@
       <c r="AU34">
         <v>927</v>
       </c>
-    </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV34">
+        <v>17</v>
+      </c>
+      <c r="AW34">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>43009</v>
       </c>
@@ -4360,8 +4582,14 @@
       <c r="AU35">
         <v>743</v>
       </c>
-    </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV35">
+        <v>19</v>
+      </c>
+      <c r="AW35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>43040</v>
       </c>
@@ -4461,8 +4689,14 @@
       <c r="AU36">
         <v>1392</v>
       </c>
-    </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV36">
+        <v>23</v>
+      </c>
+      <c r="AW36">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>43070</v>
       </c>
@@ -4575,8 +4809,14 @@
       <c r="AU37">
         <v>745</v>
       </c>
-    </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV37">
+        <v>23</v>
+      </c>
+      <c r="AW37">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>43101</v>
       </c>
@@ -4676,8 +4916,14 @@
       <c r="AU38">
         <v>536</v>
       </c>
-    </row>
-    <row r="39" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV38">
+        <v>16</v>
+      </c>
+      <c r="AW38">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>43132</v>
       </c>
@@ -4777,8 +5023,14 @@
       <c r="AU39">
         <v>748</v>
       </c>
-    </row>
-    <row r="40" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV39">
+        <v>21</v>
+      </c>
+      <c r="AW39">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>43160</v>
       </c>
@@ -4920,8 +5172,14 @@
       <c r="AU40">
         <v>1173</v>
       </c>
-    </row>
-    <row r="41" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV40">
+        <v>21</v>
+      </c>
+      <c r="AW40">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>43191</v>
       </c>
@@ -5021,8 +5279,14 @@
       <c r="AU41">
         <v>1115</v>
       </c>
-    </row>
-    <row r="42" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV41">
+        <v>20</v>
+      </c>
+      <c r="AW41">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>43221</v>
       </c>
@@ -5122,8 +5386,14 @@
       <c r="AU42">
         <v>1240</v>
       </c>
-    </row>
-    <row r="43" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV42">
+        <v>19</v>
+      </c>
+      <c r="AW42">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>43252</v>
       </c>
@@ -5236,8 +5506,14 @@
       <c r="AU43">
         <v>1062</v>
       </c>
-    </row>
-    <row r="44" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV43">
+        <v>18</v>
+      </c>
+      <c r="AW43">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43282</v>
       </c>
@@ -5337,8 +5613,14 @@
       <c r="AU44">
         <v>1021</v>
       </c>
-    </row>
-    <row r="45" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV44">
+        <v>16</v>
+      </c>
+      <c r="AW44">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>43313</v>
       </c>
@@ -5438,8 +5720,14 @@
       <c r="AU45">
         <v>1195</v>
       </c>
-    </row>
-    <row r="46" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV45">
+        <v>17</v>
+      </c>
+      <c r="AW45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>43344</v>
       </c>
@@ -5552,8 +5840,14 @@
       <c r="AU46">
         <v>886</v>
       </c>
-    </row>
-    <row r="47" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV46">
+        <v>17</v>
+      </c>
+      <c r="AW46">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>43374</v>
       </c>
@@ -5653,8 +5947,14 @@
       <c r="AU47">
         <v>894</v>
       </c>
-    </row>
-    <row r="48" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV47">
+        <v>18</v>
+      </c>
+      <c r="AW47">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>43405</v>
       </c>
@@ -5754,8 +6054,14 @@
       <c r="AU48">
         <v>1111</v>
       </c>
-    </row>
-    <row r="49" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV48">
+        <v>16</v>
+      </c>
+      <c r="AW48">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>43435</v>
       </c>
@@ -5868,8 +6174,14 @@
       <c r="AU49">
         <v>890</v>
       </c>
-    </row>
-    <row r="50" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV49">
+        <v>17</v>
+      </c>
+      <c r="AW49">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>43466</v>
       </c>
@@ -5969,8 +6281,14 @@
       <c r="AU50">
         <v>971</v>
       </c>
-    </row>
-    <row r="51" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV50">
+        <v>17</v>
+      </c>
+      <c r="AW50">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>43497</v>
       </c>
@@ -6070,8 +6388,14 @@
       <c r="AU51">
         <v>1284</v>
       </c>
-    </row>
-    <row r="52" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV51">
+        <v>17</v>
+      </c>
+      <c r="AW51">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>43525</v>
       </c>
@@ -6213,8 +6537,14 @@
       <c r="AU52">
         <v>1231</v>
       </c>
-    </row>
-    <row r="53" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV52">
+        <v>18</v>
+      </c>
+      <c r="AW52">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>43556</v>
       </c>
@@ -6314,8 +6644,14 @@
       <c r="AU53">
         <v>946</v>
       </c>
-    </row>
-    <row r="54" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV53">
+        <v>19</v>
+      </c>
+      <c r="AW53">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>43586</v>
       </c>
@@ -6415,8 +6751,14 @@
       <c r="AU54">
         <v>1709</v>
       </c>
-    </row>
-    <row r="55" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV54">
+        <v>18</v>
+      </c>
+      <c r="AW54">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>43617</v>
       </c>
@@ -6529,8 +6871,14 @@
       <c r="AU55">
         <v>1228</v>
       </c>
-    </row>
-    <row r="56" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV55">
+        <v>15</v>
+      </c>
+      <c r="AW55">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>43647</v>
       </c>
@@ -6630,8 +6978,14 @@
       <c r="AU56">
         <v>1319</v>
       </c>
-    </row>
-    <row r="57" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV56">
+        <v>15</v>
+      </c>
+      <c r="AW56">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>43678</v>
       </c>
@@ -6731,8 +7085,14 @@
       <c r="AU57">
         <v>1307</v>
       </c>
-    </row>
-    <row r="58" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV57">
+        <v>16</v>
+      </c>
+      <c r="AW57">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>43709</v>
       </c>
@@ -6845,8 +7205,14 @@
       <c r="AU58">
         <v>1603</v>
       </c>
-    </row>
-    <row r="59" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV58">
+        <v>17</v>
+      </c>
+      <c r="AW58">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>43739</v>
       </c>
@@ -6946,8 +7312,14 @@
       <c r="AU59">
         <v>1275</v>
       </c>
-    </row>
-    <row r="60" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV59">
+        <v>15</v>
+      </c>
+      <c r="AW59">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>43770</v>
       </c>
@@ -7047,8 +7419,14 @@
       <c r="AU60">
         <v>1232</v>
       </c>
-    </row>
-    <row r="61" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV60">
+        <v>15</v>
+      </c>
+      <c r="AW60">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>43800</v>
       </c>
@@ -7161,8 +7539,14 @@
       <c r="AU61">
         <v>1253</v>
       </c>
-    </row>
-    <row r="62" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV61">
+        <v>15</v>
+      </c>
+      <c r="AW61">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>43831</v>
       </c>
@@ -7262,8 +7646,14 @@
       <c r="AU62">
         <v>980</v>
       </c>
-    </row>
-    <row r="63" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV62">
+        <v>15</v>
+      </c>
+      <c r="AW62">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>43862</v>
       </c>
@@ -7363,8 +7753,14 @@
       <c r="AU63">
         <v>1291</v>
       </c>
-    </row>
-    <row r="64" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV63">
+        <v>15</v>
+      </c>
+      <c r="AW63">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>43891</v>
       </c>
@@ -7506,8 +7902,14 @@
       <c r="AU64">
         <v>1183</v>
       </c>
-    </row>
-    <row r="65" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV64">
+        <v>14</v>
+      </c>
+      <c r="AW64">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>43922</v>
       </c>
@@ -7607,8 +8009,14 @@
       <c r="AU65">
         <v>810</v>
       </c>
-    </row>
-    <row r="66" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV65">
+        <v>16</v>
+      </c>
+      <c r="AW65">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>43952</v>
       </c>
@@ -7708,8 +8116,14 @@
       <c r="AU66">
         <v>1628</v>
       </c>
-    </row>
-    <row r="67" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV66">
+        <v>0</v>
+      </c>
+      <c r="AW66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>43983</v>
       </c>
@@ -7822,8 +8236,14 @@
       <c r="AU67">
         <v>1592</v>
       </c>
-    </row>
-    <row r="68" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV67">
+        <v>26</v>
+      </c>
+      <c r="AW67">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>44013</v>
       </c>
@@ -7923,8 +8343,14 @@
       <c r="AU68">
         <v>1453</v>
       </c>
-    </row>
-    <row r="69" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV68">
+        <v>16</v>
+      </c>
+      <c r="AW68">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>44044</v>
       </c>
@@ -8024,8 +8450,14 @@
       <c r="AU69">
         <v>1356</v>
       </c>
-    </row>
-    <row r="70" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV69">
+        <v>13</v>
+      </c>
+      <c r="AW69">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>44075</v>
       </c>
@@ -8138,8 +8570,14 @@
       <c r="AU70">
         <v>1553</v>
       </c>
-    </row>
-    <row r="71" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV70">
+        <v>11</v>
+      </c>
+      <c r="AW70">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>44105</v>
       </c>
@@ -8239,8 +8677,14 @@
       <c r="AU71">
         <v>1703</v>
       </c>
-    </row>
-    <row r="72" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV71">
+        <v>11</v>
+      </c>
+      <c r="AW71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>44136</v>
       </c>
@@ -8340,8 +8784,14 @@
       <c r="AU72">
         <v>1825</v>
       </c>
-    </row>
-    <row r="73" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV72">
+        <v>9</v>
+      </c>
+      <c r="AW72">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>44166</v>
       </c>
@@ -8454,8 +8904,14 @@
       <c r="AU73">
         <v>1834</v>
       </c>
-    </row>
-    <row r="74" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV73">
+        <v>8</v>
+      </c>
+      <c r="AW73">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>44197</v>
       </c>
@@ -8555,8 +9011,14 @@
       <c r="AU74">
         <v>1538</v>
       </c>
-    </row>
-    <row r="75" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV74">
+        <v>8</v>
+      </c>
+      <c r="AW74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>44228</v>
       </c>
@@ -8656,8 +9118,14 @@
       <c r="AU75">
         <v>1185</v>
       </c>
-    </row>
-    <row r="76" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV75">
+        <v>9</v>
+      </c>
+      <c r="AW75">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>44256</v>
       </c>
@@ -8799,8 +9267,14 @@
       <c r="AU76">
         <v>1780</v>
       </c>
-    </row>
-    <row r="77" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV76">
+        <v>10</v>
+      </c>
+      <c r="AW76">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>44287</v>
       </c>
@@ -8900,8 +9374,14 @@
       <c r="AU77">
         <v>1855</v>
       </c>
-    </row>
-    <row r="78" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV77">
+        <v>8</v>
+      </c>
+      <c r="AW77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>44317</v>
       </c>
@@ -9001,8 +9481,14 @@
       <c r="AU78">
         <v>1775</v>
       </c>
-    </row>
-    <row r="79" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV78">
+        <v>8</v>
+      </c>
+      <c r="AW78">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>44348</v>
       </c>
@@ -9115,8 +9601,14 @@
       <c r="AU79">
         <v>1942</v>
       </c>
-    </row>
-    <row r="80" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV79">
+        <v>9</v>
+      </c>
+      <c r="AW79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>44378</v>
       </c>
@@ -9216,8 +9708,14 @@
       <c r="AU80">
         <v>1906</v>
       </c>
-    </row>
-    <row r="81" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV80">
+        <v>8</v>
+      </c>
+      <c r="AW80">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>44409</v>
       </c>
@@ -9317,8 +9815,14 @@
       <c r="AU81">
         <v>2314</v>
       </c>
-    </row>
-    <row r="82" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV81">
+        <v>8</v>
+      </c>
+      <c r="AW81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>44440</v>
       </c>
@@ -9431,8 +9935,14 @@
       <c r="AU82">
         <v>2310</v>
       </c>
-    </row>
-    <row r="83" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV82">
+        <v>10</v>
+      </c>
+      <c r="AW82">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>44470</v>
       </c>
@@ -9532,8 +10042,14 @@
       <c r="AU83">
         <v>1946</v>
       </c>
-    </row>
-    <row r="84" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV83">
+        <v>12</v>
+      </c>
+      <c r="AW83">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>44501</v>
       </c>
@@ -9633,8 +10149,14 @@
       <c r="AU84">
         <v>2564</v>
       </c>
-    </row>
-    <row r="85" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV84">
+        <v>10</v>
+      </c>
+      <c r="AW84">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>44531</v>
       </c>
@@ -9747,8 +10269,14 @@
       <c r="AU85">
         <v>2305</v>
       </c>
-    </row>
-    <row r="86" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV85">
+        <v>11</v>
+      </c>
+      <c r="AW85">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>44562</v>
       </c>
@@ -9848,8 +10376,14 @@
       <c r="AU86">
         <v>1400</v>
       </c>
-    </row>
-    <row r="87" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV86">
+        <v>13</v>
+      </c>
+      <c r="AW86">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>44593</v>
       </c>
@@ -9949,8 +10483,14 @@
       <c r="AU87">
         <v>2245</v>
       </c>
-    </row>
-    <row r="88" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV87">
+        <v>17</v>
+      </c>
+      <c r="AW87">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>44621</v>
       </c>
@@ -10092,8 +10632,14 @@
       <c r="AU88">
         <v>3000</v>
       </c>
-    </row>
-    <row r="89" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV88">
+        <v>17</v>
+      </c>
+      <c r="AW88">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>44652</v>
       </c>
@@ -10193,8 +10739,14 @@
       <c r="AU89">
         <v>2066</v>
       </c>
-    </row>
-    <row r="90" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV89">
+        <v>20</v>
+      </c>
+      <c r="AW89">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>44682</v>
       </c>
@@ -10294,8 +10846,14 @@
       <c r="AU90">
         <v>2481</v>
       </c>
-    </row>
-    <row r="91" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV90">
+        <v>21</v>
+      </c>
+      <c r="AW90">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>44713</v>
       </c>
@@ -10408,8 +10966,14 @@
       <c r="AU91">
         <v>2286</v>
       </c>
-    </row>
-    <row r="92" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV91">
+        <v>23</v>
+      </c>
+      <c r="AW91">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>44743</v>
       </c>
@@ -10509,8 +11073,14 @@
       <c r="AU92">
         <v>2370</v>
       </c>
-    </row>
-    <row r="93" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV92">
+        <v>26</v>
+      </c>
+      <c r="AW92">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>44774</v>
       </c>
@@ -10610,8 +11180,14 @@
       <c r="AU93">
         <v>2620</v>
       </c>
-    </row>
-    <row r="94" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV93">
+        <v>25</v>
+      </c>
+      <c r="AW93">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>44805</v>
       </c>
@@ -10724,8 +11300,14 @@
       <c r="AU94">
         <v>2752</v>
       </c>
-    </row>
-    <row r="95" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV94">
+        <v>24</v>
+      </c>
+      <c r="AW94">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>44835</v>
       </c>
@@ -10825,8 +11407,14 @@
       <c r="AU95">
         <v>2027</v>
       </c>
-    </row>
-    <row r="96" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV95">
+        <v>25</v>
+      </c>
+      <c r="AW95">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>44866</v>
       </c>
@@ -10926,8 +11514,14 @@
       <c r="AU96">
         <v>2812</v>
       </c>
-    </row>
-    <row r="97" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV96">
+        <v>23</v>
+      </c>
+      <c r="AW96">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>44896</v>
       </c>
@@ -11040,8 +11634,14 @@
       <c r="AU97">
         <v>2079</v>
       </c>
-    </row>
-    <row r="98" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV97">
+        <v>28</v>
+      </c>
+      <c r="AW97">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>44927</v>
       </c>
@@ -11141,8 +11741,14 @@
       <c r="AU98">
         <v>1710</v>
       </c>
-    </row>
-    <row r="99" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV98">
+        <v>28</v>
+      </c>
+      <c r="AW98">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>44958</v>
       </c>
@@ -11242,8 +11848,14 @@
       <c r="AU99">
         <v>1669</v>
       </c>
-    </row>
-    <row r="100" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV99">
+        <v>26</v>
+      </c>
+      <c r="AW99">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>44986</v>
       </c>
@@ -11385,8 +11997,14 @@
       <c r="AU100">
         <v>2385</v>
       </c>
-    </row>
-    <row r="101" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV100">
+        <v>27</v>
+      </c>
+      <c r="AW100">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>45017</v>
       </c>
@@ -11486,8 +12104,14 @@
       <c r="AU101">
         <v>1638</v>
       </c>
-    </row>
-    <row r="102" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV101">
+        <v>26</v>
+      </c>
+      <c r="AW101">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>45047</v>
       </c>
@@ -11587,8 +12211,14 @@
       <c r="AU102">
         <v>2082</v>
       </c>
-    </row>
-    <row r="103" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV102">
+        <v>22</v>
+      </c>
+      <c r="AW102">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>45078</v>
       </c>
@@ -11701,8 +12331,14 @@
       <c r="AU103">
         <v>1887</v>
       </c>
-    </row>
-    <row r="104" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV103">
+        <v>24</v>
+      </c>
+      <c r="AW103">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>45108</v>
       </c>
@@ -11802,8 +12438,14 @@
       <c r="AU104">
         <v>1875</v>
       </c>
-    </row>
-    <row r="105" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV104">
+        <v>19</v>
+      </c>
+      <c r="AW104">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>45139</v>
       </c>
@@ -11903,8 +12545,14 @@
       <c r="AU105">
         <v>1927</v>
       </c>
-    </row>
-    <row r="106" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV105">
+        <v>22</v>
+      </c>
+      <c r="AW105">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>45170</v>
       </c>
@@ -12017,8 +12665,14 @@
       <c r="AU106">
         <v>1698</v>
       </c>
-    </row>
-    <row r="107" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV106">
+        <v>21</v>
+      </c>
+      <c r="AW106">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>45200</v>
       </c>
@@ -12118,8 +12772,14 @@
       <c r="AU107">
         <v>1805</v>
       </c>
-    </row>
-    <row r="108" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV107">
+        <v>21</v>
+      </c>
+      <c r="AW107">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>45231</v>
       </c>
@@ -12219,8 +12879,14 @@
       <c r="AU108">
         <v>1496</v>
       </c>
-    </row>
-    <row r="109" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV108">
+        <v>22</v>
+      </c>
+      <c r="AW108">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>45261</v>
       </c>
@@ -12333,8 +12999,14 @@
       <c r="AU109">
         <v>1392</v>
       </c>
-    </row>
-    <row r="110" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV109">
+        <v>23</v>
+      </c>
+      <c r="AW109">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>45292</v>
       </c>
@@ -12434,8 +13106,14 @@
       <c r="AU110">
         <v>1092</v>
       </c>
-    </row>
-    <row r="111" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV110">
+        <v>22</v>
+      </c>
+      <c r="AW110">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>45323</v>
       </c>
@@ -12535,8 +13213,14 @@
       <c r="AU111">
         <v>1498</v>
       </c>
-    </row>
-    <row r="112" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV111">
+        <v>24</v>
+      </c>
+      <c r="AW111">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>45352</v>
       </c>
@@ -12678,8 +13362,14 @@
       <c r="AU112">
         <v>1680</v>
       </c>
-    </row>
-    <row r="113" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV112">
+        <v>22</v>
+      </c>
+      <c r="AW112">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>45383</v>
       </c>
@@ -12779,8 +13469,14 @@
       <c r="AU113">
         <v>1572</v>
       </c>
-    </row>
-    <row r="114" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV113">
+        <v>24</v>
+      </c>
+      <c r="AW113">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>45413</v>
       </c>
@@ -12880,8 +13576,14 @@
       <c r="AU114">
         <v>1620</v>
       </c>
-    </row>
-    <row r="115" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV114">
+        <v>23</v>
+      </c>
+      <c r="AW114">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>45444</v>
       </c>
@@ -12994,8 +13696,14 @@
       <c r="AU115">
         <v>1056</v>
       </c>
-    </row>
-    <row r="116" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV115">
+        <v>26</v>
+      </c>
+      <c r="AW115">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>45474</v>
       </c>
@@ -13095,8 +13803,14 @@
       <c r="AU116">
         <v>1667</v>
       </c>
-    </row>
-    <row r="117" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV116">
+        <v>31</v>
+      </c>
+      <c r="AW116">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>45505</v>
       </c>
@@ -13196,8 +13910,14 @@
       <c r="AU117">
         <v>1459</v>
       </c>
-    </row>
-    <row r="118" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV117">
+        <v>26</v>
+      </c>
+      <c r="AW117">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>45536</v>
       </c>
@@ -13310,8 +14030,14 @@
       <c r="AU118">
         <v>1565</v>
       </c>
-    </row>
-    <row r="119" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV118">
+        <v>26</v>
+      </c>
+      <c r="AW118">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>45566</v>
       </c>
@@ -13411,8 +14137,14 @@
       <c r="AU119">
         <v>1487</v>
       </c>
-    </row>
-    <row r="120" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV119">
+        <v>24</v>
+      </c>
+      <c r="AW119">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>45597</v>
       </c>
@@ -13512,8 +14244,14 @@
       <c r="AU120">
         <v>1698</v>
       </c>
-    </row>
-    <row r="121" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV120">
+        <v>23</v>
+      </c>
+      <c r="AW120">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>45627</v>
       </c>
@@ -13626,8 +14364,14 @@
       <c r="AU121">
         <v>1426</v>
       </c>
-    </row>
-    <row r="122" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV121">
+        <v>23</v>
+      </c>
+      <c r="AW121">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>45658</v>
       </c>
@@ -13727,8 +14471,14 @@
       <c r="AU122">
         <v>1126</v>
       </c>
-    </row>
-    <row r="123" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV122">
+        <v>24</v>
+      </c>
+      <c r="AW122">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>45689</v>
       </c>
@@ -13828,8 +14578,14 @@
       <c r="AU123">
         <v>1387</v>
       </c>
-    </row>
-    <row r="124" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV123">
+        <v>24</v>
+      </c>
+      <c r="AW123">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>45717</v>
       </c>
@@ -13971,8 +14727,14 @@
       <c r="AU124">
         <v>2024</v>
       </c>
-    </row>
-    <row r="125" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV124">
+        <v>22</v>
+      </c>
+      <c r="AW124">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>45748</v>
       </c>
@@ -14072,8 +14834,14 @@
       <c r="AU125">
         <v>1270</v>
       </c>
-    </row>
-    <row r="126" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV125">
+        <v>22</v>
+      </c>
+      <c r="AW125">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>45778</v>
       </c>
@@ -14173,8 +14941,14 @@
       <c r="AU126">
         <v>1687</v>
       </c>
-    </row>
-    <row r="127" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV126">
+        <v>22</v>
+      </c>
+      <c r="AW126">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>45809</v>
       </c>
@@ -14287,8 +15061,14 @@
       <c r="AU127">
         <v>1325</v>
       </c>
-    </row>
-    <row r="128" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV127">
+        <v>22</v>
+      </c>
+      <c r="AW127">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>45839</v>
       </c>
@@ -14388,8 +15168,14 @@
       <c r="AU128">
         <v>1740</v>
       </c>
-    </row>
-    <row r="129" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV128">
+        <v>22</v>
+      </c>
+      <c r="AW128">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>45870</v>
       </c>
@@ -14489,8 +15275,14 @@
       <c r="AU129">
         <v>1588</v>
       </c>
-    </row>
-    <row r="130" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV129">
+        <v>24</v>
+      </c>
+      <c r="AW129">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>45901</v>
       </c>
@@ -14603,8 +15395,14 @@
       <c r="AU130">
         <v>2146</v>
       </c>
-    </row>
-    <row r="131" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV130">
+        <v>24</v>
+      </c>
+      <c r="AW130">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>45931</v>
       </c>
@@ -14704,8 +15502,14 @@
       <c r="AU131">
         <v>1952</v>
       </c>
-    </row>
-    <row r="132" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV131">
+        <v>23</v>
+      </c>
+      <c r="AW131">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="132" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>45962</v>
       </c>
@@ -14805,8 +15609,14 @@
       <c r="AU132">
         <v>1910</v>
       </c>
-    </row>
-    <row r="133" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV132">
+        <v>22</v>
+      </c>
+      <c r="AW132">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>45992</v>
       </c>
@@ -14919,8 +15729,14 @@
       <c r="AU133">
         <v>1829</v>
       </c>
-    </row>
-    <row r="134" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV133">
+        <v>22</v>
+      </c>
+      <c r="AW133">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>46023</v>
       </c>
@@ -15020,8 +15836,14 @@
       <c r="AU134">
         <v>1338</v>
       </c>
-    </row>
-    <row r="135" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV134">
+        <v>22</v>
+      </c>
+      <c r="AW134">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>46054</v>
       </c>
@@ -15115,8 +15937,14 @@
       <c r="AU135">
         <v>1636</v>
       </c>
-    </row>
-    <row r="136" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV135">
+        <v>24</v>
+      </c>
+      <c r="AW135">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>46082</v>
       </c>
@@ -15231,8 +16059,14 @@
       <c r="AU136">
         <v>1948</v>
       </c>
-    </row>
-    <row r="137" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV136">
+        <v>22</v>
+      </c>
+      <c r="AW136">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="137" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>46113</v>
       </c>
@@ -15326,8 +16160,14 @@
       <c r="AU137">
         <v>2088</v>
       </c>
-    </row>
-    <row r="138" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV137">
+        <v>22</v>
+      </c>
+      <c r="AW137">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="138" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>46143</v>
       </c>
@@ -15421,8 +16261,14 @@
       <c r="AU138">
         <v>1966</v>
       </c>
-    </row>
-    <row r="139" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV138">
+        <v>24</v>
+      </c>
+      <c r="AW138">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>46174</v>
       </c>
@@ -15525,8 +16371,14 @@
       <c r="AU139">
         <v>1813</v>
       </c>
-    </row>
-    <row r="140" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV139">
+        <v>25</v>
+      </c>
+      <c r="AW139">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>46204</v>
       </c>
@@ -15618,8 +16470,14 @@
       <c r="AU140">
         <v>1810</v>
       </c>
-    </row>
-    <row r="141" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV140">
+        <v>24</v>
+      </c>
+      <c r="AW140">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>46235</v>
       </c>
@@ -15697,8 +16555,18 @@
       <c r="AU141">
         <v>1736</v>
       </c>
-    </row>
-    <row r="142" spans="1:47" x14ac:dyDescent="0.35">
+      <c r="AV141">
+        <v>26</v>
+      </c>
+      <c r="AW141">
+        <v>15</v>
+      </c>
+      <c r="BA141">
+        <f ca="1">BA141</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>46266</v>
       </c>
@@ -15731,6 +16599,12 @@
       <c r="AH142">
         <v>2</v>
       </c>
+      <c r="AV142">
+        <v>27</v>
+      </c>
+      <c r="AW142">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Time_series_data.xlsx
+++ b/Time_series_data.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Documents\DATA309\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64aae3e7249de19e/Documents/DATA309-Housing-Affordability/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD18F50-42D1-4584-9E35-3BF8A0A5C17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="22780" windowHeight="14540" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Combined" sheetId="1" r:id="rId1"/>
@@ -237,7 +237,7 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -543,12 +543,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BA142"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="23" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:53" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -697,7 +697,7 @@
       <c r="AZ1" s="6"/>
       <c r="BA1" s="6"/>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>42005</v>
       </c>
@@ -798,7 +798,7 @@
         <v>562</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>42036</v>
       </c>
@@ -899,7 +899,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A4" s="2">
         <v>42064</v>
       </c>
@@ -1042,7 +1042,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A5" s="2">
         <v>42095</v>
       </c>
@@ -1143,7 +1143,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A6" s="2">
         <v>42125</v>
       </c>
@@ -1244,7 +1244,7 @@
         <v>584</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A7" s="2">
         <v>42156</v>
       </c>
@@ -1358,7 +1358,7 @@
         <v>540</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A8" s="2">
         <v>42186</v>
       </c>
@@ -1459,7 +1459,7 @@
         <v>1025</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A9" s="2">
         <v>42217</v>
       </c>
@@ -1560,7 +1560,7 @@
         <v>674</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A10" s="2">
         <v>42248</v>
       </c>
@@ -1674,7 +1674,7 @@
         <v>461</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A11" s="2">
         <v>42278</v>
       </c>
@@ -1775,7 +1775,7 @@
         <v>617</v>
       </c>
     </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A12" s="2">
         <v>42309</v>
       </c>
@@ -1876,7 +1876,7 @@
         <v>967</v>
       </c>
     </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A13" s="2">
         <v>42339</v>
       </c>
@@ -1990,7 +1990,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A14" s="2">
         <v>42370</v>
       </c>
@@ -2091,7 +2091,7 @@
         <v>409</v>
       </c>
     </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A15" s="2">
         <v>42401</v>
       </c>
@@ -2192,7 +2192,7 @@
         <v>667</v>
       </c>
     </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
       <c r="A16" s="2">
         <v>42430</v>
       </c>
@@ -2335,7 +2335,7 @@
         <v>500</v>
       </c>
     </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A17" s="2">
         <v>42461</v>
       </c>
@@ -2436,7 +2436,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A18" s="2">
         <v>42491</v>
       </c>
@@ -2537,7 +2537,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A19" s="2">
         <v>42522</v>
       </c>
@@ -2651,7 +2651,7 @@
         <v>889</v>
       </c>
     </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A20" s="2">
         <v>42552</v>
       </c>
@@ -2752,7 +2752,7 @@
         <v>1050</v>
       </c>
     </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A21" s="2">
         <v>42583</v>
       </c>
@@ -2853,7 +2853,7 @@
         <v>819</v>
       </c>
     </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A22" s="2">
         <v>42614</v>
       </c>
@@ -2967,7 +2967,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A23" s="2">
         <v>42644</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>773</v>
       </c>
     </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A24" s="2">
         <v>42675</v>
       </c>
@@ -3169,7 +3169,7 @@
         <v>1119</v>
       </c>
     </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A25" s="2">
         <v>42705</v>
       </c>
@@ -3283,7 +3283,7 @@
         <v>625</v>
       </c>
     </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A26" s="2">
         <v>42736</v>
       </c>
@@ -3384,7 +3384,7 @@
         <v>499</v>
       </c>
     </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A27" s="2">
         <v>42767</v>
       </c>
@@ -3485,7 +3485,7 @@
         <v>657</v>
       </c>
     </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A28" s="2">
         <v>42795</v>
       </c>
@@ -3628,7 +3628,7 @@
         <v>856</v>
       </c>
     </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A29" s="2">
         <v>42826</v>
       </c>
@@ -3729,7 +3729,7 @@
         <v>619</v>
       </c>
     </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A30" s="2">
         <v>42856</v>
       </c>
@@ -3830,7 +3830,7 @@
         <v>755</v>
       </c>
     </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A31" s="2">
         <v>42887</v>
       </c>
@@ -3944,7 +3944,7 @@
         <v>869</v>
       </c>
     </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A32" s="2">
         <v>42917</v>
       </c>
@@ -4045,7 +4045,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A33" s="2">
         <v>42948</v>
       </c>
@@ -4146,7 +4146,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A34" s="2">
         <v>42979</v>
       </c>
@@ -4260,7 +4260,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A35" s="2">
         <v>43009</v>
       </c>
@@ -4361,7 +4361,7 @@
         <v>743</v>
       </c>
     </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A36" s="2">
         <v>43040</v>
       </c>
@@ -4462,7 +4462,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A37" s="2">
         <v>43070</v>
       </c>
@@ -4576,7 +4576,7 @@
         <v>745</v>
       </c>
     </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A38" s="2">
         <v>43101</v>
       </c>
@@ -4677,7 +4677,7 @@
         <v>536</v>
       </c>
     </row>
-    <row r="39" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A39" s="2">
         <v>43132</v>
       </c>
@@ -4778,7 +4778,7 @@
         <v>748</v>
       </c>
     </row>
-    <row r="40" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A40" s="2">
         <v>43160</v>
       </c>
@@ -4921,7 +4921,7 @@
         <v>1173</v>
       </c>
     </row>
-    <row r="41" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A41" s="2">
         <v>43191</v>
       </c>
@@ -5022,7 +5022,7 @@
         <v>1115</v>
       </c>
     </row>
-    <row r="42" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A42" s="2">
         <v>43221</v>
       </c>
@@ -5123,7 +5123,7 @@
         <v>1240</v>
       </c>
     </row>
-    <row r="43" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A43" s="2">
         <v>43252</v>
       </c>
@@ -5237,7 +5237,7 @@
         <v>1062</v>
       </c>
     </row>
-    <row r="44" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A44" s="2">
         <v>43282</v>
       </c>
@@ -5338,7 +5338,7 @@
         <v>1021</v>
       </c>
     </row>
-    <row r="45" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A45" s="2">
         <v>43313</v>
       </c>
@@ -5439,7 +5439,7 @@
         <v>1195</v>
       </c>
     </row>
-    <row r="46" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A46" s="2">
         <v>43344</v>
       </c>
@@ -5553,7 +5553,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="47" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A47" s="2">
         <v>43374</v>
       </c>
@@ -5654,7 +5654,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="48" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A48" s="2">
         <v>43405</v>
       </c>
@@ -5755,7 +5755,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="49" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A49" s="2">
         <v>43435</v>
       </c>
@@ -5869,7 +5869,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="50" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A50" s="2">
         <v>43466</v>
       </c>
@@ -5970,7 +5970,7 @@
         <v>971</v>
       </c>
     </row>
-    <row r="51" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A51" s="2">
         <v>43497</v>
       </c>
@@ -6071,7 +6071,7 @@
         <v>1284</v>
       </c>
     </row>
-    <row r="52" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A52" s="2">
         <v>43525</v>
       </c>
@@ -6214,7 +6214,7 @@
         <v>1231</v>
       </c>
     </row>
-    <row r="53" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A53" s="2">
         <v>43556</v>
       </c>
@@ -6315,7 +6315,7 @@
         <v>946</v>
       </c>
     </row>
-    <row r="54" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A54" s="2">
         <v>43586</v>
       </c>
@@ -6416,7 +6416,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="55" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A55" s="2">
         <v>43617</v>
       </c>
@@ -6530,7 +6530,7 @@
         <v>1228</v>
       </c>
     </row>
-    <row r="56" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A56" s="2">
         <v>43647</v>
       </c>
@@ -6631,7 +6631,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="57" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A57" s="2">
         <v>43678</v>
       </c>
@@ -6732,7 +6732,7 @@
         <v>1307</v>
       </c>
     </row>
-    <row r="58" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A58" s="2">
         <v>43709</v>
       </c>
@@ -6846,7 +6846,7 @@
         <v>1603</v>
       </c>
     </row>
-    <row r="59" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A59" s="2">
         <v>43739</v>
       </c>
@@ -6947,7 +6947,7 @@
         <v>1275</v>
       </c>
     </row>
-    <row r="60" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A60" s="2">
         <v>43770</v>
       </c>
@@ -7048,7 +7048,7 @@
         <v>1232</v>
       </c>
     </row>
-    <row r="61" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A61" s="2">
         <v>43800</v>
       </c>
@@ -7162,7 +7162,7 @@
         <v>1253</v>
       </c>
     </row>
-    <row r="62" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A62" s="2">
         <v>43831</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>980</v>
       </c>
     </row>
-    <row r="63" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A63" s="2">
         <v>43862</v>
       </c>
@@ -7364,7 +7364,7 @@
         <v>1291</v>
       </c>
     </row>
-    <row r="64" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A64" s="2">
         <v>43891</v>
       </c>
@@ -7507,7 +7507,7 @@
         <v>1183</v>
       </c>
     </row>
-    <row r="65" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A65" s="2">
         <v>43922</v>
       </c>
@@ -7608,7 +7608,7 @@
         <v>810</v>
       </c>
     </row>
-    <row r="66" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A66" s="2">
         <v>43952</v>
       </c>
@@ -7709,7 +7709,7 @@
         <v>1628</v>
       </c>
     </row>
-    <row r="67" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A67" s="2">
         <v>43983</v>
       </c>
@@ -7823,7 +7823,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="68" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A68" s="2">
         <v>44013</v>
       </c>
@@ -7924,7 +7924,7 @@
         <v>1453</v>
       </c>
     </row>
-    <row r="69" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A69" s="2">
         <v>44044</v>
       </c>
@@ -8025,7 +8025,7 @@
         <v>1356</v>
       </c>
     </row>
-    <row r="70" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A70" s="2">
         <v>44075</v>
       </c>
@@ -8139,7 +8139,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="71" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A71" s="2">
         <v>44105</v>
       </c>
@@ -8240,7 +8240,7 @@
         <v>1703</v>
       </c>
     </row>
-    <row r="72" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A72" s="2">
         <v>44136</v>
       </c>
@@ -8341,7 +8341,7 @@
         <v>1825</v>
       </c>
     </row>
-    <row r="73" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A73" s="2">
         <v>44166</v>
       </c>
@@ -8455,7 +8455,7 @@
         <v>1834</v>
       </c>
     </row>
-    <row r="74" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A74" s="2">
         <v>44197</v>
       </c>
@@ -8556,7 +8556,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="75" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A75" s="2">
         <v>44228</v>
       </c>
@@ -8657,7 +8657,7 @@
         <v>1185</v>
       </c>
     </row>
-    <row r="76" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A76" s="2">
         <v>44256</v>
       </c>
@@ -8800,7 +8800,7 @@
         <v>1780</v>
       </c>
     </row>
-    <row r="77" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A77" s="2">
         <v>44287</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>1855</v>
       </c>
     </row>
-    <row r="78" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A78" s="2">
         <v>44317</v>
       </c>
@@ -9002,7 +9002,7 @@
         <v>1775</v>
       </c>
     </row>
-    <row r="79" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A79" s="2">
         <v>44348</v>
       </c>
@@ -9116,7 +9116,7 @@
         <v>1942</v>
       </c>
     </row>
-    <row r="80" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A80" s="2">
         <v>44378</v>
       </c>
@@ -9217,7 +9217,7 @@
         <v>1906</v>
       </c>
     </row>
-    <row r="81" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A81" s="2">
         <v>44409</v>
       </c>
@@ -9318,7 +9318,7 @@
         <v>2314</v>
       </c>
     </row>
-    <row r="82" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A82" s="2">
         <v>44440</v>
       </c>
@@ -9432,7 +9432,7 @@
         <v>2310</v>
       </c>
     </row>
-    <row r="83" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A83" s="2">
         <v>44470</v>
       </c>
@@ -9533,7 +9533,7 @@
         <v>1946</v>
       </c>
     </row>
-    <row r="84" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A84" s="2">
         <v>44501</v>
       </c>
@@ -9634,7 +9634,7 @@
         <v>2564</v>
       </c>
     </row>
-    <row r="85" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A85" s="2">
         <v>44531</v>
       </c>
@@ -9748,7 +9748,7 @@
         <v>2305</v>
       </c>
     </row>
-    <row r="86" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A86" s="2">
         <v>44562</v>
       </c>
@@ -9849,7 +9849,7 @@
         <v>1400</v>
       </c>
     </row>
-    <row r="87" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A87" s="2">
         <v>44593</v>
       </c>
@@ -9950,7 +9950,7 @@
         <v>2245</v>
       </c>
     </row>
-    <row r="88" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A88" s="2">
         <v>44621</v>
       </c>
@@ -10093,7 +10093,7 @@
         <v>3000</v>
       </c>
     </row>
-    <row r="89" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A89" s="2">
         <v>44652</v>
       </c>
@@ -10194,7 +10194,7 @@
         <v>2066</v>
       </c>
     </row>
-    <row r="90" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A90" s="2">
         <v>44682</v>
       </c>
@@ -10295,7 +10295,7 @@
         <v>2481</v>
       </c>
     </row>
-    <row r="91" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A91" s="2">
         <v>44713</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>2286</v>
       </c>
     </row>
-    <row r="92" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A92" s="2">
         <v>44743</v>
       </c>
@@ -10510,7 +10510,7 @@
         <v>2370</v>
       </c>
     </row>
-    <row r="93" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A93" s="2">
         <v>44774</v>
       </c>
@@ -10611,7 +10611,7 @@
         <v>2620</v>
       </c>
     </row>
-    <row r="94" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A94" s="2">
         <v>44805</v>
       </c>
@@ -10725,7 +10725,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="95" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A95" s="2">
         <v>44835</v>
       </c>
@@ -10826,7 +10826,7 @@
         <v>2027</v>
       </c>
     </row>
-    <row r="96" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A96" s="2">
         <v>44866</v>
       </c>
@@ -10927,7 +10927,7 @@
         <v>2812</v>
       </c>
     </row>
-    <row r="97" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A97" s="2">
         <v>44896</v>
       </c>
@@ -11041,7 +11041,7 @@
         <v>2079</v>
       </c>
     </row>
-    <row r="98" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A98" s="2">
         <v>44927</v>
       </c>
@@ -11142,7 +11142,7 @@
         <v>1710</v>
       </c>
     </row>
-    <row r="99" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A99" s="2">
         <v>44958</v>
       </c>
@@ -11243,7 +11243,7 @@
         <v>1669</v>
       </c>
     </row>
-    <row r="100" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A100" s="2">
         <v>44986</v>
       </c>
@@ -11386,7 +11386,7 @@
         <v>2385</v>
       </c>
     </row>
-    <row r="101" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A101" s="2">
         <v>45017</v>
       </c>
@@ -11487,7 +11487,7 @@
         <v>1638</v>
       </c>
     </row>
-    <row r="102" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A102" s="2">
         <v>45047</v>
       </c>
@@ -11588,7 +11588,7 @@
         <v>2082</v>
       </c>
     </row>
-    <row r="103" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A103" s="2">
         <v>45078</v>
       </c>
@@ -11702,7 +11702,7 @@
         <v>1887</v>
       </c>
     </row>
-    <row r="104" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A104" s="2">
         <v>45108</v>
       </c>
@@ -11803,7 +11803,7 @@
         <v>1875</v>
       </c>
     </row>
-    <row r="105" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A105" s="2">
         <v>45139</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>1927</v>
       </c>
     </row>
-    <row r="106" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A106" s="2">
         <v>45170</v>
       </c>
@@ -12018,7 +12018,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="107" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A107" s="2">
         <v>45200</v>
       </c>
@@ -12119,7 +12119,7 @@
         <v>1805</v>
       </c>
     </row>
-    <row r="108" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A108" s="2">
         <v>45231</v>
       </c>
@@ -12220,7 +12220,7 @@
         <v>1496</v>
       </c>
     </row>
-    <row r="109" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A109" s="2">
         <v>45261</v>
       </c>
@@ -12334,7 +12334,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="110" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A110" s="2">
         <v>45292</v>
       </c>
@@ -12435,7 +12435,7 @@
         <v>1092</v>
       </c>
     </row>
-    <row r="111" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A111" s="2">
         <v>45323</v>
       </c>
@@ -12536,7 +12536,7 @@
         <v>1498</v>
       </c>
     </row>
-    <row r="112" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A112" s="2">
         <v>45352</v>
       </c>
@@ -12679,7 +12679,7 @@
         <v>1680</v>
       </c>
     </row>
-    <row r="113" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A113" s="2">
         <v>45383</v>
       </c>
@@ -12780,7 +12780,7 @@
         <v>1572</v>
       </c>
     </row>
-    <row r="114" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A114" s="2">
         <v>45413</v>
       </c>
@@ -12881,7 +12881,7 @@
         <v>1620</v>
       </c>
     </row>
-    <row r="115" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A115" s="2">
         <v>45444</v>
       </c>
@@ -12995,7 +12995,7 @@
         <v>1056</v>
       </c>
     </row>
-    <row r="116" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A116" s="2">
         <v>45474</v>
       </c>
@@ -13096,7 +13096,7 @@
         <v>1667</v>
       </c>
     </row>
-    <row r="117" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A117" s="2">
         <v>45505</v>
       </c>
@@ -13197,7 +13197,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="118" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A118" s="2">
         <v>45536</v>
       </c>
@@ -13311,7 +13311,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="119" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A119" s="2">
         <v>45566</v>
       </c>
@@ -13412,7 +13412,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="120" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A120" s="2">
         <v>45597</v>
       </c>
@@ -13513,7 +13513,7 @@
         <v>1698</v>
       </c>
     </row>
-    <row r="121" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A121" s="2">
         <v>45627</v>
       </c>
@@ -13627,7 +13627,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="122" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A122" s="2">
         <v>45658</v>
       </c>
@@ -13728,7 +13728,7 @@
         <v>1126</v>
       </c>
     </row>
-    <row r="123" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A123" s="2">
         <v>45689</v>
       </c>
@@ -13829,7 +13829,7 @@
         <v>1387</v>
       </c>
     </row>
-    <row r="124" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A124" s="2">
         <v>45717</v>
       </c>
@@ -13972,7 +13972,7 @@
         <v>2024</v>
       </c>
     </row>
-    <row r="125" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A125" s="2">
         <v>45748</v>
       </c>
@@ -14073,7 +14073,7 @@
         <v>1270</v>
       </c>
     </row>
-    <row r="126" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A126" s="2">
         <v>45778</v>
       </c>
@@ -14174,7 +14174,7 @@
         <v>1687</v>
       </c>
     </row>
-    <row r="127" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A127" s="2">
         <v>45809</v>
       </c>
@@ -14288,7 +14288,7 @@
         <v>1325</v>
       </c>
     </row>
-    <row r="128" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A128" s="2">
         <v>45839</v>
       </c>
@@ -14389,7 +14389,7 @@
         <v>1740</v>
       </c>
     </row>
-    <row r="129" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A129" s="2">
         <v>45870</v>
       </c>
@@ -14490,7 +14490,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="130" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A130" s="2">
         <v>45901</v>
       </c>
@@ -14604,7 +14604,7 @@
         <v>2146</v>
       </c>
     </row>
-    <row r="131" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A131" s="2">
         <v>45931</v>
       </c>
@@ -14705,7 +14705,7 @@
         <v>1952</v>
       </c>
     </row>
-    <row r="132" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A132" s="2">
         <v>45962</v>
       </c>
@@ -14806,7 +14806,7 @@
         <v>1910</v>
       </c>
     </row>
-    <row r="133" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A133" s="2">
         <v>45992</v>
       </c>
@@ -14920,7 +14920,7 @@
         <v>1829</v>
       </c>
     </row>
-    <row r="134" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A134" s="2">
         <v>46023</v>
       </c>
@@ -15021,7 +15021,7 @@
         <v>1338</v>
       </c>
     </row>
-    <row r="135" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A135" s="2">
         <v>46054</v>
       </c>
@@ -15116,7 +15116,7 @@
         <v>1636</v>
       </c>
     </row>
-    <row r="136" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A136" s="2">
         <v>46082</v>
       </c>
@@ -15232,7 +15232,7 @@
         <v>1948</v>
       </c>
     </row>
-    <row r="137" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A137" s="2">
         <v>46113</v>
       </c>
@@ -15327,7 +15327,7 @@
         <v>2088</v>
       </c>
     </row>
-    <row r="138" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A138" s="2">
         <v>46143</v>
       </c>
@@ -15422,7 +15422,7 @@
         <v>1966</v>
       </c>
     </row>
-    <row r="139" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A139" s="2">
         <v>46174</v>
       </c>
@@ -15526,7 +15526,7 @@
         <v>1813</v>
       </c>
     </row>
-    <row r="140" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A140" s="2">
         <v>46204</v>
       </c>
@@ -15619,7 +15619,7 @@
         <v>1810</v>
       </c>
     </row>
-    <row r="141" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A141" s="2">
         <v>46235</v>
       </c>
@@ -15698,7 +15698,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="142" spans="1:47" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:47" x14ac:dyDescent="0.3">
       <c r="A142" s="2">
         <v>46266</v>
       </c>
@@ -15740,12 +15740,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B612"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -15753,7 +15753,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" s="4">
         <v>42006</v>
       </c>
@@ -15761,7 +15761,7 @@
         <v>183.04151139999999</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" s="4">
         <v>42013</v>
       </c>
@@ -15769,7 +15769,7 @@
         <v>176.63809520000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" s="4">
         <v>42020</v>
       </c>
@@ -15777,7 +15777,7 @@
         <v>166.78095239999999</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" s="4">
         <v>42027</v>
       </c>
@@ -15785,7 +15785,7 @@
         <v>165.06666670000001</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A6" s="4">
         <v>42034</v>
       </c>
@@ -15793,7 +15793,7 @@
         <v>165.06666670000001</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A7" s="4">
         <v>42041</v>
       </c>
@@ -15801,7 +15801,7 @@
         <v>172.9238095</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A8" s="4">
         <v>42048</v>
       </c>
@@ -15809,7 +15809,7 @@
         <v>179.35238100000001</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A9" s="4">
         <v>42055</v>
       </c>
@@ -15817,7 +15817,7 @@
         <v>184.49523809999999</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A10" s="4">
         <v>42062</v>
       </c>
@@ -15825,7 +15825,7 @@
         <v>185.06666670000001</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A11" s="4">
         <v>42069</v>
       </c>
@@ -15833,7 +15833,7 @@
         <v>186.78095239999999</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A12" s="4">
         <v>42076</v>
       </c>
@@ -15841,7 +15841,7 @@
         <v>187.06666670000001</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A13" s="4">
         <v>42083</v>
       </c>
@@ -15849,7 +15849,7 @@
         <v>187.35238100000001</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A14" s="4">
         <v>42090</v>
       </c>
@@ -15857,7 +15857,7 @@
         <v>185.35238100000001</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A15" s="4">
         <v>42097</v>
       </c>
@@ -15865,7 +15865,7 @@
         <v>184.12893769999999</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A16" s="4">
         <v>42104</v>
       </c>
@@ -15873,7 +15873,7 @@
         <v>183.7538462</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A17" s="4">
         <v>42111</v>
       </c>
@@ -15881,7 +15881,7 @@
         <v>185.0395604</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A18" s="4">
         <v>42118</v>
       </c>
@@ -15889,7 +15889,7 @@
         <v>190.7538462</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A19" s="4">
         <v>42125</v>
       </c>
@@ -15897,7 +15897,7 @@
         <v>193.32527469999999</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A20" s="4">
         <v>42132</v>
       </c>
@@ -15905,7 +15905,7 @@
         <v>198.7538462</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A21" s="4">
         <v>42139</v>
       </c>
@@ -15913,7 +15913,7 @@
         <v>197.7538462</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A22" s="4">
         <v>42146</v>
       </c>
@@ -15921,7 +15921,7 @@
         <v>195.7538462</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A23" s="4">
         <v>42153</v>
       </c>
@@ -15929,7 +15929,7 @@
         <v>195.7538462</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A24" s="4">
         <v>42160</v>
       </c>
@@ -15937,7 +15937,7 @@
         <v>197.4681319</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A25" s="4">
         <v>42167</v>
       </c>
@@ -15945,7 +15945,7 @@
         <v>198.0395604</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A26" s="4">
         <v>42174</v>
       </c>
@@ -15953,7 +15953,7 @@
         <v>201.4681319</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A27" s="4">
         <v>42181</v>
       </c>
@@ -15961,7 +15961,7 @@
         <v>202.7538462</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A28" s="4">
         <v>42188</v>
       </c>
@@ -15969,7 +15969,7 @@
         <v>203.8908505</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A29" s="4">
         <v>42195</v>
       </c>
@@ -15977,7 +15977,7 @@
         <v>203.20279500000001</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A30" s="4">
         <v>42202</v>
       </c>
@@ -15985,7 +15985,7 @@
         <v>202.34565219999999</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A31" s="4">
         <v>42209</v>
       </c>
@@ -15993,7 +15993,7 @@
         <v>202.34565219999999</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A32" s="4">
         <v>42216</v>
       </c>
@@ -16001,7 +16001,7 @@
         <v>199.7742236</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A33" s="4">
         <v>42223</v>
       </c>
@@ -16009,7 +16009,7 @@
         <v>198.20279500000001</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A34" s="4">
         <v>42230</v>
       </c>
@@ -16017,7 +16017,7 @@
         <v>197.34565219999999</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A35" s="4">
         <v>42237</v>
       </c>
@@ -16025,7 +16025,7 @@
         <v>195.91708070000001</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A36" s="4">
         <v>42244</v>
       </c>
@@ -16033,7 +16033,7 @@
         <v>190.34565219999999</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A37" s="4">
         <v>42251</v>
       </c>
@@ -16041,7 +16041,7 @@
         <v>193.20279500000001</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A38" s="4">
         <v>42258</v>
       </c>
@@ -16049,7 +16049,7 @@
         <v>195.4885093</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A39" s="4">
         <v>42265</v>
       </c>
@@ -16057,7 +16057,7 @@
         <v>196.34565219999999</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A40" s="4">
         <v>42272</v>
       </c>
@@ -16065,7 +16065,7 @@
         <v>196.34565219999999</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A41" s="4">
         <v>42279</v>
       </c>
@@ -16073,7 +16073,7 @@
         <v>194.47111799999999</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A42" s="4">
         <v>42286</v>
       </c>
@@ -16081,7 +16081,7 @@
         <v>193.06521739999999</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A43" s="4">
         <v>42293</v>
       </c>
@@ -16089,7 +16089,7 @@
         <v>190.20807450000001</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A44" s="4">
         <v>42300</v>
       </c>
@@ -16097,7 +16097,7 @@
         <v>186.20807450000001</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A45" s="4">
         <v>42307</v>
       </c>
@@ -16105,7 +16105,7 @@
         <v>185.06521739999999</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A46" s="4">
         <v>42314</v>
       </c>
@@ -16113,7 +16113,7 @@
         <v>185.06521739999999</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A47" s="4">
         <v>42321</v>
       </c>
@@ -16121,7 +16121,7 @@
         <v>185.06521739999999</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A48" s="4">
         <v>42328</v>
       </c>
@@ -16129,7 +16129,7 @@
         <v>183.35093169999999</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A49" s="4">
         <v>42335</v>
       </c>
@@ -16137,7 +16137,7 @@
         <v>183.06521739999999</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A50" s="4">
         <v>42342</v>
       </c>
@@ -16145,7 +16145,7 @@
         <v>183.06521739999999</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A51" s="4">
         <v>42349</v>
       </c>
@@ -16153,7 +16153,7 @@
         <v>177.92236020000001</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A52" s="4">
         <v>42356</v>
       </c>
@@ -16161,7 +16161,7 @@
         <v>175.7795031</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A53" s="4">
         <v>42363</v>
       </c>
@@ -16169,7 +16169,7 @@
         <v>174.06521739999999</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A54" s="4">
         <v>42370</v>
       </c>
@@ -16177,7 +16177,7 @@
         <v>173.48624670000001</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A55" s="4">
         <v>42377</v>
       </c>
@@ -16185,7 +16185,7 @@
         <v>172.7142857</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A56" s="4">
         <v>42384</v>
       </c>
@@ -16193,7 +16193,7 @@
         <v>171.2857143</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A57" s="4">
         <v>42391</v>
       </c>
@@ -16201,7 +16201,7 @@
         <v>168.57142859999999</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A58" s="4">
         <v>42398</v>
       </c>
@@ -16209,7 +16209,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A59" s="4">
         <v>42405</v>
       </c>
@@ -16217,7 +16217,7 @@
         <v>170.7142857</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A60" s="4">
         <v>42412</v>
       </c>
@@ -16225,7 +16225,7 @@
         <v>165.14285709999999</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A61" s="4">
         <v>42419</v>
       </c>
@@ -16233,7 +16233,7 @@
         <v>161.7142857</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A62" s="4">
         <v>42426</v>
       </c>
@@ -16241,7 +16241,7 @@
         <v>161.7142857</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A63" s="4">
         <v>42433</v>
       </c>
@@ -16249,7 +16249,7 @@
         <v>164.7142857</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A64" s="4">
         <v>42440</v>
       </c>
@@ -16257,7 +16257,7 @@
         <v>168.14285709999999</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A65" s="4">
         <v>42447</v>
       </c>
@@ -16265,7 +16265,7 @@
         <v>174.7142857</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A66" s="4">
         <v>42454</v>
       </c>
@@ -16273,7 +16273,7 @@
         <v>174.7142857</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A67" s="4">
         <v>42461</v>
       </c>
@@ -16281,7 +16281,7 @@
         <v>174.0036107</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A68" s="4">
         <v>42468</v>
       </c>
@@ -16289,7 +16289,7 @@
         <v>171.34175819999999</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A69" s="4">
         <v>42475</v>
       </c>
@@ -16297,7 +16297,7 @@
         <v>174.91318680000001</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A70" s="4">
         <v>42482</v>
       </c>
@@ -16305,7 +16305,7 @@
         <v>174.62747250000001</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A71" s="4">
         <v>42489</v>
       </c>
@@ -16313,7 +16313,7 @@
         <v>175.4846154</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A72" s="4">
         <v>42496</v>
       </c>
@@ -16321,7 +16321,7 @@
         <v>176.05604400000001</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A73" s="4">
         <v>42503</v>
       </c>
@@ -16329,7 +16329,7 @@
         <v>177.77032969999999</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A74" s="4">
         <v>42510</v>
       </c>
@@ -16337,7 +16337,7 @@
         <v>180.34175819999999</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A75" s="4">
         <v>42517</v>
       </c>
@@ -16345,7 +16345,7 @@
         <v>183.34175819999999</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A76" s="4">
         <v>42524</v>
       </c>
@@ -16353,7 +16353,7 @@
         <v>185.05604400000001</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A77" s="4">
         <v>42531</v>
       </c>
@@ -16361,7 +16361,7 @@
         <v>182.91318680000001</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A78" s="4">
         <v>42538</v>
       </c>
@@ -16369,7 +16369,7 @@
         <v>180.77032969999999</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A79" s="4">
         <v>42545</v>
       </c>
@@ -16377,7 +16377,7 @@
         <v>177.34175819999999</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A80" s="4">
         <v>42552</v>
       </c>
@@ -16385,7 +16385,7 @@
         <v>178.8981742</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A81" s="4">
         <v>42559</v>
       </c>
@@ -16393,7 +16393,7 @@
         <v>179.64006209999999</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A82" s="4">
         <v>42566</v>
       </c>
@@ -16401,7 +16401,7 @@
         <v>173.3543478</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A83" s="4">
         <v>42573</v>
       </c>
@@ -16409,7 +16409,7 @@
         <v>173.3543478</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A84" s="4">
         <v>42580</v>
       </c>
@@ -16417,7 +16417,7 @@
         <v>169.0686335</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A85" s="4">
         <v>42587</v>
       </c>
@@ -16425,7 +16425,7 @@
         <v>167.3543478</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A86" s="4">
         <v>42594</v>
       </c>
@@ -16433,7 +16433,7 @@
         <v>168.7829193</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A87" s="4">
         <v>42601</v>
       </c>
@@ -16441,7 +16441,7 @@
         <v>174.49720500000001</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A88" s="4">
         <v>42608</v>
       </c>
@@ -16449,7 +16449,7 @@
         <v>177.92577639999999</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A89" s="4">
         <v>42615</v>
       </c>
@@ -16457,7 +16457,7 @@
         <v>179.7829193</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A90" s="4">
         <v>42622</v>
       </c>
@@ -16465,7 +16465,7 @@
         <v>178.3543478</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A91" s="4">
         <v>42629</v>
       </c>
@@ -16473,7 +16473,7 @@
         <v>178.3543478</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A92" s="4">
         <v>42636</v>
       </c>
@@ -16481,7 +16481,7 @@
         <v>178.3543478</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A93" s="4">
         <v>42643</v>
       </c>
@@ -16489,7 +16489,7 @@
         <v>177.1593168</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A94" s="4">
         <v>42650</v>
       </c>
@@ -16497,7 +16497,7 @@
         <v>177.02888200000001</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A95" s="4">
         <v>42657</v>
       </c>
@@ -16505,7 +16505,7 @@
         <v>180.8860248</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A96" s="4">
         <v>42664</v>
       </c>
@@ -16513,7 +16513,7 @@
         <v>184.8860248</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A97" s="4">
         <v>42671</v>
       </c>
@@ -16521,7 +16521,7 @@
         <v>185.1717391</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A98" s="4">
         <v>42678</v>
       </c>
@@ -16529,7 +16529,7 @@
         <v>184.02888200000001</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A99" s="4">
         <v>42685</v>
       </c>
@@ -16537,7 +16537,7 @@
         <v>178.02888200000001</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A100" s="4">
         <v>42692</v>
       </c>
@@ -16545,7 +16545,7 @@
         <v>175.1717391</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A101" s="4">
         <v>42699</v>
       </c>
@@ -16553,7 +16553,7 @@
         <v>177.74316769999999</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A102" s="4">
         <v>42706</v>
       </c>
@@ -16561,7 +16561,7 @@
         <v>180.6003106</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A103" s="4">
         <v>42713</v>
       </c>
@@ -16569,7 +16569,7 @@
         <v>184.31459630000001</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A104" s="4">
         <v>42720</v>
       </c>
@@ -16577,7 +16577,7 @@
         <v>187.31459630000001</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A105" s="4">
         <v>42727</v>
       </c>
@@ -16585,7 +16585,7 @@
         <v>189.31459630000001</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A106" s="4">
         <v>42734</v>
       </c>
@@ -16593,7 +16593,7 @@
         <v>189.72815729999999</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A107" s="4">
         <v>42741</v>
       </c>
@@ -16601,7 +16601,7 @@
         <v>188.49523809999999</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A108" s="4">
         <v>42748</v>
       </c>
@@ -16609,7 +16609,7 @@
         <v>189.06666670000001</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A109" s="4">
         <v>42755</v>
       </c>
@@ -16617,7 +16617,7 @@
         <v>191.63809520000001</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A110" s="4">
         <v>42762</v>
       </c>
@@ -16625,7 +16625,7 @@
         <v>192.06666670000001</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A111" s="4">
         <v>42769</v>
       </c>
@@ -16633,7 +16633,7 @@
         <v>192.06666670000001</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A112" s="4">
         <v>42776</v>
       </c>
@@ -16641,7 +16641,7 @@
         <v>190.9238095</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A113" s="4">
         <v>42783</v>
       </c>
@@ -16649,7 +16649,7 @@
         <v>190.06666670000001</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A114" s="4">
         <v>42790</v>
       </c>
@@ -16657,7 +16657,7 @@
         <v>190.06666670000001</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A115" s="4">
         <v>42797</v>
       </c>
@@ -16665,7 +16665,7 @@
         <v>190.06666670000001</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A116" s="4">
         <v>42804</v>
       </c>
@@ -16673,7 +16673,7 @@
         <v>190.06666670000001</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A117" s="4">
         <v>42811</v>
       </c>
@@ -16681,7 +16681,7 @@
         <v>188.35238100000001</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A118" s="4">
         <v>42818</v>
       </c>
@@ -16689,7 +16689,7 @@
         <v>187.06666670000001</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A119" s="4">
         <v>42825</v>
       </c>
@@ -16697,7 +16697,7 @@
         <v>187.66645740000001</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A120" s="4">
         <v>42832</v>
       </c>
@@ -16705,7 +16705,7 @@
         <v>189.16593409999999</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A121" s="4">
         <v>42839</v>
       </c>
@@ -16713,7 +16713,7 @@
         <v>191.16593409999999</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A122" s="4">
         <v>42846</v>
       </c>
@@ -16721,7 +16721,7 @@
         <v>191.16593409999999</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A123" s="4">
         <v>42853</v>
       </c>
@@ -16729,7 +16729,7 @@
         <v>191.16593409999999</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A124" s="4">
         <v>42860</v>
       </c>
@@ -16737,7 +16737,7 @@
         <v>191.16593409999999</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A125" s="4">
         <v>42867</v>
       </c>
@@ -16745,7 +16745,7 @@
         <v>187.16593409999999</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A126" s="4">
         <v>42874</v>
       </c>
@@ -16753,7 +16753,7 @@
         <v>187.16593409999999</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A127" s="4">
         <v>42881</v>
       </c>
@@ -16761,7 +16761,7 @@
         <v>187.16593409999999</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A128" s="4">
         <v>42888</v>
       </c>
@@ -16769,7 +16769,7 @@
         <v>187.16593409999999</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A129" s="4">
         <v>42895</v>
       </c>
@@ -16777,7 +16777,7 @@
         <v>187.16593409999999</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A130" s="4">
         <v>42902</v>
       </c>
@@ -16785,7 +16785,7 @@
         <v>180.45164840000001</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A131" s="4">
         <v>42909</v>
       </c>
@@ -16793,7 +16793,7 @@
         <v>172.88021979999999</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A132" s="4">
         <v>42916</v>
       </c>
@@ -16801,7 +16801,7 @@
         <v>171.8340523</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A133" s="4">
         <v>42923</v>
       </c>
@@ -16809,7 +16809,7 @@
         <v>173.50434780000001</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A134" s="4">
         <v>42930</v>
       </c>
@@ -16817,7 +16817,7 @@
         <v>173.50434780000001</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A135" s="4">
         <v>42937</v>
       </c>
@@ -16825,7 +16825,7 @@
         <v>173.50434780000001</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A136" s="4">
         <v>42944</v>
       </c>
@@ -16833,7 +16833,7 @@
         <v>175.50434780000001</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A137" s="4">
         <v>42951</v>
       </c>
@@ -16841,7 +16841,7 @@
         <v>178.93291930000001</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A138" s="4">
         <v>42958</v>
       </c>
@@ -16849,7 +16849,7 @@
         <v>182.7900621</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A139" s="4">
         <v>42965</v>
       </c>
@@ -16857,7 +16857,7 @@
         <v>184.50434780000001</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A140" s="4">
         <v>42972</v>
       </c>
@@ -16865,7 +16865,7 @@
         <v>185.64720500000001</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A141" s="4">
         <v>42979</v>
       </c>
@@ -16873,7 +16873,7 @@
         <v>188.64720500000001</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A142" s="4">
         <v>42986</v>
       </c>
@@ -16881,7 +16881,7 @@
         <v>191.64720500000001</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A143" s="4">
         <v>42993</v>
       </c>
@@ -16889,7 +16889,7 @@
         <v>192.50434780000001</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A144" s="4">
         <v>43000</v>
       </c>
@@ -16897,7 +16897,7 @@
         <v>192.50434780000001</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A145" s="4">
         <v>43007</v>
       </c>
@@ -16905,7 +16905,7 @@
         <v>192.1118012</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A146" s="4">
         <v>43014</v>
       </c>
@@ -16913,7 +16913,7 @@
         <v>189.75652170000001</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A147" s="4">
         <v>43021</v>
       </c>
@@ -16921,7 +16921,7 @@
         <v>188.3279503</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A148" s="4">
         <v>43028</v>
       </c>
@@ -16929,7 +16929,7 @@
         <v>187.75652170000001</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A149" s="4">
         <v>43035</v>
       </c>
@@ -16937,7 +16937,7 @@
         <v>187.75652170000001</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A150" s="4">
         <v>43042</v>
       </c>
@@ -16945,7 +16945,7 @@
         <v>192.61366459999999</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A151" s="4">
         <v>43049</v>
       </c>
@@ -16953,7 +16953,7 @@
         <v>196.89937889999999</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A152" s="4">
         <v>43056</v>
       </c>
@@ -16961,7 +16961,7 @@
         <v>197.75652170000001</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A153" s="4">
         <v>43063</v>
       </c>
@@ -16969,7 +16969,7 @@
         <v>197.75652170000001</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A154" s="4">
         <v>43070</v>
       </c>
@@ -16977,7 +16977,7 @@
         <v>199.75652170000001</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A155" s="4">
         <v>43077</v>
       </c>
@@ -16985,7 +16985,7 @@
         <v>199.75652170000001</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A156" s="4">
         <v>43084</v>
       </c>
@@ -16993,7 +16993,7 @@
         <v>196.89937889999999</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A157" s="4">
         <v>43091</v>
       </c>
@@ -17001,7 +17001,7 @@
         <v>195.75652170000001</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A158" s="4">
         <v>43098</v>
       </c>
@@ -17009,7 +17009,7 @@
         <v>195.75652170000001</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A159" s="4">
         <v>43105</v>
       </c>
@@ -17017,7 +17017,7 @@
         <v>201.24444439999999</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A160" s="4">
         <v>43112</v>
       </c>
@@ -17025,7 +17025,7 @@
         <v>202.10158730000001</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A161" s="4">
         <v>43119</v>
       </c>
@@ -17033,7 +17033,7 @@
         <v>203.24444439999999</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A162" s="4">
         <v>43126</v>
       </c>
@@ -17041,7 +17041,7 @@
         <v>203.24444439999999</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A163" s="4">
         <v>43133</v>
       </c>
@@ -17049,7 +17049,7 @@
         <v>203.24444439999999</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A164" s="4">
         <v>43140</v>
       </c>
@@ -17057,7 +17057,7 @@
         <v>202.3873016</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A165" s="4">
         <v>43147</v>
       </c>
@@ -17065,7 +17065,7 @@
         <v>198.95873019999999</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A166" s="4">
         <v>43154</v>
       </c>
@@ -17073,7 +17073,7 @@
         <v>197.24444439999999</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A167" s="4">
         <v>43161</v>
       </c>
@@ -17081,7 +17081,7 @@
         <v>197.24444439999999</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A168" s="4">
         <v>43168</v>
       </c>
@@ -17089,7 +17089,7 @@
         <v>197.24444439999999</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A169" s="4">
         <v>43175</v>
       </c>
@@ -17097,7 +17097,7 @@
         <v>197.24444439999999</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A170" s="4">
         <v>43182</v>
       </c>
@@ -17105,7 +17105,7 @@
         <v>197.24444439999999</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A171" s="4">
         <v>43189</v>
       </c>
@@ -17113,7 +17113,7 @@
         <v>198.54406069999999</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A172" s="4">
         <v>43196</v>
       </c>
@@ -17121,7 +17121,7 @@
         <v>194.34175819999999</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A173" s="4">
         <v>43203</v>
       </c>
@@ -17129,7 +17129,7 @@
         <v>196.05604400000001</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A174" s="4">
         <v>43210</v>
       </c>
@@ -17137,7 +17137,7 @@
         <v>197.34175819999999</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A175" s="4">
         <v>43217</v>
       </c>
@@ -17145,7 +17145,7 @@
         <v>203.34175819999999</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A176" s="4">
         <v>43224</v>
       </c>
@@ -17153,7 +17153,7 @@
         <v>203.34175819999999</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A177" s="4">
         <v>43231</v>
       </c>
@@ -17161,7 +17161,7 @@
         <v>207.05604400000001</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A178" s="4">
         <v>43238</v>
       </c>
@@ -17169,7 +17169,7 @@
         <v>213.05604400000001</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A179" s="4">
         <v>43245</v>
       </c>
@@ -17177,7 +17177,7 @@
         <v>215.34175819999999</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A180" s="4">
         <v>43252</v>
       </c>
@@ -17185,7 +17185,7 @@
         <v>215.34175819999999</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A181" s="4">
         <v>43259</v>
       </c>
@@ -17193,7 +17193,7 @@
         <v>211.05604400000001</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A182" s="4">
         <v>43266</v>
       </c>
@@ -17201,7 +17201,7 @@
         <v>209.34175819999999</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A183" s="4">
         <v>43273</v>
       </c>
@@ -17209,7 +17209,7 @@
         <v>208.1989011</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A184" s="4">
         <v>43280</v>
       </c>
@@ -17217,7 +17217,7 @@
         <v>207.72854369999999</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A185" s="4">
         <v>43287</v>
       </c>
@@ -17225,7 +17225,7 @@
         <v>210.0492562</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A186" s="4">
         <v>43294</v>
       </c>
@@ -17233,7 +17233,7 @@
         <v>210.0492562</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A187" s="4">
         <v>43301</v>
       </c>
@@ -17241,7 +17241,7 @@
         <v>210.0492562</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A188" s="4">
         <v>43308</v>
       </c>
@@ -17249,7 +17249,7 @@
         <v>211.77337900000001</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A189" s="4">
         <v>43315</v>
       </c>
@@ -17257,7 +17257,7 @@
         <v>213.06647100000001</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A190" s="4">
         <v>43322</v>
       </c>
@@ -17265,7 +17265,7 @@
         <v>214.79059380000001</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A191" s="4">
         <v>43329</v>
       </c>
@@ -17273,7 +17273,7 @@
         <v>218.0951623</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A192" s="4">
         <v>43336</v>
       </c>
@@ -17281,7 +17281,7 @@
         <v>218.0951623</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A193" s="4">
         <v>43343</v>
       </c>
@@ -17289,7 +17289,7 @@
         <v>221.1123771</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A194" s="4">
         <v>43350</v>
       </c>
@@ -17297,7 +17297,7 @@
         <v>222.83649980000001</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A195" s="4">
         <v>43357</v>
       </c>
@@ -17305,7 +17305,7 @@
         <v>226.2847453</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A196" s="4">
         <v>43364</v>
       </c>
@@ -17313,7 +17313,7 @@
         <v>227.14680659999999</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A197" s="4">
         <v>43371</v>
       </c>
@@ -17321,7 +17321,7 @@
         <v>229.1582832</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A198" s="4">
         <v>43378</v>
       </c>
@@ -17329,7 +17329,7 @@
         <v>240.4777005</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A199" s="4">
         <v>43385</v>
       </c>
@@ -17337,7 +17337,7 @@
         <v>242.7844522</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A200" s="4">
         <v>43392</v>
       </c>
@@ -17345,7 +17345,7 @@
         <v>238.89180870000001</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A201" s="4">
         <v>43399</v>
       </c>
@@ -17353,7 +17353,7 @@
         <v>234.99916529999999</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A202" s="4">
         <v>43406</v>
       </c>
@@ -17361,7 +17361,7 @@
         <v>228.79977020000001</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A203" s="4">
         <v>43413</v>
       </c>
@@ -17369,7 +17369,7 @@
         <v>218.85190360000001</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A204" s="4">
         <v>43420</v>
       </c>
@@ -17377,7 +17377,7 @@
         <v>210.4899288</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A205" s="4">
         <v>43427</v>
       </c>
@@ -17385,7 +17385,7 @@
         <v>207.60648929999999</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A206" s="4">
         <v>43434</v>
       </c>
@@ -17393,7 +17393,7 @@
         <v>202.99298590000001</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A207" s="4">
         <v>43441</v>
       </c>
@@ -17401,7 +17401,7 @@
         <v>200.3978903</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A208" s="4">
         <v>43448</v>
       </c>
@@ -17409,7 +17409,7 @@
         <v>198.66782649999999</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A209" s="4">
         <v>43455</v>
       </c>
@@ -17417,7 +17417,7 @@
         <v>197.3702787</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A210" s="4">
         <v>43462</v>
       </c>
@@ -17425,7 +17425,7 @@
         <v>196.5052469</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A211" s="4">
         <v>43469</v>
       </c>
@@ -17433,7 +17433,7 @@
         <v>193.15929890000001</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A212" s="4">
         <v>43476</v>
       </c>
@@ -17441,7 +17441,7 @@
         <v>192.79387019999999</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A213" s="4">
         <v>43483</v>
       </c>
@@ -17449,7 +17449,7 @@
         <v>194.8113414</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A214" s="4">
         <v>43490</v>
       </c>
@@ -17457,7 +17457,7 @@
         <v>196.8288125</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A215" s="4">
         <v>43497</v>
       </c>
@@ -17465,7 +17465,7 @@
         <v>196.8288125</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A216" s="4">
         <v>43504</v>
       </c>
@@ -17473,7 +17473,7 @@
         <v>196.8288125</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A217" s="4">
         <v>43511</v>
       </c>
@@ -17481,7 +17481,7 @@
         <v>198.99038870000001</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A218" s="4">
         <v>43518</v>
       </c>
@@ -17489,7 +17489,7 @@
         <v>204.3222768</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A219" s="4">
         <v>43525</v>
       </c>
@@ -17497,7 +17497,7 @@
         <v>206.6279581</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A220" s="4">
         <v>43532</v>
       </c>
@@ -17505,7 +17505,7 @@
         <v>206.91616830000001</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A221" s="4">
         <v>43539</v>
       </c>
@@ -17513,7 +17513,7 @@
         <v>209.07774449999999</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A222" s="4">
         <v>43546</v>
       </c>
@@ -17521,7 +17521,7 @@
         <v>206.91616830000001</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A223" s="4">
         <v>43553</v>
       </c>
@@ -17529,7 +17529,7 @@
         <v>210.66290040000001</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A224" s="4">
         <v>43560</v>
       </c>
@@ -17537,7 +17537,7 @@
         <v>209.4661466</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A225" s="4">
         <v>43567</v>
       </c>
@@ -17545,7 +17545,7 @@
         <v>215.47852219999999</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A226" s="4">
         <v>43574</v>
       </c>
@@ -17553,7 +17553,7 @@
         <v>217.053192</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A227" s="4">
         <v>43581</v>
       </c>
@@ -17561,7 +17561,7 @@
         <v>220.48883520000001</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A228" s="4">
         <v>43588</v>
       </c>
@@ -17569,7 +17569,7 @@
         <v>214.4764596</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A229" s="4">
         <v>43595</v>
       </c>
@@ -17577,7 +17577,7 @@
         <v>211.6134236</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A230" s="4">
         <v>43602</v>
       </c>
@@ -17585,7 +17585,7 @@
         <v>214.4764596</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A231" s="4">
         <v>43609</v>
       </c>
@@ -17593,7 +17593,7 @@
         <v>220.34568340000001</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A232" s="4">
         <v>43616</v>
       </c>
@@ -17601,7 +17601,7 @@
         <v>217.19634379999999</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A233" s="4">
         <v>43623</v>
       </c>
@@ -17609,7 +17609,7 @@
         <v>208.60723580000001</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A234" s="4">
         <v>43630</v>
       </c>
@@ -17617,7 +17617,7 @@
         <v>207.032566</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A235" s="4">
         <v>43637</v>
       </c>
@@ -17625,7 +17625,7 @@
         <v>207.032566</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A236" s="4">
         <v>43644</v>
       </c>
@@ -17633,7 +17633,7 @@
         <v>207.032566</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A237" s="4">
         <v>43651</v>
       </c>
@@ -17641,7 +17641,7 @@
         <v>205.2073896</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A238" s="4">
         <v>43658</v>
       </c>
@@ -17649,7 +17649,7 @@
         <v>207.35539019999999</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A239" s="4">
         <v>43665</v>
       </c>
@@ -17657,7 +17657,7 @@
         <v>209.93299089999999</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A240" s="4">
         <v>43672</v>
       </c>
@@ -17665,7 +17665,7 @@
         <v>210.219391</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A241" s="4">
         <v>43679</v>
       </c>
@@ -17673,7 +17673,7 @@
         <v>210.219391</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A242" s="4">
         <v>43686</v>
       </c>
@@ -17681,7 +17681,7 @@
         <v>210.219391</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A243" s="4">
         <v>43693</v>
       </c>
@@ -17689,7 +17689,7 @@
         <v>210.219391</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A244" s="4">
         <v>43700</v>
       </c>
@@ -17697,7 +17697,7 @@
         <v>210.219391</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A245" s="4">
         <v>43707</v>
       </c>
@@ -17705,7 +17705,7 @@
         <v>211.50819139999999</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A246" s="4">
         <v>43714</v>
       </c>
@@ -17713,7 +17713,7 @@
         <v>213.22659189999999</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A247" s="4">
         <v>43721</v>
       </c>
@@ -17721,7 +17721,7 @@
         <v>213.22659189999999</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A248" s="4">
         <v>43728</v>
       </c>
@@ -17729,7 +17729,7 @@
         <v>217.09299300000001</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A249" s="4">
         <v>43735</v>
       </c>
@@ -17737,7 +17737,7 @@
         <v>216.23379270000001</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A250" s="4">
         <v>43742</v>
       </c>
@@ -17745,7 +17745,7 @@
         <v>211.80014650000001</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A251" s="4">
         <v>43749</v>
       </c>
@@ -17753,7 +17753,7 @@
         <v>211.0612055</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A252" s="4">
         <v>43756</v>
       </c>
@@ -17761,7 +17761,7 @@
         <v>211.0612055</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A253" s="4">
         <v>43763</v>
       </c>
@@ -17769,7 +17769,7 @@
         <v>211.0612055</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A254" s="4">
         <v>43770</v>
       </c>
@@ -17777,7 +17777,7 @@
         <v>211.0612055</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A255" s="4">
         <v>43777</v>
       </c>
@@ -17785,7 +17785,7 @@
         <v>212.3582854</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A256" s="4">
         <v>43784</v>
       </c>
@@ -17793,7 +17793,7 @@
         <v>215.24068510000001</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A257" s="4">
         <v>43791</v>
       </c>
@@ -17801,7 +17801,7 @@
         <v>216.10540499999999</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A258" s="4">
         <v>43798</v>
       </c>
@@ -17809,7 +17809,7 @@
         <v>216.10540499999999</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A259" s="4">
         <v>43805</v>
       </c>
@@ -17817,7 +17817,7 @@
         <v>216.10540499999999</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A260" s="4">
         <v>43812</v>
       </c>
@@ -17825,7 +17825,7 @@
         <v>216.10540499999999</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A261" s="4">
         <v>43819</v>
       </c>
@@ -17833,7 +17833,7 @@
         <v>216.10540499999999</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A262" s="4">
         <v>43826</v>
       </c>
@@ -17841,7 +17841,7 @@
         <v>216.9701249</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A263" s="4">
         <v>43833</v>
       </c>
@@ -17849,7 +17849,7 @@
         <v>223.05377910000001</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A264" s="4">
         <v>43840</v>
       </c>
@@ -17857,7 +17857,7 @@
         <v>224.38956049999999</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A265" s="4">
         <v>43847</v>
       </c>
@@ -17865,7 +17865,7 @@
         <v>222.94297800000001</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A266" s="4">
         <v>43854</v>
       </c>
@@ -17873,7 +17873,7 @@
         <v>221.3517372</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A267" s="4">
         <v>43861</v>
       </c>
@@ -17881,7 +17881,7 @@
         <v>216.4333566</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A268" s="4">
         <v>43868</v>
       </c>
@@ -17889,7 +17889,7 @@
         <v>214.69745760000001</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A269" s="4">
         <v>43875</v>
       </c>
@@ -17897,7 +17897,7 @@
         <v>214.69745760000001</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A270" s="4">
         <v>43882</v>
       </c>
@@ -17905,7 +17905,7 @@
         <v>214.11882460000001</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A271" s="4">
         <v>43889</v>
       </c>
@@ -17913,7 +17913,7 @@
         <v>213.2508751</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A272" s="4">
         <v>43896</v>
       </c>
@@ -17921,7 +17921,7 @@
         <v>211.37031780000001</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A273" s="4">
         <v>43903</v>
       </c>
@@ -17929,7 +17929,7 @@
         <v>191.98611210000001</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A274" s="4">
         <v>43910</v>
       </c>
@@ -17937,7 +17937,7 @@
         <v>179.25618600000001</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A275" s="4">
         <v>43917</v>
       </c>
@@ -17945,7 +17945,7 @@
         <v>179.25618600000001</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A276" s="4">
         <v>43924</v>
       </c>
@@ -17953,7 +17953,7 @@
         <v>180.02010290000001</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A277" s="4">
         <v>43931</v>
       </c>
@@ -17961,7 +17961,7 @@
         <v>180.3256696</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A278" s="4">
         <v>43938</v>
       </c>
@@ -17969,7 +17969,7 @@
         <v>180.3256696</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A279" s="4">
         <v>43945</v>
       </c>
@@ -17977,7 +17977,7 @@
         <v>180.3256696</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A280" s="4">
         <v>43952</v>
       </c>
@@ -17985,7 +17985,7 @@
         <v>181.48454609999999</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A281" s="4">
         <v>43959</v>
       </c>
@@ -17993,7 +17993,7 @@
         <v>182.35370349999999</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A282" s="4">
         <v>43966</v>
       </c>
@@ -18001,7 +18001,7 @@
         <v>184.09201820000001</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A283" s="4">
         <v>43973</v>
       </c>
@@ -18009,7 +18009,7 @@
         <v>183.51258000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A284" s="4">
         <v>43980</v>
       </c>
@@ -18017,7 +18017,7 @@
         <v>183.2228609</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A285" s="4">
         <v>43987</v>
       </c>
@@ -18025,7 +18025,7 @@
         <v>185.39575429999999</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A286" s="4">
         <v>43994</v>
       </c>
@@ -18033,7 +18033,7 @@
         <v>185.39575429999999</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A287" s="4">
         <v>44001</v>
       </c>
@@ -18041,7 +18041,7 @@
         <v>185.39575429999999</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A288" s="4">
         <v>44008</v>
       </c>
@@ -18049,7 +18049,7 @@
         <v>185.39575429999999</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A289" s="4">
         <v>44015</v>
       </c>
@@ -18057,7 +18057,7 @@
         <v>185.95540750000001</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A290" s="4">
         <v>44022</v>
       </c>
@@ -18065,7 +18065,7 @@
         <v>184.43864529999999</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A291" s="4">
         <v>44029</v>
       </c>
@@ -18073,7 +18073,7 @@
         <v>185.0188531</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A292" s="4">
         <v>44036</v>
       </c>
@@ -18081,7 +18081,7 @@
         <v>186.46937270000001</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A293" s="4">
         <v>44043</v>
       </c>
@@ -18089,7 +18089,7 @@
         <v>188.20999620000001</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A294" s="4">
         <v>44050</v>
       </c>
@@ -18097,7 +18097,7 @@
         <v>185.8891648</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A295" s="4">
         <v>44057</v>
       </c>
@@ -18105,7 +18105,7 @@
         <v>185.0188531</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A296" s="4">
         <v>44064</v>
       </c>
@@ -18113,7 +18113,7 @@
         <v>186.17926879999999</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A297" s="4">
         <v>44071</v>
       </c>
@@ -18121,7 +18121,7 @@
         <v>189.08030790000001</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A298" s="4">
         <v>44078</v>
       </c>
@@ -18129,7 +18129,7 @@
         <v>189.08030790000001</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A299" s="4">
         <v>44085</v>
       </c>
@@ -18137,7 +18137,7 @@
         <v>187.33968440000001</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A300" s="4">
         <v>44092</v>
       </c>
@@ -18145,7 +18145,7 @@
         <v>184.43864529999999</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A301" s="4">
         <v>44099</v>
       </c>
@@ -18153,7 +18153,7 @@
         <v>185.8891648</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A302" s="4">
         <v>44106</v>
       </c>
@@ -18161,7 +18161,7 @@
         <v>188.3545349</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A303" s="4">
         <v>44113</v>
       </c>
@@ -18169,7 +18169,7 @@
         <v>185.3495345</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A304" s="4">
         <v>44120</v>
       </c>
@@ -18177,7 +18177,7 @@
         <v>186.6535361</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A305" s="4">
         <v>44127</v>
       </c>
@@ -18185,7 +18185,7 @@
         <v>186.9433142</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A306" s="4">
         <v>44134</v>
       </c>
@@ -18193,7 +18193,7 @@
         <v>186.3637579</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A307" s="4">
         <v>44141</v>
       </c>
@@ -18201,7 +18201,7 @@
         <v>185.92909069999999</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A308" s="4">
         <v>44148</v>
       </c>
@@ -18209,7 +18209,7 @@
         <v>187.23309230000001</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A309" s="4">
         <v>44155</v>
       </c>
@@ -18217,7 +18217,7 @@
         <v>185.92909069999999</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A310" s="4">
         <v>44162</v>
       </c>
@@ -18225,7 +18225,7 @@
         <v>185.63931260000001</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A311" s="4">
         <v>44169</v>
       </c>
@@ -18233,7 +18233,7 @@
         <v>187.95753759999999</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A312" s="4">
         <v>44176</v>
       </c>
@@ -18241,7 +18241,7 @@
         <v>189.69620639999999</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A313" s="4">
         <v>44183</v>
       </c>
@@ -18249,7 +18249,7 @@
         <v>188.2473157</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A314" s="4">
         <v>44190</v>
       </c>
@@ -18257,7 +18257,7 @@
         <v>184.9148673</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A315" s="4">
         <v>44197</v>
       </c>
@@ -18265,7 +18265,7 @@
         <v>186.3872006</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A316" s="4">
         <v>44204</v>
       </c>
@@ -18273,7 +18273,7 @@
         <v>192.39724279999999</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A317" s="4">
         <v>44211</v>
       </c>
@@ -18281,7 +18281,7 @@
         <v>197.1668402</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A318" s="4">
         <v>44218</v>
       </c>
@@ -18289,7 +18289,7 @@
         <v>199.47937229999999</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A319" s="4">
         <v>44225</v>
       </c>
@@ -18297,7 +18297,7 @@
         <v>195.57697440000001</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A320" s="4">
         <v>44232</v>
       </c>
@@ -18305,7 +18305,7 @@
         <v>195.28790789999999</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A321" s="4">
         <v>44239</v>
       </c>
@@ -18313,7 +18313,7 @@
         <v>200.0575053</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A322" s="4">
         <v>44246</v>
       </c>
@@ -18321,7 +18321,7 @@
         <v>201.5028379</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A323" s="4">
         <v>44253</v>
       </c>
@@ -18329,7 +18329,7 @@
         <v>202.94817040000001</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A324" s="4">
         <v>44260</v>
       </c>
@@ -18337,7 +18337,7 @@
         <v>205.6943023</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A325" s="4">
         <v>44267</v>
       </c>
@@ -18345,7 +18345,7 @@
         <v>207.13963480000001</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A326" s="4">
         <v>44274</v>
       </c>
@@ -18353,7 +18353,7 @@
         <v>206.5615018</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A327" s="4">
         <v>44281</v>
       </c>
@@ -18361,7 +18361,7 @@
         <v>203.52630350000001</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A328" s="4">
         <v>44288</v>
       </c>
@@ -18369,7 +18369,7 @@
         <v>204.58969339999999</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A329" s="4">
         <v>44295</v>
       </c>
@@ -18377,7 +18377,7 @@
         <v>205.38723580000001</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A330" s="4">
         <v>44302</v>
       </c>
@@ -18385,7 +18385,7 @@
         <v>205.96514070000001</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A331" s="4">
         <v>44309</v>
       </c>
@@ -18393,7 +18393,7 @@
         <v>208.9991417</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A332" s="4">
         <v>44316</v>
       </c>
@@ -18401,7 +18401,7 @@
         <v>209.4325704</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A333" s="4">
         <v>44323</v>
       </c>
@@ -18409,7 +18409,7 @@
         <v>210.58838019999999</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A334" s="4">
         <v>44330</v>
       </c>
@@ -18417,7 +18417,7 @@
         <v>211.4552376</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A335" s="4">
         <v>44337</v>
       </c>
@@ -18425,7 +18425,7 @@
         <v>211.4552376</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A336" s="4">
         <v>44344</v>
       </c>
@@ -18433,7 +18433,7 @@
         <v>213.1889525</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A337" s="4">
         <v>44351</v>
       </c>
@@ -18441,7 +18441,7 @@
         <v>215.50057219999999</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A338" s="4">
         <v>44358</v>
       </c>
@@ -18449,7 +18449,7 @@
         <v>217.6677158</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A339" s="4">
         <v>44365</v>
       </c>
@@ -18457,7 +18457,7 @@
         <v>220.70171669999999</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A340" s="4">
         <v>44372</v>
       </c>
@@ -18465,7 +18465,7 @@
         <v>223.73571759999999</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A341" s="4">
         <v>44379</v>
       </c>
@@ -18473,7 +18473,7 @@
         <v>223.5137599</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A342" s="4">
         <v>44386</v>
       </c>
@@ -18481,7 +18481,7 @@
         <v>224.57014570000001</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A343" s="4">
         <v>44393</v>
       </c>
@@ -18489,7 +18489,7 @@
         <v>224.85829910000001</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A344" s="4">
         <v>44400</v>
       </c>
@@ -18497,7 +18497,7 @@
         <v>223.12937869999999</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A345" s="4">
         <v>44407</v>
       </c>
@@ -18505,7 +18505,7 @@
         <v>224.71422240000001</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A346" s="4">
         <v>44414</v>
       </c>
@@ -18513,7 +18513,7 @@
         <v>228.3161399</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A347" s="4">
         <v>44421</v>
       </c>
@@ -18521,7 +18521,7 @@
         <v>227.307603</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A348" s="4">
         <v>44428</v>
       </c>
@@ -18529,7 +18529,7 @@
         <v>226.7312962</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A349" s="4">
         <v>44435</v>
       </c>
@@ -18537,7 +18537,7 @@
         <v>228.0279865</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A350" s="4">
         <v>44442</v>
       </c>
@@ -18545,7 +18545,7 @@
         <v>229.75690689999999</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A351" s="4">
         <v>44449</v>
       </c>
@@ -18553,7 +18553,7 @@
         <v>229.18060009999999</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A352" s="4">
         <v>44456</v>
       </c>
@@ -18561,7 +18561,7 @@
         <v>230.04506029999999</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A353" s="4">
         <v>44463</v>
       </c>
@@ -18569,7 +18569,7 @@
         <v>231.62990400000001</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A354" s="4">
         <v>44470</v>
       </c>
@@ -18577,7 +18577,7 @@
         <v>231.485491</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A355" s="4">
         <v>44477</v>
       </c>
@@ -18585,7 +18585,7 @@
         <v>234.73517810000001</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A356" s="4">
         <v>44484</v>
       </c>
@@ -18593,7 +18593,7 @@
         <v>239.47579289999999</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A357" s="4">
         <v>44491</v>
       </c>
@@ -18601,7 +18601,7 @@
         <v>244.36006280000001</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A358" s="4">
         <v>44498</v>
       </c>
@@ -18609,7 +18609,7 @@
         <v>249.3879876</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A359" s="4">
         <v>44505</v>
       </c>
@@ -18617,7 +18617,7 @@
         <v>251.5428125</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A360" s="4">
         <v>44512</v>
       </c>
@@ -18625,7 +18625,7 @@
         <v>251.5428125</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A361" s="4">
         <v>44519</v>
       </c>
@@ -18633,7 +18633,7 @@
         <v>251.5428125</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A362" s="4">
         <v>44526</v>
       </c>
@@ -18641,7 +18641,7 @@
         <v>248.5260576</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A363" s="4">
         <v>44533</v>
       </c>
@@ -18649,7 +18649,7 @@
         <v>248.5260576</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A364" s="4">
         <v>44540</v>
       </c>
@@ -18657,7 +18657,7 @@
         <v>246.37123270000001</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A365" s="4">
         <v>44547</v>
       </c>
@@ -18665,7 +18665,7 @@
         <v>243.49813280000001</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A366" s="4">
         <v>44554</v>
       </c>
@@ -18673,7 +18673,7 @@
         <v>243.49813280000001</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A367" s="4">
         <v>44561</v>
       </c>
@@ -18681,7 +18681,7 @@
         <v>244.76314500000001</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A368" s="4">
         <v>44568</v>
       </c>
@@ -18689,7 +18689,7 @@
         <v>248.1949272</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A369" s="4">
         <v>44575</v>
       </c>
@@ -18697,7 +18697,7 @@
         <v>250.11103080000001</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A370" s="4">
         <v>44582</v>
       </c>
@@ -18705,7 +18705,7 @@
         <v>253.68428639999999</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A371" s="4">
         <v>44589</v>
       </c>
@@ -18713,7 +18713,7 @@
         <v>257.0946131</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A372" s="4">
         <v>44596</v>
       </c>
@@ -18721,7 +18721,7 @@
         <v>261.09927379999999</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A373" s="4">
         <v>44603</v>
       </c>
@@ -18729,7 +18729,7 @@
         <v>265.04422219999998</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A374" s="4">
         <v>44610</v>
       </c>
@@ -18737,7 +18737,7 @@
         <v>269.28846540000001</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A375" s="4">
         <v>44617</v>
       </c>
@@ -18745,7 +18745,7 @@
         <v>272.79145390000002</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A376" s="4">
         <v>44624</v>
       </c>
@@ -18753,7 +18753,7 @@
         <v>279.91749609999999</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A377" s="4">
         <v>44631</v>
       </c>
@@ -18761,7 +18761,7 @@
         <v>298.78123049999999</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A378" s="4">
         <v>44638</v>
       </c>
@@ -18769,7 +18769,7 @@
         <v>279.83095630000003</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A379" s="4">
         <v>44645</v>
       </c>
@@ -18777,7 +18777,7 @@
         <v>269.5906956</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A380" s="4">
         <v>44652</v>
       </c>
@@ -18785,7 +18785,7 @@
         <v>268.18248569999997</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A381" s="4">
         <v>44659</v>
       </c>
@@ -18793,7 +18793,7 @@
         <v>263.00874069999998</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A382" s="4">
         <v>44666</v>
       </c>
@@ -18801,7 +18801,7 @@
         <v>260.72666609999999</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A383" s="4">
         <v>44673</v>
       </c>
@@ -18809,7 +18809,7 @@
         <v>262.00509929999998</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A384" s="4">
         <v>44680</v>
       </c>
@@ -18817,7 +18817,7 @@
         <v>265.5409568</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A385" s="4">
         <v>44687</v>
       </c>
@@ -18825,7 +18825,7 @@
         <v>273.5595075</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A386" s="4">
         <v>44694</v>
       </c>
@@ -18833,7 +18833,7 @@
         <v>284.20828799999998</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A387" s="4">
         <v>44701</v>
       </c>
@@ -18841,7 +18841,7 @@
         <v>291.4605439</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A388" s="4">
         <v>44708</v>
       </c>
@@ -18849,7 +18849,7 @@
         <v>294.8444437</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A389" s="4">
         <v>44715</v>
       </c>
@@ -18857,7 +18857,7 @@
         <v>294.18145060000001</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A390" s="4">
         <v>44722</v>
       </c>
@@ -18865,7 +18865,7 @@
         <v>295.73487390000003</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A391" s="4">
         <v>44729</v>
       </c>
@@ -18873,7 +18873,7 @@
         <v>303.65522659999999</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A392" s="4">
         <v>44736</v>
       </c>
@@ -18881,7 +18881,7 @@
         <v>308.50244500000002</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A393" s="4">
         <v>44743</v>
       </c>
@@ -18889,7 +18889,7 @@
         <v>308.9297353</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A394" s="4">
         <v>44750</v>
       </c>
@@ -18897,7 +18897,7 @@
         <v>307.98289149999999</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A395" s="4">
         <v>44757</v>
       </c>
@@ -18905,7 +18905,7 @@
         <v>303.49418120000001</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A396" s="4">
         <v>44764</v>
       </c>
@@ -18913,7 +18913,7 @@
         <v>285.76360060000002</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A397" s="4">
         <v>44771</v>
       </c>
@@ -18921,7 +18921,7 @@
         <v>269.54442030000001</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A398" s="4">
         <v>44778</v>
       </c>
@@ -18929,7 +18929,7 @@
         <v>264.51088620000002</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A399" s="4">
         <v>44785</v>
       </c>
@@ -18937,7 +18937,7 @@
         <v>261.25137999999998</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A400" s="4">
         <v>44792</v>
       </c>
@@ -18945,7 +18945,7 @@
         <v>258.52456769999998</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A401" s="4">
         <v>44799</v>
       </c>
@@ -18953,7 +18953,7 @@
         <v>258.6883373</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A402" s="4">
         <v>44806</v>
       </c>
@@ -18961,7 +18961,7 @@
         <v>261.30671719999998</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A403" s="4">
         <v>44813</v>
       </c>
@@ -18969,7 +18969,7 @@
         <v>261.83220110000002</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A404" s="4">
         <v>44820</v>
       </c>
@@ -18977,7 +18977,7 @@
         <v>261.30040839999998</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A405" s="4">
         <v>44827</v>
       </c>
@@ -18985,7 +18985,7 @@
         <v>261.02088070000002</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A406" s="4">
         <v>44834</v>
       </c>
@@ -18993,7 +18993,7 @@
         <v>259.58808699999997</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A407" s="4">
         <v>44841</v>
       </c>
@@ -19001,7 +19001,7 @@
         <v>257.17659650000002</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A408" s="4">
         <v>44848</v>
       </c>
@@ -19009,7 +19009,7 @@
         <v>257.39425619999997</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A409" s="4">
         <v>44855</v>
       </c>
@@ -19017,7 +19017,7 @@
         <v>257.56476759999998</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A410" s="4">
         <v>44862</v>
       </c>
@@ -19025,7 +19025,7 @@
         <v>258.04264410000002</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A411" s="4">
         <v>44869</v>
       </c>
@@ -19033,7 +19033,7 @@
         <v>257.1721235</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A412" s="4">
         <v>44876</v>
       </c>
@@ -19041,7 +19041,7 @@
         <v>257.67942219999998</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A413" s="4">
         <v>44883</v>
       </c>
@@ -19049,7 +19049,7 @@
         <v>257.61125029999999</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A414" s="4">
         <v>44890</v>
       </c>
@@ -19057,7 +19057,7 @@
         <v>256.15321340000003</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A415" s="4">
         <v>44897</v>
       </c>
@@ -19065,7 +19065,7 @@
         <v>252.7027133</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A416" s="4">
         <v>44904</v>
       </c>
@@ -19073,7 +19073,7 @@
         <v>246.94869069999999</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A417" s="4">
         <v>44911</v>
       </c>
@@ -19081,7 +19081,7 @@
         <v>240.20331669999999</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A418" s="4">
         <v>44918</v>
       </c>
@@ -19089,7 +19089,7 @@
         <v>236.84588539999999</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A419" s="4">
         <v>44925</v>
       </c>
@@ -19097,7 +19097,7 @@
         <v>238.81537650000001</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A420" s="4">
         <v>44932</v>
       </c>
@@ -19105,7 +19105,7 @@
         <v>243.2337756</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A421" s="4">
         <v>44939</v>
       </c>
@@ -19113,7 +19113,7 @@
         <v>242.88477449999999</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A422" s="4">
         <v>44946</v>
       </c>
@@ -19121,7 +19121,7 @@
         <v>242.9840662</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A423" s="4">
         <v>44953</v>
       </c>
@@ -19129,7 +19129,7 @@
         <v>247.95092779999999</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A424" s="4">
         <v>44960</v>
       </c>
@@ -19137,7 +19137,7 @@
         <v>247.97214880000001</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A425" s="4">
         <v>44967</v>
       </c>
@@ -19145,7 +19145,7 @@
         <v>246.8799731</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A426" s="4">
         <v>44974</v>
       </c>
@@ -19153,7 +19153,7 @@
         <v>247.1915626</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A427" s="4">
         <v>44981</v>
       </c>
@@ -19161,7 +19161,7 @@
         <v>245.26399520000001</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A428" s="4">
         <v>44988</v>
       </c>
@@ -19169,7 +19169,7 @@
         <v>245.98254539999999</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A429" s="4">
         <v>44995</v>
       </c>
@@ -19177,7 +19177,7 @@
         <v>245.68445399999999</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A430" s="4">
         <v>45002</v>
       </c>
@@ -19185,7 +19185,7 @@
         <v>244.81362089999999</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A431" s="4">
         <v>45009</v>
       </c>
@@ -19193,7 +19193,7 @@
         <v>243.06928300000001</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A432" s="4">
         <v>45016</v>
       </c>
@@ -19201,7 +19201,7 @@
         <v>241.82912110000001</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A433" s="4">
         <v>45023</v>
       </c>
@@ -19209,7 +19209,7 @@
         <v>246.19009589999999</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A434" s="4">
         <v>45030</v>
       </c>
@@ -19217,7 +19217,7 @@
         <v>248.76394099999999</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A435" s="4">
         <v>45037</v>
       </c>
@@ -19225,7 +19225,7 @@
         <v>249.3106157</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A436" s="4">
         <v>45044</v>
       </c>
@@ -19233,7 +19233,7 @@
         <v>248.90071370000001</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A437" s="4">
         <v>45051</v>
       </c>
@@ -19241,7 +19241,7 @@
         <v>245.37753420000001</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A438" s="4">
         <v>45058</v>
       </c>
@@ -19249,7 +19249,7 @@
         <v>239.63877189999999</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A439" s="4">
         <v>45065</v>
       </c>
@@ -19257,7 +19257,7 @@
         <v>235.75663729999999</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A440" s="4">
         <v>45072</v>
       </c>
@@ -19265,7 +19265,7 @@
         <v>236.32711029999999</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A441" s="4">
         <v>45079</v>
       </c>
@@ -19273,7 +19273,7 @@
         <v>239.2969861</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A442" s="4">
         <v>45086</v>
       </c>
@@ -19281,7 +19281,7 @@
         <v>238.78242059999999</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A443" s="4">
         <v>45093</v>
       </c>
@@ -19289,7 +19289,7 @@
         <v>238.5626288</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A444" s="4">
         <v>45100</v>
       </c>
@@ -19297,7 +19297,7 @@
         <v>238.62232900000001</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A445" s="4">
         <v>45107</v>
       </c>
@@ -19305,7 +19305,7 @@
         <v>243.49078900000001</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A446" s="4">
         <v>45114</v>
       </c>
@@ -19313,7 +19313,7 @@
         <v>264.64432640000001</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A447" s="4">
         <v>45121</v>
       </c>
@@ -19321,7 +19321,7 @@
         <v>264.28787560000001</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A448" s="4">
         <v>45128</v>
       </c>
@@ -19329,7 +19329,7 @@
         <v>266.78185259999998</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A449" s="4">
         <v>45135</v>
       </c>
@@ -19337,7 +19337,7 @@
         <v>272.374798</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A450" s="4">
         <v>45142</v>
       </c>
@@ -19345,7 +19345,7 @@
         <v>277.76442739999999</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A451" s="4">
         <v>45149</v>
       </c>
@@ -19353,7 +19353,7 @@
         <v>281.27566789999997</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A452" s="4">
         <v>45156</v>
       </c>
@@ -19361,7 +19361,7 @@
         <v>286.40290950000002</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A453" s="4">
         <v>45163</v>
       </c>
@@ -19369,7 +19369,7 @@
         <v>288.64616799999999</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A454" s="4">
         <v>45170</v>
       </c>
@@ -19377,7 +19377,7 @@
         <v>290.93826280000002</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A455" s="4">
         <v>45177</v>
       </c>
@@ -19385,7 +19385,7 @@
         <v>293.43467920000001</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A456" s="4">
         <v>45184</v>
       </c>
@@ -19393,7 +19393,7 @@
         <v>296.53593660000001</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A457" s="4">
         <v>45191</v>
       </c>
@@ -19401,7 +19401,7 @@
         <v>301.00098309999998</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A458" s="4">
         <v>45198</v>
       </c>
@@ -19409,7 +19409,7 @@
         <v>301.93506430000002</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A459" s="4">
         <v>45205</v>
       </c>
@@ -19417,7 +19417,7 @@
         <v>296.72163069999999</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A460" s="4">
         <v>45212</v>
       </c>
@@ -19425,7 +19425,7 @@
         <v>292.43642139999997</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A461" s="4">
         <v>45219</v>
       </c>
@@ -19433,7 +19433,7 @@
         <v>289.36485520000002</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A462" s="4">
         <v>45226</v>
       </c>
@@ -19441,7 +19441,7 @@
         <v>287.62794070000001</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A463" s="4">
         <v>45233</v>
       </c>
@@ -19449,7 +19449,7 @@
         <v>286.79197429999999</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A464" s="4">
         <v>45240</v>
       </c>
@@ -19457,7 +19457,7 @@
         <v>285.5771848</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A465" s="4">
         <v>45247</v>
       </c>
@@ -19465,7 +19465,7 @@
         <v>282.63599570000002</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A466" s="4">
         <v>45254</v>
       </c>
@@ -19473,7 +19473,7 @@
         <v>279.73079469999999</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A467" s="4">
         <v>45261</v>
       </c>
@@ -19481,7 +19481,7 @@
         <v>276.71581229999998</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A468" s="4">
         <v>45268</v>
       </c>
@@ -19489,7 +19489,7 @@
         <v>272.97806919999999</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A469" s="4">
         <v>45275</v>
       </c>
@@ -19497,7 +19497,7 @@
         <v>268.07097060000001</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A470" s="4">
         <v>45282</v>
       </c>
@@ -19505,7 +19505,7 @@
         <v>266.05018360000003</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A471" s="4">
         <v>45289</v>
       </c>
@@ -19513,7 +19513,7 @@
         <v>265.76198449999998</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A472" s="4">
         <v>45296</v>
       </c>
@@ -19521,7 +19521,7 @@
         <v>265.7174574</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A473" s="4">
         <v>45303</v>
       </c>
@@ -19529,7 +19529,7 @@
         <v>265.3049054</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A474" s="4">
         <v>45310</v>
       </c>
@@ -19537,7 +19537,7 @@
         <v>265.05007430000001</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A475" s="4">
         <v>45317</v>
       </c>
@@ -19545,7 +19545,7 @@
         <v>266.54534100000001</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A476" s="4">
         <v>45324</v>
       </c>
@@ -19553,7 +19553,7 @@
         <v>272.1266885</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A477" s="4">
         <v>45331</v>
       </c>
@@ -19561,7 +19561,7 @@
         <v>275.58411630000001</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A478" s="4">
         <v>45338</v>
       </c>
@@ -19569,7 +19569,7 @@
         <v>277.82113989999999</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A479" s="4">
         <v>45345</v>
       </c>
@@ -19577,7 +19577,7 @@
         <v>279.24328509999998</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A480" s="4">
         <v>45352</v>
       </c>
@@ -19585,7 +19585,7 @@
         <v>279.32440580000002</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A481" s="4">
         <v>45359</v>
       </c>
@@ -19593,7 +19593,7 @@
         <v>280.16422399999999</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A482" s="4">
         <v>45366</v>
       </c>
@@ -19601,7 +19601,7 @@
         <v>279.50204439999999</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A483" s="4">
         <v>45373</v>
       </c>
@@ -19609,7 +19609,7 @@
         <v>279.84370130000002</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A484" s="4">
         <v>45380</v>
       </c>
@@ -19617,7 +19617,7 @@
         <v>282.27261659999999</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A485" s="4">
         <v>45387</v>
       </c>
@@ -19625,7 +19625,7 @@
         <v>283.56304640000002</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A486" s="4">
         <v>45394</v>
       </c>
@@ -19633,7 +19633,7 @@
         <v>284.86303859999998</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A487" s="4">
         <v>45401</v>
       </c>
@@ -19641,7 +19641,7 @@
         <v>285.19454189999999</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A488" s="4">
         <v>45408</v>
       </c>
@@ -19649,7 +19649,7 @@
         <v>284.59299549999997</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A489" s="4">
         <v>45415</v>
       </c>
@@ -19657,7 +19657,7 @@
         <v>283.61880880000001</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A490" s="4">
         <v>45422</v>
       </c>
@@ -19665,7 +19665,7 @@
         <v>281.86104419999998</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A491" s="4">
         <v>45429</v>
       </c>
@@ -19673,7 +19673,7 @@
         <v>278.70979670000003</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A492" s="4">
         <v>45436</v>
       </c>
@@ -19681,7 +19681,7 @@
         <v>275.94843550000002</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A493" s="4">
         <v>45443</v>
       </c>
@@ -19689,7 +19689,7 @@
         <v>273.23884850000002</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A494" s="4">
         <v>45450</v>
       </c>
@@ -19697,7 +19697,7 @@
         <v>268.67537090000002</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A495" s="4">
         <v>45457</v>
       </c>
@@ -19705,7 +19705,7 @@
         <v>264.30792220000001</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A496" s="4">
         <v>45464</v>
       </c>
@@ -19713,7 +19713,7 @@
         <v>263.13433659999998</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A497" s="4">
         <v>45471</v>
       </c>
@@ -19721,7 +19721,7 @@
         <v>265.49181420000002</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A498" s="4">
         <v>45478</v>
       </c>
@@ -19729,7 +19729,7 @@
         <v>262.13687579999998</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A499" s="4">
         <v>45485</v>
       </c>
@@ -19737,7 +19737,7 @@
         <v>264.27202169999998</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A500" s="4">
         <v>45492</v>
       </c>
@@ -19745,7 +19745,7 @@
         <v>264.63758100000001</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A501" s="4">
         <v>45499</v>
       </c>
@@ -19753,7 +19753,7 @@
         <v>264.28085329999999</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A502" s="4">
         <v>45506</v>
       </c>
@@ -19761,7 +19761,7 @@
         <v>263.49845119999998</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A503" s="4">
         <v>45513</v>
       </c>
@@ -19769,7 +19769,7 @@
         <v>262.51468549999998</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A504" s="4">
         <v>45520</v>
       </c>
@@ -19777,7 +19777,7 @@
         <v>260.56074799999999</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A505" s="4">
         <v>45527</v>
       </c>
@@ -19785,7 +19785,7 @@
         <v>258.82574519999997</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A506" s="4">
         <v>45534</v>
       </c>
@@ -19793,7 +19793,7 @@
         <v>256.43474670000001</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A507" s="4">
         <v>45541</v>
       </c>
@@ -19801,7 +19801,7 @@
         <v>254.4328812</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A508" s="4">
         <v>45548</v>
       </c>
@@ -19809,7 +19809,7 @@
         <v>251.69259450000001</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A509" s="4">
         <v>45555</v>
       </c>
@@ -19817,7 +19817,7 @@
         <v>249.01809610000001</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A510" s="4">
         <v>45562</v>
       </c>
@@ -19825,7 +19825,7 @@
         <v>247.26206189999999</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A511" s="4">
         <v>45569</v>
       </c>
@@ -19833,7 +19833,7 @@
         <v>246.79487750000001</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A512" s="4">
         <v>45576</v>
       </c>
@@ -19841,7 +19841,7 @@
         <v>249.43657540000001</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A513" s="4">
         <v>45583</v>
       </c>
@@ -19849,7 +19849,7 @@
         <v>252.26114899999999</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A514" s="4">
         <v>45590</v>
       </c>
@@ -19857,7 +19857,7 @@
         <v>253.18533740000001</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A515" s="4">
         <v>45597</v>
       </c>
@@ -19865,7 +19865,7 @@
         <v>252.33932129999999</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A516" s="4">
         <v>45604</v>
       </c>
@@ -19873,7 +19873,7 @@
         <v>253.76761680000001</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A517" s="4">
         <v>45611</v>
       </c>
@@ -19881,7 +19881,7 @@
         <v>255.8128596</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A518" s="4">
         <v>45618</v>
       </c>
@@ -19889,7 +19889,7 @@
         <v>255.972995</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A519" s="4">
         <v>45625</v>
       </c>
@@ -19897,7 +19897,7 @@
         <v>255.8713042</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A520" s="4">
         <v>45632</v>
       </c>
@@ -19905,7 +19905,7 @@
         <v>255.46482409999999</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A521" s="4">
         <v>45639</v>
       </c>
@@ -19913,7 +19913,7 @@
         <v>255.64667940000001</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A522" s="4">
         <v>45646</v>
       </c>
@@ -19921,7 +19921,7 @@
         <v>258.50677100000001</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A523" s="4">
         <v>45653</v>
       </c>
@@ -19929,7 +19929,7 @@
         <v>262.34053280000001</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A524" s="4">
         <v>45660</v>
       </c>
@@ -19937,7 +19937,7 @@
         <v>264.73920479999998</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A525" s="4">
         <v>45667</v>
       </c>
@@ -19945,7 +19945,7 @@
         <v>265.70118530000002</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A526" s="4">
         <v>45674</v>
       </c>
@@ -19953,7 +19953,7 @@
         <v>268.18693949999999</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A527" s="4">
         <v>45681</v>
       </c>
@@ -19961,7 +19961,7 @@
         <v>270.64791930000001</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A528" s="4">
         <v>45688</v>
       </c>
@@ -19969,7 +19969,7 @@
         <v>270.3937717</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A529" s="4">
         <v>45695</v>
       </c>
@@ -19977,7 +19977,7 @@
         <v>269.39890939999998</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A530" s="4">
         <v>45702</v>
       </c>
@@ -19985,7 +19985,7 @@
         <v>268.81659209999998</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A531" s="4">
         <v>45709</v>
       </c>
@@ -19993,7 +19993,7 @@
         <v>268.37462240000002</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A532" s="4">
         <v>45716</v>
       </c>
@@ -20001,7 +20001,7 @@
         <v>267.70196540000001</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A533" s="4">
         <v>45723</v>
       </c>
@@ -20009,7 +20009,7 @@
         <v>266.34197719999997</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A534" s="4">
         <v>45730</v>
       </c>
@@ -20017,7 +20017,7 @@
         <v>263.86124319999999</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A535" s="4">
         <v>45737</v>
       </c>
@@ -20025,7 +20025,7 @@
         <v>261.66781559999998</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A536" s="4">
         <v>45744</v>
       </c>
@@ -20033,7 +20033,7 @@
         <v>261.21330460000001</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A537" s="4">
         <v>45751</v>
       </c>
@@ -20041,7 +20041,7 @@
         <v>261.21368589999997</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A538" s="4">
         <v>45758</v>
       </c>
@@ -20049,7 +20049,7 @@
         <v>260.0092148</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A539" s="4">
         <v>45765</v>
       </c>
@@ -20057,7 +20057,7 @@
         <v>257.33806229999999</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A540" s="4">
         <v>45772</v>
       </c>
@@ -20065,7 +20065,7 @@
         <v>255.48949189999999</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A541" s="4">
         <v>45779</v>
       </c>
@@ -20073,7 +20073,7 @@
         <v>254.23606939999999</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A542" s="4">
         <v>45786</v>
       </c>
@@ -20081,7 +20081,7 @@
         <v>252.97837659999999</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A543" s="4">
         <v>45793</v>
       </c>
@@ -20089,7 +20089,7 @@
         <v>251.68383589999999</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A544" s="4">
         <v>45800</v>
       </c>
@@ -20097,7 +20097,7 @@
         <v>251.15133839999999</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A545" s="4">
         <v>45807</v>
       </c>
@@ -20105,7 +20105,7 @@
         <v>250.36283169999999</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A546" s="4">
         <v>45814</v>
       </c>
@@ -20113,7 +20113,7 @@
         <v>248.86195839999999</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A547" s="4">
         <v>45821</v>
       </c>
@@ -20121,7 +20121,7 @@
         <v>248.3089774</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A548" s="4">
         <v>45828</v>
       </c>
@@ -20129,7 +20129,7 @@
         <v>250.71980880000001</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A549" s="4">
         <v>45835</v>
       </c>
@@ -20137,7 +20137,7 @@
         <v>255.178076</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A550" s="4">
         <v>45842</v>
       </c>
@@ -20145,7 +20145,7 @@
         <v>256.09046960000001</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A551" s="4">
         <v>45849</v>
       </c>
@@ -20153,7 +20153,7 @@
         <v>254.87867739999999</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A552" s="4">
         <v>45856</v>
       </c>
@@ -20161,7 +20161,7 @@
         <v>253.89432149999999</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A553" s="4">
         <v>45863</v>
       </c>
@@ -20169,7 +20169,7 @@
         <v>254.1245538</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A554" s="4">
         <v>45870</v>
       </c>
@@ -20177,7 +20177,7 @@
         <v>253.9131763</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A555" s="4">
         <v>45877</v>
       </c>
@@ -20185,7 +20185,7 @@
         <v>254.14235149999999</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A556" s="4">
         <v>45884</v>
       </c>
@@ -20193,7 +20193,7 @@
         <v>252.74203700000001</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A557" s="4">
         <v>45891</v>
       </c>
@@ -20201,7 +20201,7 @@
         <v>251.6431882</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A558" s="4">
         <v>45898</v>
       </c>
@@ -20209,7 +20209,7 @@
         <v>252.58462359999999</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A559" s="4">
         <v>45905</v>
       </c>
@@ -20217,7 +20217,7 @@
         <v>253.45306959999999</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A560" s="4">
         <v>45912</v>
       </c>
@@ -20225,7 +20225,7 @@
         <v>254.7162792</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A561" s="4">
         <v>45919</v>
       </c>
@@ -20233,7 +20233,7 @@
         <v>254.94850439999999</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A562" s="4">
         <v>45926</v>
       </c>
@@ -20241,7 +20241,7 @@
         <v>254.88564550000001</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A563" s="4">
         <v>45933</v>
       </c>
@@ -20249,7 +20249,7 @@
         <v>256.79284209999997</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A564" s="4">
         <v>45940</v>
       </c>
@@ -20257,7 +20257,7 @@
         <v>257.77437040000001</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A565" s="4">
         <v>45947</v>
       </c>
@@ -20265,7 +20265,7 @@
         <v>257.92833419999999</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A566" s="4">
         <v>45954</v>
       </c>
@@ -20273,7 +20273,7 @@
         <v>258.02821</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A567" s="4">
         <v>45961</v>
       </c>
@@ -20281,7 +20281,7 @@
         <v>258.19403729999999</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A568" s="4">
         <v>45968</v>
       </c>
@@ -20289,7 +20289,7 @@
         <v>259.9795168</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A569" s="4">
         <v>45975</v>
       </c>
@@ -20297,7 +20297,7 @@
         <v>261.09767190000002</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A570" s="4">
         <v>45982</v>
       </c>
@@ -20305,7 +20305,7 @@
         <v>262.71388400000001</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A571" s="4">
         <v>45989</v>
       </c>
@@ -20313,7 +20313,7 @@
         <v>263.6667521</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A572" s="4">
         <v>45996</v>
       </c>
@@ -20321,7 +20321,7 @@
         <v>263.29859740000001</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A573" s="4">
         <v>46003</v>
       </c>
@@ -20329,7 +20329,7 @@
         <v>263.55805559999999</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A574" s="4">
         <v>46010</v>
       </c>
@@ -20337,7 +20337,7 @@
         <v>262.68088180000001</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A575" s="4">
         <v>46017</v>
       </c>
@@ -20345,7 +20345,7 @@
         <v>260.87594039999999</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A576" s="4">
         <v>46024</v>
       </c>
@@ -20353,7 +20353,7 @@
         <v>259.34794870000002</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A577" s="4">
         <v>46031</v>
       </c>
@@ -20361,7 +20361,7 @@
         <v>257.89418749999999</v>
       </c>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A578" s="4">
         <v>46038</v>
       </c>
@@ -20369,7 +20369,7 @@
         <v>255.8569047</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="579" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A579" s="4">
         <v>46045</v>
       </c>
@@ -20377,7 +20377,7 @@
         <v>254.82883749999999</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A580" s="4">
         <v>46052</v>
       </c>
@@ -20385,7 +20385,7 @@
         <v>254.2878493</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="581" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A581" s="4">
         <v>46059</v>
       </c>
@@ -20393,7 +20393,7 @@
         <v>253.69099979999999</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="582" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A582" s="4">
         <v>46066</v>
       </c>
@@ -20401,7 +20401,7 @@
         <v>252.8266606</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A583" s="4">
         <v>46073</v>
       </c>
@@ -20409,7 +20409,7 @@
         <v>252.3097181</v>
       </c>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A584" s="4">
         <v>46080</v>
       </c>
@@ -20417,7 +20417,7 @@
         <v>252.9454796</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="585" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A585" s="4">
         <v>46087</v>
       </c>
@@ -20425,7 +20425,7 @@
         <v>258.0163786</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="586" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A586" s="4">
         <v>46094</v>
       </c>
@@ -20433,7 +20433,7 @@
         <v>282.0612648</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="587" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A587" s="4">
         <v>46101</v>
       </c>
@@ -20441,7 +20441,7 @@
         <v>313.91989310000002</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="588" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A588" s="4">
         <v>46108</v>
       </c>
@@ -20449,7 +20449,7 @@
         <v>335.24787889999999</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="589" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A589" s="4">
         <v>46115</v>
       </c>
@@ -20457,7 +20457,7 @@
         <v>340.24394469999999</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="590" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A590" s="4">
         <v>46122</v>
       </c>
@@ -20465,7 +20465,7 @@
         <v>346.8315159</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="591" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A591" s="4">
         <v>46129</v>
       </c>
@@ -20473,7 +20473,7 @@
         <v>342.1280625</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="592" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A592" s="4">
         <v>46136</v>
       </c>
@@ -20481,7 +20481,7 @@
         <v>330.34025170000001</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A593" s="4">
         <v>46143</v>
       </c>
@@ -20489,7 +20489,7 @@
         <v>322.47753130000001</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A594" s="4">
         <v>46150</v>
       </c>
@@ -20497,7 +20497,7 @@
         <v>323.04009719999999</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A595" s="4">
         <v>46157</v>
       </c>
@@ -20505,7 +20505,7 @@
         <v>322.1773541</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A596" s="4">
         <v>46164</v>
       </c>
@@ -20513,7 +20513,7 @@
         <v>324.40253189999999</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A597" s="4">
         <v>46171</v>
       </c>
@@ -20521,7 +20521,7 @@
         <v>324.84309610000003</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A598" s="4">
         <v>46178</v>
       </c>
@@ -20529,7 +20529,7 @@
         <v>322.24647850000002</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A599" s="4">
         <v>46185</v>
       </c>
@@ -20537,7 +20537,7 @@
         <v>317.13150569999999</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A600" s="4">
         <v>46192</v>
       </c>
@@ -20545,7 +20545,7 @@
         <v>309.7663948</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A601" s="4">
         <v>46199</v>
       </c>
@@ -20553,7 +20553,7 @@
         <v>301.0267073</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A602" s="4">
         <v>46206</v>
       </c>
@@ -20561,7 +20561,7 @@
         <v>296.10165360000002</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A603" s="4">
         <v>46213</v>
       </c>
@@ -20569,7 +20569,7 @@
         <v>292.66670069999998</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A604" s="4">
         <v>46220</v>
       </c>
@@ -20577,7 +20577,7 @@
         <v>290.50132930000001</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A605" s="4">
         <v>46227</v>
       </c>
@@ -20585,7 +20585,7 @@
         <v>291.9867855</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A606" s="4">
         <v>46234</v>
       </c>
@@ -20593,7 +20593,7 @@
         <v>298.54918620000001</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A607" s="4">
         <v>46241</v>
       </c>
@@ -20601,7 +20601,7 @@
         <v>300.83523769999999</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A608" s="4">
         <v>46248</v>
       </c>
@@ -20609,7 +20609,7 @@
         <v>298.81317960000001</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A609" s="4">
         <v>46255</v>
       </c>
@@ -20617,7 +20617,7 @@
         <v>298.03322309999999</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A610" s="4">
         <v>46262</v>
       </c>
@@ -20625,7 +20625,7 @@
         <v>297.88171610000001</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A611" s="4">
         <v>46269</v>
       </c>
@@ -20633,7 +20633,7 @@
         <v>296.71102450000001</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.35">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A612" s="4">
         <v>46276</v>
       </c>

--- a/Time_series_data.xlsx
+++ b/Time_series_data.xlsx
@@ -5,23 +5,36 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/64aae3e7249de19e/Documents/DATA309-Housing-Affordability/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\danth\Documents\DATA309\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{4AD18F50-42D1-4584-9E35-3BF8A0A5C17D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D99B5AA-75E9-4A93-A826-27FE2407A246}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3260" yWindow="3260" windowWidth="16920" windowHeight="10450" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Combined" sheetId="1" r:id="rId1"/>
     <sheet name="Week" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="49" uniqueCount="48">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="50">
   <si>
     <t>Date</t>
   </si>
@@ -165,6 +178,12 @@
   </si>
   <si>
     <t>Floating Mortgage Rate</t>
+  </si>
+  <si>
+    <t>Weeks of Inventory</t>
+  </si>
+  <si>
+    <t>Weeks of Inventory Canterbury</t>
   </si>
 </sst>
 </file>
@@ -543,12 +562,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:BA142"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="23" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -690,14 +709,18 @@
       <c r="AU1" s="5" t="s">
         <v>46</v>
       </c>
-      <c r="AV1" s="6"/>
-      <c r="AW1" s="6"/>
+      <c r="AV1" s="5" t="s">
+        <v>48</v>
+      </c>
+      <c r="AW1" s="5" t="s">
+        <v>49</v>
+      </c>
       <c r="AX1" s="6"/>
       <c r="AY1" s="6"/>
       <c r="AZ1" s="6"/>
       <c r="BA1" s="6"/>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A2" s="2">
         <v>42005</v>
       </c>
@@ -797,8 +820,14 @@
       <c r="AU2">
         <v>562</v>
       </c>
-    </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV2">
+        <v>22</v>
+      </c>
+      <c r="AW2">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="3" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A3" s="2">
         <v>42036</v>
       </c>
@@ -898,8 +927,14 @@
       <c r="AU3">
         <v>409</v>
       </c>
-    </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV3">
+        <v>24</v>
+      </c>
+      <c r="AW3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A4" s="2">
         <v>42064</v>
       </c>
@@ -1041,8 +1076,14 @@
       <c r="AU4">
         <v>631</v>
       </c>
-    </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV4">
+        <v>22</v>
+      </c>
+      <c r="AW4">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="5" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A5" s="2">
         <v>42095</v>
       </c>
@@ -1142,8 +1183,14 @@
       <c r="AU5">
         <v>747</v>
       </c>
-    </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV5">
+        <v>20</v>
+      </c>
+      <c r="AW5">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="6" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A6" s="2">
         <v>42125</v>
       </c>
@@ -1243,8 +1290,14 @@
       <c r="AU6">
         <v>584</v>
       </c>
-    </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV6">
+        <v>21</v>
+      </c>
+      <c r="AW6">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="7" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A7" s="2">
         <v>42156</v>
       </c>
@@ -1357,8 +1410,14 @@
       <c r="AU7">
         <v>540</v>
       </c>
-    </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV7">
+        <v>20</v>
+      </c>
+      <c r="AW7">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="8" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A8" s="2">
         <v>42186</v>
       </c>
@@ -1458,8 +1517,14 @@
       <c r="AU8">
         <v>1025</v>
       </c>
-    </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV8">
+        <v>18</v>
+      </c>
+      <c r="AW8">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="9" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A9" s="2">
         <v>42217</v>
       </c>
@@ -1559,8 +1624,14 @@
       <c r="AU9">
         <v>674</v>
       </c>
-    </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV9">
+        <v>17</v>
+      </c>
+      <c r="AW9">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="10" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A10" s="2">
         <v>42248</v>
       </c>
@@ -1673,8 +1744,14 @@
       <c r="AU10">
         <v>461</v>
       </c>
-    </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV10">
+        <v>17</v>
+      </c>
+      <c r="AW10">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A11" s="2">
         <v>42278</v>
       </c>
@@ -1774,8 +1851,14 @@
       <c r="AU11">
         <v>617</v>
       </c>
-    </row>
-    <row r="12" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV11">
+        <v>17</v>
+      </c>
+      <c r="AW11">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="12" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A12" s="2">
         <v>42309</v>
       </c>
@@ -1875,8 +1958,14 @@
       <c r="AU12">
         <v>967</v>
       </c>
-    </row>
-    <row r="13" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV12">
+        <v>16</v>
+      </c>
+      <c r="AW12">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="13" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A13" s="2">
         <v>42339</v>
       </c>
@@ -1989,8 +2078,14 @@
       <c r="AU13">
         <v>877</v>
       </c>
-    </row>
-    <row r="14" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV13">
+        <v>16</v>
+      </c>
+      <c r="AW13">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="14" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A14" s="2">
         <v>42370</v>
       </c>
@@ -2090,8 +2185,14 @@
       <c r="AU14">
         <v>409</v>
       </c>
-    </row>
-    <row r="15" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV14">
+        <v>16</v>
+      </c>
+      <c r="AW14">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="15" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A15" s="2">
         <v>42401</v>
       </c>
@@ -2191,8 +2292,14 @@
       <c r="AU15">
         <v>667</v>
       </c>
-    </row>
-    <row r="16" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="AV15">
+        <v>16</v>
+      </c>
+      <c r="AW15">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="16" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A16" s="2">
         <v>42430</v>
       </c>
@@ -2334,8 +2441,14 @@
       <c r="AU16">
         <v>500</v>
       </c>
-    </row>
-    <row r="17" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV16">
+        <v>14</v>
+      </c>
+      <c r="AW16">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="17" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A17" s="2">
         <v>42461</v>
       </c>
@@ -2435,8 +2548,14 @@
       <c r="AU17">
         <v>619</v>
       </c>
-    </row>
-    <row r="18" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV17">
+        <v>13</v>
+      </c>
+      <c r="AW17">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="18" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A18" s="2">
         <v>42491</v>
       </c>
@@ -2536,8 +2655,14 @@
       <c r="AU18">
         <v>564</v>
       </c>
-    </row>
-    <row r="19" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV18">
+        <v>12</v>
+      </c>
+      <c r="AW18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A19" s="2">
         <v>42522</v>
       </c>
@@ -2650,8 +2775,14 @@
       <c r="AU19">
         <v>889</v>
       </c>
-    </row>
-    <row r="20" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV19">
+        <v>12</v>
+      </c>
+      <c r="AW19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A20" s="2">
         <v>42552</v>
       </c>
@@ -2751,8 +2882,14 @@
       <c r="AU20">
         <v>1050</v>
       </c>
-    </row>
-    <row r="21" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV20">
+        <v>13</v>
+      </c>
+      <c r="AW20">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="21" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A21" s="2">
         <v>42583</v>
       </c>
@@ -2852,8 +2989,14 @@
       <c r="AU21">
         <v>819</v>
       </c>
-    </row>
-    <row r="22" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV21">
+        <v>14</v>
+      </c>
+      <c r="AW21">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="22" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A22" s="2">
         <v>42614</v>
       </c>
@@ -2966,8 +3109,14 @@
       <c r="AU22">
         <v>722</v>
       </c>
-    </row>
-    <row r="23" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV22">
+        <v>14</v>
+      </c>
+      <c r="AW22">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="23" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A23" s="2">
         <v>42644</v>
       </c>
@@ -3067,8 +3216,14 @@
       <c r="AU23">
         <v>773</v>
       </c>
-    </row>
-    <row r="24" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV23">
+        <v>14</v>
+      </c>
+      <c r="AW23">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="24" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A24" s="2">
         <v>42675</v>
       </c>
@@ -3168,8 +3323,14 @@
       <c r="AU24">
         <v>1119</v>
       </c>
-    </row>
-    <row r="25" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV24">
+        <v>15</v>
+      </c>
+      <c r="AW24">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A25" s="2">
         <v>42705</v>
       </c>
@@ -3282,8 +3443,14 @@
       <c r="AU25">
         <v>625</v>
       </c>
-    </row>
-    <row r="26" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV25">
+        <v>15</v>
+      </c>
+      <c r="AW25">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="26" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A26" s="2">
         <v>42736</v>
       </c>
@@ -3383,8 +3550,14 @@
       <c r="AU26">
         <v>499</v>
       </c>
-    </row>
-    <row r="27" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV26">
+        <v>15</v>
+      </c>
+      <c r="AW26">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="27" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A27" s="2">
         <v>42767</v>
       </c>
@@ -3484,8 +3657,14 @@
       <c r="AU27">
         <v>657</v>
       </c>
-    </row>
-    <row r="28" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV27">
+        <v>17</v>
+      </c>
+      <c r="AW27">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="28" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A28" s="2">
         <v>42795</v>
       </c>
@@ -3627,8 +3806,14 @@
       <c r="AU28">
         <v>856</v>
       </c>
-    </row>
-    <row r="29" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV28">
+        <v>16</v>
+      </c>
+      <c r="AW28">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="29" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A29" s="2">
         <v>42826</v>
       </c>
@@ -3728,8 +3913,14 @@
       <c r="AU29">
         <v>619</v>
       </c>
-    </row>
-    <row r="30" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV29">
+        <v>15</v>
+      </c>
+      <c r="AW29">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A30" s="2">
         <v>42856</v>
       </c>
@@ -3829,8 +4020,14 @@
       <c r="AU30">
         <v>755</v>
       </c>
-    </row>
-    <row r="31" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV30">
+        <v>16</v>
+      </c>
+      <c r="AW30">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="31" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A31" s="2">
         <v>42887</v>
       </c>
@@ -3943,8 +4140,14 @@
       <c r="AU31">
         <v>869</v>
       </c>
-    </row>
-    <row r="32" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV31">
+        <v>17</v>
+      </c>
+      <c r="AW31">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A32" s="2">
         <v>42917</v>
       </c>
@@ -4044,8 +4247,14 @@
       <c r="AU32">
         <v>862</v>
       </c>
-    </row>
-    <row r="33" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV32">
+        <v>17</v>
+      </c>
+      <c r="AW32">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="33" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A33" s="2">
         <v>42948</v>
       </c>
@@ -4145,8 +4354,14 @@
       <c r="AU33">
         <v>1141</v>
       </c>
-    </row>
-    <row r="34" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV33">
+        <v>18</v>
+      </c>
+      <c r="AW33">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="34" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A34" s="2">
         <v>42979</v>
       </c>
@@ -4259,8 +4474,14 @@
       <c r="AU34">
         <v>927</v>
       </c>
-    </row>
-    <row r="35" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV34">
+        <v>17</v>
+      </c>
+      <c r="AW34">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="35" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A35" s="2">
         <v>43009</v>
       </c>
@@ -4360,8 +4581,14 @@
       <c r="AU35">
         <v>743</v>
       </c>
-    </row>
-    <row r="36" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV35">
+        <v>19</v>
+      </c>
+      <c r="AW35">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="36" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A36" s="2">
         <v>43040</v>
       </c>
@@ -4461,8 +4688,14 @@
       <c r="AU36">
         <v>1392</v>
       </c>
-    </row>
-    <row r="37" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV36">
+        <v>23</v>
+      </c>
+      <c r="AW36">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="37" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A37" s="2">
         <v>43070</v>
       </c>
@@ -4575,8 +4808,14 @@
       <c r="AU37">
         <v>745</v>
       </c>
-    </row>
-    <row r="38" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV37">
+        <v>23</v>
+      </c>
+      <c r="AW37">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="38" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A38" s="2">
         <v>43101</v>
       </c>
@@ -4676,8 +4915,14 @@
       <c r="AU38">
         <v>536</v>
       </c>
-    </row>
-    <row r="39" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV38">
+        <v>16</v>
+      </c>
+      <c r="AW38">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="39" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A39" s="2">
         <v>43132</v>
       </c>
@@ -4777,8 +5022,14 @@
       <c r="AU39">
         <v>748</v>
       </c>
-    </row>
-    <row r="40" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV39">
+        <v>21</v>
+      </c>
+      <c r="AW39">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="40" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A40" s="2">
         <v>43160</v>
       </c>
@@ -4920,8 +5171,14 @@
       <c r="AU40">
         <v>1173</v>
       </c>
-    </row>
-    <row r="41" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV40">
+        <v>21</v>
+      </c>
+      <c r="AW40">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="41" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A41" s="2">
         <v>43191</v>
       </c>
@@ -5021,8 +5278,14 @@
       <c r="AU41">
         <v>1115</v>
       </c>
-    </row>
-    <row r="42" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV41">
+        <v>20</v>
+      </c>
+      <c r="AW41">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="42" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A42" s="2">
         <v>43221</v>
       </c>
@@ -5122,8 +5385,14 @@
       <c r="AU42">
         <v>1240</v>
       </c>
-    </row>
-    <row r="43" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV42">
+        <v>19</v>
+      </c>
+      <c r="AW42">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="43" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A43" s="2">
         <v>43252</v>
       </c>
@@ -5236,8 +5505,14 @@
       <c r="AU43">
         <v>1062</v>
       </c>
-    </row>
-    <row r="44" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV43">
+        <v>18</v>
+      </c>
+      <c r="AW43">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="44" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A44" s="2">
         <v>43282</v>
       </c>
@@ -5337,8 +5612,14 @@
       <c r="AU44">
         <v>1021</v>
       </c>
-    </row>
-    <row r="45" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV44">
+        <v>16</v>
+      </c>
+      <c r="AW44">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="45" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A45" s="2">
         <v>43313</v>
       </c>
@@ -5438,8 +5719,14 @@
       <c r="AU45">
         <v>1195</v>
       </c>
-    </row>
-    <row r="46" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV45">
+        <v>17</v>
+      </c>
+      <c r="AW45">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="46" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A46" s="2">
         <v>43344</v>
       </c>
@@ -5552,8 +5839,14 @@
       <c r="AU46">
         <v>886</v>
       </c>
-    </row>
-    <row r="47" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV46">
+        <v>17</v>
+      </c>
+      <c r="AW46">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="47" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A47" s="2">
         <v>43374</v>
       </c>
@@ -5653,8 +5946,14 @@
       <c r="AU47">
         <v>894</v>
       </c>
-    </row>
-    <row r="48" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV47">
+        <v>18</v>
+      </c>
+      <c r="AW47">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="48" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A48" s="2">
         <v>43405</v>
       </c>
@@ -5754,8 +6053,14 @@
       <c r="AU48">
         <v>1111</v>
       </c>
-    </row>
-    <row r="49" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV48">
+        <v>16</v>
+      </c>
+      <c r="AW48">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="49" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A49" s="2">
         <v>43435</v>
       </c>
@@ -5868,8 +6173,14 @@
       <c r="AU49">
         <v>890</v>
       </c>
-    </row>
-    <row r="50" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV49">
+        <v>17</v>
+      </c>
+      <c r="AW49">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="50" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A50" s="2">
         <v>43466</v>
       </c>
@@ -5969,8 +6280,14 @@
       <c r="AU50">
         <v>971</v>
       </c>
-    </row>
-    <row r="51" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV50">
+        <v>17</v>
+      </c>
+      <c r="AW50">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="51" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A51" s="2">
         <v>43497</v>
       </c>
@@ -6070,8 +6387,14 @@
       <c r="AU51">
         <v>1284</v>
       </c>
-    </row>
-    <row r="52" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV51">
+        <v>17</v>
+      </c>
+      <c r="AW51">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="52" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A52" s="2">
         <v>43525</v>
       </c>
@@ -6213,8 +6536,14 @@
       <c r="AU52">
         <v>1231</v>
       </c>
-    </row>
-    <row r="53" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV52">
+        <v>18</v>
+      </c>
+      <c r="AW52">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="53" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A53" s="2">
         <v>43556</v>
       </c>
@@ -6314,8 +6643,14 @@
       <c r="AU53">
         <v>946</v>
       </c>
-    </row>
-    <row r="54" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV53">
+        <v>19</v>
+      </c>
+      <c r="AW53">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="54" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A54" s="2">
         <v>43586</v>
       </c>
@@ -6415,8 +6750,14 @@
       <c r="AU54">
         <v>1709</v>
       </c>
-    </row>
-    <row r="55" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV54">
+        <v>18</v>
+      </c>
+      <c r="AW54">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="55" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A55" s="2">
         <v>43617</v>
       </c>
@@ -6529,8 +6870,14 @@
       <c r="AU55">
         <v>1228</v>
       </c>
-    </row>
-    <row r="56" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV55">
+        <v>15</v>
+      </c>
+      <c r="AW55">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="56" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A56" s="2">
         <v>43647</v>
       </c>
@@ -6630,8 +6977,14 @@
       <c r="AU56">
         <v>1319</v>
       </c>
-    </row>
-    <row r="57" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV56">
+        <v>15</v>
+      </c>
+      <c r="AW56">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="57" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A57" s="2">
         <v>43678</v>
       </c>
@@ -6731,8 +7084,14 @@
       <c r="AU57">
         <v>1307</v>
       </c>
-    </row>
-    <row r="58" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV57">
+        <v>16</v>
+      </c>
+      <c r="AW57">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="58" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A58" s="2">
         <v>43709</v>
       </c>
@@ -6845,8 +7204,14 @@
       <c r="AU58">
         <v>1603</v>
       </c>
-    </row>
-    <row r="59" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV58">
+        <v>17</v>
+      </c>
+      <c r="AW58">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="59" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A59" s="2">
         <v>43739</v>
       </c>
@@ -6946,8 +7311,14 @@
       <c r="AU59">
         <v>1275</v>
       </c>
-    </row>
-    <row r="60" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV59">
+        <v>15</v>
+      </c>
+      <c r="AW59">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="60" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A60" s="2">
         <v>43770</v>
       </c>
@@ -7047,8 +7418,14 @@
       <c r="AU60">
         <v>1232</v>
       </c>
-    </row>
-    <row r="61" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV60">
+        <v>15</v>
+      </c>
+      <c r="AW60">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="61" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A61" s="2">
         <v>43800</v>
       </c>
@@ -7161,8 +7538,14 @@
       <c r="AU61">
         <v>1253</v>
       </c>
-    </row>
-    <row r="62" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV61">
+        <v>15</v>
+      </c>
+      <c r="AW61">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="62" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A62" s="2">
         <v>43831</v>
       </c>
@@ -7262,8 +7645,14 @@
       <c r="AU62">
         <v>980</v>
       </c>
-    </row>
-    <row r="63" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV62">
+        <v>15</v>
+      </c>
+      <c r="AW62">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="63" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A63" s="2">
         <v>43862</v>
       </c>
@@ -7363,8 +7752,14 @@
       <c r="AU63">
         <v>1291</v>
       </c>
-    </row>
-    <row r="64" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV63">
+        <v>15</v>
+      </c>
+      <c r="AW63">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="64" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A64" s="2">
         <v>43891</v>
       </c>
@@ -7506,8 +7901,14 @@
       <c r="AU64">
         <v>1183</v>
       </c>
-    </row>
-    <row r="65" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV64">
+        <v>14</v>
+      </c>
+      <c r="AW64">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="65" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A65" s="2">
         <v>43922</v>
       </c>
@@ -7607,8 +8008,14 @@
       <c r="AU65">
         <v>810</v>
       </c>
-    </row>
-    <row r="66" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV65">
+        <v>16</v>
+      </c>
+      <c r="AW65">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="66" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A66" s="2">
         <v>43952</v>
       </c>
@@ -7708,8 +8115,14 @@
       <c r="AU66">
         <v>1628</v>
       </c>
-    </row>
-    <row r="67" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV66">
+        <v>0</v>
+      </c>
+      <c r="AW66">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A67" s="2">
         <v>43983</v>
       </c>
@@ -7822,8 +8235,14 @@
       <c r="AU67">
         <v>1592</v>
       </c>
-    </row>
-    <row r="68" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV67">
+        <v>26</v>
+      </c>
+      <c r="AW67">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="68" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A68" s="2">
         <v>44013</v>
       </c>
@@ -7923,8 +8342,14 @@
       <c r="AU68">
         <v>1453</v>
       </c>
-    </row>
-    <row r="69" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV68">
+        <v>16</v>
+      </c>
+      <c r="AW68">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="69" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A69" s="2">
         <v>44044</v>
       </c>
@@ -8024,8 +8449,14 @@
       <c r="AU69">
         <v>1356</v>
       </c>
-    </row>
-    <row r="70" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV69">
+        <v>13</v>
+      </c>
+      <c r="AW69">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="70" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A70" s="2">
         <v>44075</v>
       </c>
@@ -8138,8 +8569,14 @@
       <c r="AU70">
         <v>1553</v>
       </c>
-    </row>
-    <row r="71" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV70">
+        <v>11</v>
+      </c>
+      <c r="AW70">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="71" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A71" s="2">
         <v>44105</v>
       </c>
@@ -8239,8 +8676,14 @@
       <c r="AU71">
         <v>1703</v>
       </c>
-    </row>
-    <row r="72" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV71">
+        <v>11</v>
+      </c>
+      <c r="AW71">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="72" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A72" s="2">
         <v>44136</v>
       </c>
@@ -8340,8 +8783,14 @@
       <c r="AU72">
         <v>1825</v>
       </c>
-    </row>
-    <row r="73" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV72">
+        <v>9</v>
+      </c>
+      <c r="AW72">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="73" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A73" s="2">
         <v>44166</v>
       </c>
@@ -8454,8 +8903,14 @@
       <c r="AU73">
         <v>1834</v>
       </c>
-    </row>
-    <row r="74" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV73">
+        <v>8</v>
+      </c>
+      <c r="AW73">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="74" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A74" s="2">
         <v>44197</v>
       </c>
@@ -8555,8 +9010,14 @@
       <c r="AU74">
         <v>1538</v>
       </c>
-    </row>
-    <row r="75" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV74">
+        <v>8</v>
+      </c>
+      <c r="AW74">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="75" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A75" s="2">
         <v>44228</v>
       </c>
@@ -8656,8 +9117,14 @@
       <c r="AU75">
         <v>1185</v>
       </c>
-    </row>
-    <row r="76" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV75">
+        <v>9</v>
+      </c>
+      <c r="AW75">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="76" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A76" s="2">
         <v>44256</v>
       </c>
@@ -8799,8 +9266,14 @@
       <c r="AU76">
         <v>1780</v>
       </c>
-    </row>
-    <row r="77" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV76">
+        <v>10</v>
+      </c>
+      <c r="AW76">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="77" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A77" s="2">
         <v>44287</v>
       </c>
@@ -8900,8 +9373,14 @@
       <c r="AU77">
         <v>1855</v>
       </c>
-    </row>
-    <row r="78" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV77">
+        <v>8</v>
+      </c>
+      <c r="AW77">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="78" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A78" s="2">
         <v>44317</v>
       </c>
@@ -9001,8 +9480,14 @@
       <c r="AU78">
         <v>1775</v>
       </c>
-    </row>
-    <row r="79" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV78">
+        <v>8</v>
+      </c>
+      <c r="AW78">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="79" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A79" s="2">
         <v>44348</v>
       </c>
@@ -9115,8 +9600,14 @@
       <c r="AU79">
         <v>1942</v>
       </c>
-    </row>
-    <row r="80" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV79">
+        <v>9</v>
+      </c>
+      <c r="AW79">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="80" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A80" s="2">
         <v>44378</v>
       </c>
@@ -9216,8 +9707,14 @@
       <c r="AU80">
         <v>1906</v>
       </c>
-    </row>
-    <row r="81" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV80">
+        <v>8</v>
+      </c>
+      <c r="AW80">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="81" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A81" s="2">
         <v>44409</v>
       </c>
@@ -9317,8 +9814,14 @@
       <c r="AU81">
         <v>2314</v>
       </c>
-    </row>
-    <row r="82" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV81">
+        <v>8</v>
+      </c>
+      <c r="AW81">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="82" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A82" s="2">
         <v>44440</v>
       </c>
@@ -9431,8 +9934,14 @@
       <c r="AU82">
         <v>2310</v>
       </c>
-    </row>
-    <row r="83" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV82">
+        <v>10</v>
+      </c>
+      <c r="AW82">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="83" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A83" s="2">
         <v>44470</v>
       </c>
@@ -9532,8 +10041,14 @@
       <c r="AU83">
         <v>1946</v>
       </c>
-    </row>
-    <row r="84" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV83">
+        <v>12</v>
+      </c>
+      <c r="AW83">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="84" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A84" s="2">
         <v>44501</v>
       </c>
@@ -9633,8 +10148,14 @@
       <c r="AU84">
         <v>2564</v>
       </c>
-    </row>
-    <row r="85" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV84">
+        <v>10</v>
+      </c>
+      <c r="AW84">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="85" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A85" s="2">
         <v>44531</v>
       </c>
@@ -9747,8 +10268,14 @@
       <c r="AU85">
         <v>2305</v>
       </c>
-    </row>
-    <row r="86" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV85">
+        <v>11</v>
+      </c>
+      <c r="AW85">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="86" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A86" s="2">
         <v>44562</v>
       </c>
@@ -9848,8 +10375,14 @@
       <c r="AU86">
         <v>1400</v>
       </c>
-    </row>
-    <row r="87" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV86">
+        <v>13</v>
+      </c>
+      <c r="AW86">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="87" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A87" s="2">
         <v>44593</v>
       </c>
@@ -9949,8 +10482,14 @@
       <c r="AU87">
         <v>2245</v>
       </c>
-    </row>
-    <row r="88" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV87">
+        <v>17</v>
+      </c>
+      <c r="AW87">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="88" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A88" s="2">
         <v>44621</v>
       </c>
@@ -10092,8 +10631,14 @@
       <c r="AU88">
         <v>3000</v>
       </c>
-    </row>
-    <row r="89" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV88">
+        <v>17</v>
+      </c>
+      <c r="AW88">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="89" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A89" s="2">
         <v>44652</v>
       </c>
@@ -10193,8 +10738,14 @@
       <c r="AU89">
         <v>2066</v>
       </c>
-    </row>
-    <row r="90" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV89">
+        <v>20</v>
+      </c>
+      <c r="AW89">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="90" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A90" s="2">
         <v>44682</v>
       </c>
@@ -10294,8 +10845,14 @@
       <c r="AU90">
         <v>2481</v>
       </c>
-    </row>
-    <row r="91" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV90">
+        <v>21</v>
+      </c>
+      <c r="AW90">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="91" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A91" s="2">
         <v>44713</v>
       </c>
@@ -10408,8 +10965,14 @@
       <c r="AU91">
         <v>2286</v>
       </c>
-    </row>
-    <row r="92" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV91">
+        <v>23</v>
+      </c>
+      <c r="AW91">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="92" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A92" s="2">
         <v>44743</v>
       </c>
@@ -10509,8 +11072,14 @@
       <c r="AU92">
         <v>2370</v>
       </c>
-    </row>
-    <row r="93" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV92">
+        <v>26</v>
+      </c>
+      <c r="AW92">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="93" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A93" s="2">
         <v>44774</v>
       </c>
@@ -10610,8 +11179,14 @@
       <c r="AU93">
         <v>2620</v>
       </c>
-    </row>
-    <row r="94" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV93">
+        <v>25</v>
+      </c>
+      <c r="AW93">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="94" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A94" s="2">
         <v>44805</v>
       </c>
@@ -10724,8 +11299,14 @@
       <c r="AU94">
         <v>2752</v>
       </c>
-    </row>
-    <row r="95" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV94">
+        <v>24</v>
+      </c>
+      <c r="AW94">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="95" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A95" s="2">
         <v>44835</v>
       </c>
@@ -10825,8 +11406,14 @@
       <c r="AU95">
         <v>2027</v>
       </c>
-    </row>
-    <row r="96" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV95">
+        <v>25</v>
+      </c>
+      <c r="AW95">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="96" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A96" s="2">
         <v>44866</v>
       </c>
@@ -10926,8 +11513,14 @@
       <c r="AU96">
         <v>2812</v>
       </c>
-    </row>
-    <row r="97" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV96">
+        <v>23</v>
+      </c>
+      <c r="AW96">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="97" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A97" s="2">
         <v>44896</v>
       </c>
@@ -11040,8 +11633,14 @@
       <c r="AU97">
         <v>2079</v>
       </c>
-    </row>
-    <row r="98" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV97">
+        <v>28</v>
+      </c>
+      <c r="AW97">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="98" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A98" s="2">
         <v>44927</v>
       </c>
@@ -11141,8 +11740,14 @@
       <c r="AU98">
         <v>1710</v>
       </c>
-    </row>
-    <row r="99" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV98">
+        <v>28</v>
+      </c>
+      <c r="AW98">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="99" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A99" s="2">
         <v>44958</v>
       </c>
@@ -11242,8 +11847,14 @@
       <c r="AU99">
         <v>1669</v>
       </c>
-    </row>
-    <row r="100" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV99">
+        <v>26</v>
+      </c>
+      <c r="AW99">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="100" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A100" s="2">
         <v>44986</v>
       </c>
@@ -11385,8 +11996,14 @@
       <c r="AU100">
         <v>2385</v>
       </c>
-    </row>
-    <row r="101" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV100">
+        <v>27</v>
+      </c>
+      <c r="AW100">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="101" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A101" s="2">
         <v>45017</v>
       </c>
@@ -11486,8 +12103,14 @@
       <c r="AU101">
         <v>1638</v>
       </c>
-    </row>
-    <row r="102" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV101">
+        <v>26</v>
+      </c>
+      <c r="AW101">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="102" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A102" s="2">
         <v>45047</v>
       </c>
@@ -11587,8 +12210,14 @@
       <c r="AU102">
         <v>2082</v>
       </c>
-    </row>
-    <row r="103" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV102">
+        <v>22</v>
+      </c>
+      <c r="AW102">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="103" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A103" s="2">
         <v>45078</v>
       </c>
@@ -11701,8 +12330,14 @@
       <c r="AU103">
         <v>1887</v>
       </c>
-    </row>
-    <row r="104" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV103">
+        <v>24</v>
+      </c>
+      <c r="AW103">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="104" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A104" s="2">
         <v>45108</v>
       </c>
@@ -11802,8 +12437,14 @@
       <c r="AU104">
         <v>1875</v>
       </c>
-    </row>
-    <row r="105" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV104">
+        <v>19</v>
+      </c>
+      <c r="AW104">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="105" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A105" s="2">
         <v>45139</v>
       </c>
@@ -11903,8 +12544,14 @@
       <c r="AU105">
         <v>1927</v>
       </c>
-    </row>
-    <row r="106" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV105">
+        <v>22</v>
+      </c>
+      <c r="AW105">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="106" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A106" s="2">
         <v>45170</v>
       </c>
@@ -12017,8 +12664,14 @@
       <c r="AU106">
         <v>1698</v>
       </c>
-    </row>
-    <row r="107" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV106">
+        <v>21</v>
+      </c>
+      <c r="AW106">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="107" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A107" s="2">
         <v>45200</v>
       </c>
@@ -12118,8 +12771,14 @@
       <c r="AU107">
         <v>1805</v>
       </c>
-    </row>
-    <row r="108" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV107">
+        <v>21</v>
+      </c>
+      <c r="AW107">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="108" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A108" s="2">
         <v>45231</v>
       </c>
@@ -12219,8 +12878,14 @@
       <c r="AU108">
         <v>1496</v>
       </c>
-    </row>
-    <row r="109" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV108">
+        <v>22</v>
+      </c>
+      <c r="AW108">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="109" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A109" s="2">
         <v>45261</v>
       </c>
@@ -12333,8 +12998,14 @@
       <c r="AU109">
         <v>1392</v>
       </c>
-    </row>
-    <row r="110" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV109">
+        <v>23</v>
+      </c>
+      <c r="AW109">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="110" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A110" s="2">
         <v>45292</v>
       </c>
@@ -12434,8 +13105,14 @@
       <c r="AU110">
         <v>1092</v>
       </c>
-    </row>
-    <row r="111" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV110">
+        <v>22</v>
+      </c>
+      <c r="AW110">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="111" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A111" s="2">
         <v>45323</v>
       </c>
@@ -12535,8 +13212,14 @@
       <c r="AU111">
         <v>1498</v>
       </c>
-    </row>
-    <row r="112" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV111">
+        <v>24</v>
+      </c>
+      <c r="AW111">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="112" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A112" s="2">
         <v>45352</v>
       </c>
@@ -12678,8 +13361,14 @@
       <c r="AU112">
         <v>1680</v>
       </c>
-    </row>
-    <row r="113" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV112">
+        <v>22</v>
+      </c>
+      <c r="AW112">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="113" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A113" s="2">
         <v>45383</v>
       </c>
@@ -12779,8 +13468,14 @@
       <c r="AU113">
         <v>1572</v>
       </c>
-    </row>
-    <row r="114" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV113">
+        <v>24</v>
+      </c>
+      <c r="AW113">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="114" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A114" s="2">
         <v>45413</v>
       </c>
@@ -12880,8 +13575,14 @@
       <c r="AU114">
         <v>1620</v>
       </c>
-    </row>
-    <row r="115" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV114">
+        <v>23</v>
+      </c>
+      <c r="AW114">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="115" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A115" s="2">
         <v>45444</v>
       </c>
@@ -12994,8 +13695,14 @@
       <c r="AU115">
         <v>1056</v>
       </c>
-    </row>
-    <row r="116" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV115">
+        <v>26</v>
+      </c>
+      <c r="AW115">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="116" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A116" s="2">
         <v>45474</v>
       </c>
@@ -13095,8 +13802,14 @@
       <c r="AU116">
         <v>1667</v>
       </c>
-    </row>
-    <row r="117" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV116">
+        <v>31</v>
+      </c>
+      <c r="AW116">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="117" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A117" s="2">
         <v>45505</v>
       </c>
@@ -13196,8 +13909,14 @@
       <c r="AU117">
         <v>1459</v>
       </c>
-    </row>
-    <row r="118" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV117">
+        <v>26</v>
+      </c>
+      <c r="AW117">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="118" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A118" s="2">
         <v>45536</v>
       </c>
@@ -13310,8 +14029,14 @@
       <c r="AU118">
         <v>1565</v>
       </c>
-    </row>
-    <row r="119" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV118">
+        <v>26</v>
+      </c>
+      <c r="AW118">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="119" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A119" s="2">
         <v>45566</v>
       </c>
@@ -13411,8 +14136,14 @@
       <c r="AU119">
         <v>1487</v>
       </c>
-    </row>
-    <row r="120" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV119">
+        <v>24</v>
+      </c>
+      <c r="AW119">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="120" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A120" s="2">
         <v>45597</v>
       </c>
@@ -13512,8 +14243,14 @@
       <c r="AU120">
         <v>1698</v>
       </c>
-    </row>
-    <row r="121" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV120">
+        <v>23</v>
+      </c>
+      <c r="AW120">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="121" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A121" s="2">
         <v>45627</v>
       </c>
@@ -13626,8 +14363,14 @@
       <c r="AU121">
         <v>1426</v>
       </c>
-    </row>
-    <row r="122" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV121">
+        <v>23</v>
+      </c>
+      <c r="AW121">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="122" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A122" s="2">
         <v>45658</v>
       </c>
@@ -13727,8 +14470,14 @@
       <c r="AU122">
         <v>1126</v>
       </c>
-    </row>
-    <row r="123" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV122">
+        <v>24</v>
+      </c>
+      <c r="AW122">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="123" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A123" s="2">
         <v>45689</v>
       </c>
@@ -13828,8 +14577,14 @@
       <c r="AU123">
         <v>1387</v>
       </c>
-    </row>
-    <row r="124" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV123">
+        <v>24</v>
+      </c>
+      <c r="AW123">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="124" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A124" s="2">
         <v>45717</v>
       </c>
@@ -13971,8 +14726,14 @@
       <c r="AU124">
         <v>2024</v>
       </c>
-    </row>
-    <row r="125" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV124">
+        <v>22</v>
+      </c>
+      <c r="AW124">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="125" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A125" s="2">
         <v>45748</v>
       </c>
@@ -14072,8 +14833,14 @@
       <c r="AU125">
         <v>1270</v>
       </c>
-    </row>
-    <row r="126" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV125">
+        <v>22</v>
+      </c>
+      <c r="AW125">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="126" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A126" s="2">
         <v>45778</v>
       </c>
@@ -14173,8 +14940,14 @@
       <c r="AU126">
         <v>1687</v>
       </c>
-    </row>
-    <row r="127" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV126">
+        <v>22</v>
+      </c>
+      <c r="AW126">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="127" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A127" s="2">
         <v>45809</v>
       </c>
@@ -14287,8 +15060,14 @@
       <c r="AU127">
         <v>1325</v>
       </c>
-    </row>
-    <row r="128" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV127">
+        <v>22</v>
+      </c>
+      <c r="AW127">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="128" spans="1:49" x14ac:dyDescent="0.35">
       <c r="A128" s="2">
         <v>45839</v>
       </c>
@@ -14388,8 +15167,14 @@
       <c r="AU128">
         <v>1740</v>
       </c>
-    </row>
-    <row r="129" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV128">
+        <v>22</v>
+      </c>
+      <c r="AW128">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="129" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A129" s="2">
         <v>45870</v>
       </c>
@@ -14489,8 +15274,14 @@
       <c r="AU129">
         <v>1588</v>
       </c>
-    </row>
-    <row r="130" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV129">
+        <v>24</v>
+      </c>
+      <c r="AW129">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="130" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A130" s="2">
         <v>45901</v>
       </c>
@@ -14603,8 +15394,14 @@
       <c r="AU130">
         <v>2146</v>
       </c>
-    </row>
-    <row r="131" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV130">
+        <v>24</v>
+      </c>
+      <c r="AW130">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="131" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A131" s="2">
         <v>45931</v>
       </c>
@@ -14704,8 +15501,14 @@
       <c r="AU131">
         <v>1952</v>
       </c>
-    </row>
-    <row r="132" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV131">
+        <v>23</v>
+      </c>
+      <c r="AW131">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="132" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A132" s="2">
         <v>45962</v>
       </c>
@@ -14805,8 +15608,14 @@
       <c r="AU132">
         <v>1910</v>
       </c>
-    </row>
-    <row r="133" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV132">
+        <v>22</v>
+      </c>
+      <c r="AW132">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="133" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A133" s="2">
         <v>45992</v>
       </c>
@@ -14919,8 +15728,14 @@
       <c r="AU133">
         <v>1829</v>
       </c>
-    </row>
-    <row r="134" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV133">
+        <v>22</v>
+      </c>
+      <c r="AW133">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="134" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A134" s="2">
         <v>46023</v>
       </c>
@@ -15020,8 +15835,14 @@
       <c r="AU134">
         <v>1338</v>
       </c>
-    </row>
-    <row r="135" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV134">
+        <v>22</v>
+      </c>
+      <c r="AW134">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="135" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A135" s="2">
         <v>46054</v>
       </c>
@@ -15115,8 +15936,14 @@
       <c r="AU135">
         <v>1636</v>
       </c>
-    </row>
-    <row r="136" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV135">
+        <v>24</v>
+      </c>
+      <c r="AW135">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="136" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A136" s="2">
         <v>46082</v>
       </c>
@@ -15231,8 +16058,14 @@
       <c r="AU136">
         <v>1948</v>
       </c>
-    </row>
-    <row r="137" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV136">
+        <v>22</v>
+      </c>
+      <c r="AW136">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="137" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A137" s="2">
         <v>46113</v>
       </c>
@@ -15326,8 +16159,14 @@
       <c r="AU137">
         <v>2088</v>
       </c>
-    </row>
-    <row r="138" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV137">
+        <v>22</v>
+      </c>
+      <c r="AW137">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="138" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A138" s="2">
         <v>46143</v>
       </c>
@@ -15421,8 +16260,14 @@
       <c r="AU138">
         <v>1966</v>
       </c>
-    </row>
-    <row r="139" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV138">
+        <v>24</v>
+      </c>
+      <c r="AW138">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="139" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A139" s="2">
         <v>46174</v>
       </c>
@@ -15525,8 +16370,14 @@
       <c r="AU139">
         <v>1813</v>
       </c>
-    </row>
-    <row r="140" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV139">
+        <v>25</v>
+      </c>
+      <c r="AW139">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="140" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A140" s="2">
         <v>46204</v>
       </c>
@@ -15618,8 +16469,14 @@
       <c r="AU140">
         <v>1810</v>
       </c>
-    </row>
-    <row r="141" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV140">
+        <v>24</v>
+      </c>
+      <c r="AW140">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="141" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A141" s="2">
         <v>46235</v>
       </c>
@@ -15697,8 +16554,18 @@
       <c r="AU141">
         <v>1736</v>
       </c>
-    </row>
-    <row r="142" spans="1:47" x14ac:dyDescent="0.3">
+      <c r="AV141">
+        <v>26</v>
+      </c>
+      <c r="AW141">
+        <v>15</v>
+      </c>
+      <c r="BA141">
+        <f ca="1">BA141</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="142" spans="1:53" x14ac:dyDescent="0.35">
       <c r="A142" s="2">
         <v>46266</v>
       </c>
@@ -15731,6 +16598,12 @@
       <c r="AH142">
         <v>2</v>
       </c>
+      <c r="AV142">
+        <v>27</v>
+      </c>
+      <c r="AW142">
+        <v>17</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -15740,12 +16613,12 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:B612"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="2" width="16" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" ht="60" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>17</v>
       </c>
@@ -15753,7 +16626,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A2" s="4">
         <v>42006</v>
       </c>
@@ -15761,7 +16634,7 @@
         <v>183.04151139999999</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A3" s="4">
         <v>42013</v>
       </c>
@@ -15769,7 +16642,7 @@
         <v>176.63809520000001</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A4" s="4">
         <v>42020</v>
       </c>
@@ -15777,7 +16650,7 @@
         <v>166.78095239999999</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A5" s="4">
         <v>42027</v>
       </c>
@@ -15785,7 +16658,7 @@
         <v>165.06666670000001</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A6" s="4">
         <v>42034</v>
       </c>
@@ -15793,7 +16666,7 @@
         <v>165.06666670000001</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A7" s="4">
         <v>42041</v>
       </c>
@@ -15801,7 +16674,7 @@
         <v>172.9238095</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A8" s="4">
         <v>42048</v>
       </c>
@@ -15809,7 +16682,7 @@
         <v>179.35238100000001</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A9" s="4">
         <v>42055</v>
       </c>
@@ -15817,7 +16690,7 @@
         <v>184.49523809999999</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A10" s="4">
         <v>42062</v>
       </c>
@@ -15825,7 +16698,7 @@
         <v>185.06666670000001</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A11" s="4">
         <v>42069</v>
       </c>
@@ -15833,7 +16706,7 @@
         <v>186.78095239999999</v>
       </c>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A12" s="4">
         <v>42076</v>
       </c>
@@ -15841,7 +16714,7 @@
         <v>187.06666670000001</v>
       </c>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A13" s="4">
         <v>42083</v>
       </c>
@@ -15849,7 +16722,7 @@
         <v>187.35238100000001</v>
       </c>
     </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A14" s="4">
         <v>42090</v>
       </c>
@@ -15857,7 +16730,7 @@
         <v>185.35238100000001</v>
       </c>
     </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A15" s="4">
         <v>42097</v>
       </c>
@@ -15865,7 +16738,7 @@
         <v>184.12893769999999</v>
       </c>
     </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A16" s="4">
         <v>42104</v>
       </c>
@@ -15873,7 +16746,7 @@
         <v>183.7538462</v>
       </c>
     </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A17" s="4">
         <v>42111</v>
       </c>
@@ -15881,7 +16754,7 @@
         <v>185.0395604</v>
       </c>
     </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A18" s="4">
         <v>42118</v>
       </c>
@@ -15889,7 +16762,7 @@
         <v>190.7538462</v>
       </c>
     </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A19" s="4">
         <v>42125</v>
       </c>
@@ -15897,7 +16770,7 @@
         <v>193.32527469999999</v>
       </c>
     </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A20" s="4">
         <v>42132</v>
       </c>
@@ -15905,7 +16778,7 @@
         <v>198.7538462</v>
       </c>
     </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A21" s="4">
         <v>42139</v>
       </c>
@@ -15913,7 +16786,7 @@
         <v>197.7538462</v>
       </c>
     </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A22" s="4">
         <v>42146</v>
       </c>
@@ -15921,7 +16794,7 @@
         <v>195.7538462</v>
       </c>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A23" s="4">
         <v>42153</v>
       </c>
@@ -15929,7 +16802,7 @@
         <v>195.7538462</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A24" s="4">
         <v>42160</v>
       </c>
@@ -15937,7 +16810,7 @@
         <v>197.4681319</v>
       </c>
     </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A25" s="4">
         <v>42167</v>
       </c>
@@ -15945,7 +16818,7 @@
         <v>198.0395604</v>
       </c>
     </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A26" s="4">
         <v>42174</v>
       </c>
@@ -15953,7 +16826,7 @@
         <v>201.4681319</v>
       </c>
     </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A27" s="4">
         <v>42181</v>
       </c>
@@ -15961,7 +16834,7 @@
         <v>202.7538462</v>
       </c>
     </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A28" s="4">
         <v>42188</v>
       </c>
@@ -15969,7 +16842,7 @@
         <v>203.8908505</v>
       </c>
     </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A29" s="4">
         <v>42195</v>
       </c>
@@ -15977,7 +16850,7 @@
         <v>203.20279500000001</v>
       </c>
     </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A30" s="4">
         <v>42202</v>
       </c>
@@ -15985,7 +16858,7 @@
         <v>202.34565219999999</v>
       </c>
     </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A31" s="4">
         <v>42209</v>
       </c>
@@ -15993,7 +16866,7 @@
         <v>202.34565219999999</v>
       </c>
     </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A32" s="4">
         <v>42216</v>
       </c>
@@ -16001,7 +16874,7 @@
         <v>199.7742236</v>
       </c>
     </row>
-    <row r="33" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A33" s="4">
         <v>42223</v>
       </c>
@@ -16009,7 +16882,7 @@
         <v>198.20279500000001</v>
       </c>
     </row>
-    <row r="34" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A34" s="4">
         <v>42230</v>
       </c>
@@ -16017,7 +16890,7 @@
         <v>197.34565219999999</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A35" s="4">
         <v>42237</v>
       </c>
@@ -16025,7 +16898,7 @@
         <v>195.91708070000001</v>
       </c>
     </row>
-    <row r="36" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A36" s="4">
         <v>42244</v>
       </c>
@@ -16033,7 +16906,7 @@
         <v>190.34565219999999</v>
       </c>
     </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A37" s="4">
         <v>42251</v>
       </c>
@@ -16041,7 +16914,7 @@
         <v>193.20279500000001</v>
       </c>
     </row>
-    <row r="38" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A38" s="4">
         <v>42258</v>
       </c>
@@ -16049,7 +16922,7 @@
         <v>195.4885093</v>
       </c>
     </row>
-    <row r="39" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A39" s="4">
         <v>42265</v>
       </c>
@@ -16057,7 +16930,7 @@
         <v>196.34565219999999</v>
       </c>
     </row>
-    <row r="40" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A40" s="4">
         <v>42272</v>
       </c>
@@ -16065,7 +16938,7 @@
         <v>196.34565219999999</v>
       </c>
     </row>
-    <row r="41" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A41" s="4">
         <v>42279</v>
       </c>
@@ -16073,7 +16946,7 @@
         <v>194.47111799999999</v>
       </c>
     </row>
-    <row r="42" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A42" s="4">
         <v>42286</v>
       </c>
@@ -16081,7 +16954,7 @@
         <v>193.06521739999999</v>
       </c>
     </row>
-    <row r="43" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A43" s="4">
         <v>42293</v>
       </c>
@@ -16089,7 +16962,7 @@
         <v>190.20807450000001</v>
       </c>
     </row>
-    <row r="44" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A44" s="4">
         <v>42300</v>
       </c>
@@ -16097,7 +16970,7 @@
         <v>186.20807450000001</v>
       </c>
     </row>
-    <row r="45" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A45" s="4">
         <v>42307</v>
       </c>
@@ -16105,7 +16978,7 @@
         <v>185.06521739999999</v>
       </c>
     </row>
-    <row r="46" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A46" s="4">
         <v>42314</v>
       </c>
@@ -16113,7 +16986,7 @@
         <v>185.06521739999999</v>
       </c>
     </row>
-    <row r="47" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A47" s="4">
         <v>42321</v>
       </c>
@@ -16121,7 +16994,7 @@
         <v>185.06521739999999</v>
       </c>
     </row>
-    <row r="48" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A48" s="4">
         <v>42328</v>
       </c>
@@ -16129,7 +17002,7 @@
         <v>183.35093169999999</v>
       </c>
     </row>
-    <row r="49" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A49" s="4">
         <v>42335</v>
       </c>
@@ -16137,7 +17010,7 @@
         <v>183.06521739999999</v>
       </c>
     </row>
-    <row r="50" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A50" s="4">
         <v>42342</v>
       </c>
@@ -16145,7 +17018,7 @@
         <v>183.06521739999999</v>
       </c>
     </row>
-    <row r="51" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A51" s="4">
         <v>42349</v>
       </c>
@@ -16153,7 +17026,7 @@
         <v>177.92236020000001</v>
       </c>
     </row>
-    <row r="52" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A52" s="4">
         <v>42356</v>
       </c>
@@ -16161,7 +17034,7 @@
         <v>175.7795031</v>
       </c>
     </row>
-    <row r="53" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A53" s="4">
         <v>42363</v>
       </c>
@@ -16169,7 +17042,7 @@
         <v>174.06521739999999</v>
       </c>
     </row>
-    <row r="54" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A54" s="4">
         <v>42370</v>
       </c>
@@ -16177,7 +17050,7 @@
         <v>173.48624670000001</v>
       </c>
     </row>
-    <row r="55" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A55" s="4">
         <v>42377</v>
       </c>
@@ -16185,7 +17058,7 @@
         <v>172.7142857</v>
       </c>
     </row>
-    <row r="56" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A56" s="4">
         <v>42384</v>
       </c>
@@ -16193,7 +17066,7 @@
         <v>171.2857143</v>
       </c>
     </row>
-    <row r="57" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A57" s="4">
         <v>42391</v>
       </c>
@@ -16201,7 +17074,7 @@
         <v>168.57142859999999</v>
       </c>
     </row>
-    <row r="58" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A58" s="4">
         <v>42398</v>
       </c>
@@ -16209,7 +17082,7 @@
         <v>169</v>
       </c>
     </row>
-    <row r="59" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A59" s="4">
         <v>42405</v>
       </c>
@@ -16217,7 +17090,7 @@
         <v>170.7142857</v>
       </c>
     </row>
-    <row r="60" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A60" s="4">
         <v>42412</v>
       </c>
@@ -16225,7 +17098,7 @@
         <v>165.14285709999999</v>
       </c>
     </row>
-    <row r="61" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A61" s="4">
         <v>42419</v>
       </c>
@@ -16233,7 +17106,7 @@
         <v>161.7142857</v>
       </c>
     </row>
-    <row r="62" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A62" s="4">
         <v>42426</v>
       </c>
@@ -16241,7 +17114,7 @@
         <v>161.7142857</v>
       </c>
     </row>
-    <row r="63" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A63" s="4">
         <v>42433</v>
       </c>
@@ -16249,7 +17122,7 @@
         <v>164.7142857</v>
       </c>
     </row>
-    <row r="64" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A64" s="4">
         <v>42440</v>
       </c>
@@ -16257,7 +17130,7 @@
         <v>168.14285709999999</v>
       </c>
     </row>
-    <row r="65" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A65" s="4">
         <v>42447</v>
       </c>
@@ -16265,7 +17138,7 @@
         <v>174.7142857</v>
       </c>
     </row>
-    <row r="66" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A66" s="4">
         <v>42454</v>
       </c>
@@ -16273,7 +17146,7 @@
         <v>174.7142857</v>
       </c>
     </row>
-    <row r="67" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A67" s="4">
         <v>42461</v>
       </c>
@@ -16281,7 +17154,7 @@
         <v>174.0036107</v>
       </c>
     </row>
-    <row r="68" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A68" s="4">
         <v>42468</v>
       </c>
@@ -16289,7 +17162,7 @@
         <v>171.34175819999999</v>
       </c>
     </row>
-    <row r="69" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A69" s="4">
         <v>42475</v>
       </c>
@@ -16297,7 +17170,7 @@
         <v>174.91318680000001</v>
       </c>
     </row>
-    <row r="70" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A70" s="4">
         <v>42482</v>
       </c>
@@ -16305,7 +17178,7 @@
         <v>174.62747250000001</v>
       </c>
     </row>
-    <row r="71" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A71" s="4">
         <v>42489</v>
       </c>
@@ -16313,7 +17186,7 @@
         <v>175.4846154</v>
       </c>
     </row>
-    <row r="72" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A72" s="4">
         <v>42496</v>
       </c>
@@ -16321,7 +17194,7 @@
         <v>176.05604400000001</v>
       </c>
     </row>
-    <row r="73" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A73" s="4">
         <v>42503</v>
       </c>
@@ -16329,7 +17202,7 @@
         <v>177.77032969999999</v>
       </c>
     </row>
-    <row r="74" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A74" s="4">
         <v>42510</v>
       </c>
@@ -16337,7 +17210,7 @@
         <v>180.34175819999999</v>
       </c>
     </row>
-    <row r="75" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A75" s="4">
         <v>42517</v>
       </c>
@@ -16345,7 +17218,7 @@
         <v>183.34175819999999</v>
       </c>
     </row>
-    <row r="76" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A76" s="4">
         <v>42524</v>
       </c>
@@ -16353,7 +17226,7 @@
         <v>185.05604400000001</v>
       </c>
     </row>
-    <row r="77" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A77" s="4">
         <v>42531</v>
       </c>
@@ -16361,7 +17234,7 @@
         <v>182.91318680000001</v>
       </c>
     </row>
-    <row r="78" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A78" s="4">
         <v>42538</v>
       </c>
@@ -16369,7 +17242,7 @@
         <v>180.77032969999999</v>
       </c>
     </row>
-    <row r="79" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A79" s="4">
         <v>42545</v>
       </c>
@@ -16377,7 +17250,7 @@
         <v>177.34175819999999</v>
       </c>
     </row>
-    <row r="80" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A80" s="4">
         <v>42552</v>
       </c>
@@ -16385,7 +17258,7 @@
         <v>178.8981742</v>
       </c>
     </row>
-    <row r="81" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A81" s="4">
         <v>42559</v>
       </c>
@@ -16393,7 +17266,7 @@
         <v>179.64006209999999</v>
       </c>
     </row>
-    <row r="82" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A82" s="4">
         <v>42566</v>
       </c>
@@ -16401,7 +17274,7 @@
         <v>173.3543478</v>
       </c>
     </row>
-    <row r="83" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A83" s="4">
         <v>42573</v>
       </c>
@@ -16409,7 +17282,7 @@
         <v>173.3543478</v>
       </c>
     </row>
-    <row r="84" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A84" s="4">
         <v>42580</v>
       </c>
@@ -16417,7 +17290,7 @@
         <v>169.0686335</v>
       </c>
     </row>
-    <row r="85" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A85" s="4">
         <v>42587</v>
       </c>
@@ -16425,7 +17298,7 @@
         <v>167.3543478</v>
       </c>
     </row>
-    <row r="86" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A86" s="4">
         <v>42594</v>
       </c>
@@ -16433,7 +17306,7 @@
         <v>168.7829193</v>
       </c>
     </row>
-    <row r="87" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A87" s="4">
         <v>42601</v>
       </c>
@@ -16441,7 +17314,7 @@
         <v>174.49720500000001</v>
       </c>
     </row>
-    <row r="88" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A88" s="4">
         <v>42608</v>
       </c>
@@ -16449,7 +17322,7 @@
         <v>177.92577639999999</v>
       </c>
     </row>
-    <row r="89" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A89" s="4">
         <v>42615</v>
       </c>
@@ -16457,7 +17330,7 @@
         <v>179.7829193</v>
       </c>
     </row>
-    <row r="90" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A90" s="4">
         <v>42622</v>
       </c>
@@ -16465,7 +17338,7 @@
         <v>178.3543478</v>
       </c>
     </row>
-    <row r="91" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A91" s="4">
         <v>42629</v>
       </c>
@@ -16473,7 +17346,7 @@
         <v>178.3543478</v>
       </c>
     </row>
-    <row r="92" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A92" s="4">
         <v>42636</v>
       </c>
@@ -16481,7 +17354,7 @@
         <v>178.3543478</v>
       </c>
     </row>
-    <row r="93" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A93" s="4">
         <v>42643</v>
       </c>
@@ -16489,7 +17362,7 @@
         <v>177.1593168</v>
       </c>
     </row>
-    <row r="94" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A94" s="4">
         <v>42650</v>
       </c>
@@ -16497,7 +17370,7 @@
         <v>177.02888200000001</v>
       </c>
     </row>
-    <row r="95" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A95" s="4">
         <v>42657</v>
       </c>
@@ -16505,7 +17378,7 @@
         <v>180.8860248</v>
       </c>
     </row>
-    <row r="96" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A96" s="4">
         <v>42664</v>
       </c>
@@ -16513,7 +17386,7 @@
         <v>184.8860248</v>
       </c>
     </row>
-    <row r="97" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A97" s="4">
         <v>42671</v>
       </c>
@@ -16521,7 +17394,7 @@
         <v>185.1717391</v>
       </c>
     </row>
-    <row r="98" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A98" s="4">
         <v>42678</v>
       </c>
@@ -16529,7 +17402,7 @@
         <v>184.02888200000001</v>
       </c>
     </row>
-    <row r="99" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A99" s="4">
         <v>42685</v>
       </c>
@@ -16537,7 +17410,7 @@
         <v>178.02888200000001</v>
       </c>
     </row>
-    <row r="100" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A100" s="4">
         <v>42692</v>
       </c>
@@ -16545,7 +17418,7 @@
         <v>175.1717391</v>
       </c>
     </row>
-    <row r="101" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A101" s="4">
         <v>42699</v>
       </c>
@@ -16553,7 +17426,7 @@
         <v>177.74316769999999</v>
       </c>
     </row>
-    <row r="102" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A102" s="4">
         <v>42706</v>
       </c>
@@ -16561,7 +17434,7 @@
         <v>180.6003106</v>
       </c>
     </row>
-    <row r="103" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A103" s="4">
         <v>42713</v>
       </c>
@@ -16569,7 +17442,7 @@
         <v>184.31459630000001</v>
       </c>
     </row>
-    <row r="104" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A104" s="4">
         <v>42720</v>
       </c>
@@ -16577,7 +17450,7 @@
         <v>187.31459630000001</v>
       </c>
     </row>
-    <row r="105" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A105" s="4">
         <v>42727</v>
       </c>
@@ -16585,7 +17458,7 @@
         <v>189.31459630000001</v>
       </c>
     </row>
-    <row r="106" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A106" s="4">
         <v>42734</v>
       </c>
@@ -16593,7 +17466,7 @@
         <v>189.72815729999999</v>
       </c>
     </row>
-    <row r="107" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A107" s="4">
         <v>42741</v>
       </c>
@@ -16601,7 +17474,7 @@
         <v>188.49523809999999</v>
       </c>
     </row>
-    <row r="108" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A108" s="4">
         <v>42748</v>
       </c>
@@ -16609,7 +17482,7 @@
         <v>189.06666670000001</v>
       </c>
     </row>
-    <row r="109" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A109" s="4">
         <v>42755</v>
       </c>
@@ -16617,7 +17490,7 @@
         <v>191.63809520000001</v>
       </c>
     </row>
-    <row r="110" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A110" s="4">
         <v>42762</v>
       </c>
@@ -16625,7 +17498,7 @@
         <v>192.06666670000001</v>
       </c>
     </row>
-    <row r="111" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A111" s="4">
         <v>42769</v>
       </c>
@@ -16633,7 +17506,7 @@
         <v>192.06666670000001</v>
       </c>
     </row>
-    <row r="112" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A112" s="4">
         <v>42776</v>
       </c>
@@ -16641,7 +17514,7 @@
         <v>190.9238095</v>
       </c>
     </row>
-    <row r="113" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A113" s="4">
         <v>42783</v>
       </c>
@@ -16649,7 +17522,7 @@
         <v>190.06666670000001</v>
       </c>
     </row>
-    <row r="114" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A114" s="4">
         <v>42790</v>
       </c>
@@ -16657,7 +17530,7 @@
         <v>190.06666670000001</v>
       </c>
     </row>
-    <row r="115" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A115" s="4">
         <v>42797</v>
       </c>
@@ -16665,7 +17538,7 @@
         <v>190.06666670000001</v>
       </c>
     </row>
-    <row r="116" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A116" s="4">
         <v>42804</v>
       </c>
@@ -16673,7 +17546,7 @@
         <v>190.06666670000001</v>
       </c>
     </row>
-    <row r="117" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A117" s="4">
         <v>42811</v>
       </c>
@@ -16681,7 +17554,7 @@
         <v>188.35238100000001</v>
       </c>
     </row>
-    <row r="118" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A118" s="4">
         <v>42818</v>
       </c>
@@ -16689,7 +17562,7 @@
         <v>187.06666670000001</v>
       </c>
     </row>
-    <row r="119" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A119" s="4">
         <v>42825</v>
       </c>
@@ -16697,7 +17570,7 @@
         <v>187.66645740000001</v>
       </c>
     </row>
-    <row r="120" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A120" s="4">
         <v>42832</v>
       </c>
@@ -16705,7 +17578,7 @@
         <v>189.16593409999999</v>
       </c>
     </row>
-    <row r="121" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A121" s="4">
         <v>42839</v>
       </c>
@@ -16713,7 +17586,7 @@
         <v>191.16593409999999</v>
       </c>
     </row>
-    <row r="122" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A122" s="4">
         <v>42846</v>
       </c>
@@ -16721,7 +17594,7 @@
         <v>191.16593409999999</v>
       </c>
     </row>
-    <row r="123" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A123" s="4">
         <v>42853</v>
       </c>
@@ -16729,7 +17602,7 @@
         <v>191.16593409999999</v>
       </c>
     </row>
-    <row r="124" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A124" s="4">
         <v>42860</v>
       </c>
@@ -16737,7 +17610,7 @@
         <v>191.16593409999999</v>
       </c>
     </row>
-    <row r="125" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A125" s="4">
         <v>42867</v>
       </c>
@@ -16745,7 +17618,7 @@
         <v>187.16593409999999</v>
       </c>
     </row>
-    <row r="126" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A126" s="4">
         <v>42874</v>
       </c>
@@ -16753,7 +17626,7 @@
         <v>187.16593409999999</v>
       </c>
     </row>
-    <row r="127" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A127" s="4">
         <v>42881</v>
       </c>
@@ -16761,7 +17634,7 @@
         <v>187.16593409999999</v>
       </c>
     </row>
-    <row r="128" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A128" s="4">
         <v>42888</v>
       </c>
@@ -16769,7 +17642,7 @@
         <v>187.16593409999999</v>
       </c>
     </row>
-    <row r="129" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A129" s="4">
         <v>42895</v>
       </c>
@@ -16777,7 +17650,7 @@
         <v>187.16593409999999</v>
       </c>
     </row>
-    <row r="130" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A130" s="4">
         <v>42902</v>
       </c>
@@ -16785,7 +17658,7 @@
         <v>180.45164840000001</v>
       </c>
     </row>
-    <row r="131" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A131" s="4">
         <v>42909</v>
       </c>
@@ -16793,7 +17666,7 @@
         <v>172.88021979999999</v>
       </c>
     </row>
-    <row r="132" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A132" s="4">
         <v>42916</v>
       </c>
@@ -16801,7 +17674,7 @@
         <v>171.8340523</v>
       </c>
     </row>
-    <row r="133" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A133" s="4">
         <v>42923</v>
       </c>
@@ -16809,7 +17682,7 @@
         <v>173.50434780000001</v>
       </c>
     </row>
-    <row r="134" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A134" s="4">
         <v>42930</v>
       </c>
@@ -16817,7 +17690,7 @@
         <v>173.50434780000001</v>
       </c>
     </row>
-    <row r="135" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A135" s="4">
         <v>42937</v>
       </c>
@@ -16825,7 +17698,7 @@
         <v>173.50434780000001</v>
       </c>
     </row>
-    <row r="136" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A136" s="4">
         <v>42944</v>
       </c>
@@ -16833,7 +17706,7 @@
         <v>175.50434780000001</v>
       </c>
     </row>
-    <row r="137" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A137" s="4">
         <v>42951</v>
       </c>
@@ -16841,7 +17714,7 @@
         <v>178.93291930000001</v>
       </c>
     </row>
-    <row r="138" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A138" s="4">
         <v>42958</v>
       </c>
@@ -16849,7 +17722,7 @@
         <v>182.7900621</v>
       </c>
     </row>
-    <row r="139" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A139" s="4">
         <v>42965</v>
       </c>
@@ -16857,7 +17730,7 @@
         <v>184.50434780000001</v>
       </c>
     </row>
-    <row r="140" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A140" s="4">
         <v>42972</v>
       </c>
@@ -16865,7 +17738,7 @@
         <v>185.64720500000001</v>
       </c>
     </row>
-    <row r="141" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A141" s="4">
         <v>42979</v>
       </c>
@@ -16873,7 +17746,7 @@
         <v>188.64720500000001</v>
       </c>
     </row>
-    <row r="142" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A142" s="4">
         <v>42986</v>
       </c>
@@ -16881,7 +17754,7 @@
         <v>191.64720500000001</v>
       </c>
     </row>
-    <row r="143" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A143" s="4">
         <v>42993</v>
       </c>
@@ -16889,7 +17762,7 @@
         <v>192.50434780000001</v>
       </c>
     </row>
-    <row r="144" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A144" s="4">
         <v>43000</v>
       </c>
@@ -16897,7 +17770,7 @@
         <v>192.50434780000001</v>
       </c>
     </row>
-    <row r="145" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A145" s="4">
         <v>43007</v>
       </c>
@@ -16905,7 +17778,7 @@
         <v>192.1118012</v>
       </c>
     </row>
-    <row r="146" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A146" s="4">
         <v>43014</v>
       </c>
@@ -16913,7 +17786,7 @@
         <v>189.75652170000001</v>
       </c>
     </row>
-    <row r="147" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A147" s="4">
         <v>43021</v>
       </c>
@@ -16921,7 +17794,7 @@
         <v>188.3279503</v>
       </c>
     </row>
-    <row r="148" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A148" s="4">
         <v>43028</v>
       </c>
@@ -16929,7 +17802,7 @@
         <v>187.75652170000001</v>
       </c>
     </row>
-    <row r="149" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A149" s="4">
         <v>43035</v>
       </c>
@@ -16937,7 +17810,7 @@
         <v>187.75652170000001</v>
       </c>
     </row>
-    <row r="150" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A150" s="4">
         <v>43042</v>
       </c>
@@ -16945,7 +17818,7 @@
         <v>192.61366459999999</v>
       </c>
     </row>
-    <row r="151" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A151" s="4">
         <v>43049</v>
       </c>
@@ -16953,7 +17826,7 @@
         <v>196.89937889999999</v>
       </c>
     </row>
-    <row r="152" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A152" s="4">
         <v>43056</v>
       </c>
@@ -16961,7 +17834,7 @@
         <v>197.75652170000001</v>
       </c>
     </row>
-    <row r="153" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A153" s="4">
         <v>43063</v>
       </c>
@@ -16969,7 +17842,7 @@
         <v>197.75652170000001</v>
       </c>
     </row>
-    <row r="154" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A154" s="4">
         <v>43070</v>
       </c>
@@ -16977,7 +17850,7 @@
         <v>199.75652170000001</v>
       </c>
     </row>
-    <row r="155" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A155" s="4">
         <v>43077</v>
       </c>
@@ -16985,7 +17858,7 @@
         <v>199.75652170000001</v>
       </c>
     </row>
-    <row r="156" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A156" s="4">
         <v>43084</v>
       </c>
@@ -16993,7 +17866,7 @@
         <v>196.89937889999999</v>
       </c>
     </row>
-    <row r="157" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A157" s="4">
         <v>43091</v>
       </c>
@@ -17001,7 +17874,7 @@
         <v>195.75652170000001</v>
       </c>
     </row>
-    <row r="158" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A158" s="4">
         <v>43098</v>
       </c>
@@ -17009,7 +17882,7 @@
         <v>195.75652170000001</v>
       </c>
     </row>
-    <row r="159" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A159" s="4">
         <v>43105</v>
       </c>
@@ -17017,7 +17890,7 @@
         <v>201.24444439999999</v>
       </c>
     </row>
-    <row r="160" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A160" s="4">
         <v>43112</v>
       </c>
@@ -17025,7 +17898,7 @@
         <v>202.10158730000001</v>
       </c>
     </row>
-    <row r="161" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A161" s="4">
         <v>43119</v>
       </c>
@@ -17033,7 +17906,7 @@
         <v>203.24444439999999</v>
       </c>
     </row>
-    <row r="162" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A162" s="4">
         <v>43126</v>
       </c>
@@ -17041,7 +17914,7 @@
         <v>203.24444439999999</v>
       </c>
     </row>
-    <row r="163" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A163" s="4">
         <v>43133</v>
       </c>
@@ -17049,7 +17922,7 @@
         <v>203.24444439999999</v>
       </c>
     </row>
-    <row r="164" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A164" s="4">
         <v>43140</v>
       </c>
@@ -17057,7 +17930,7 @@
         <v>202.3873016</v>
       </c>
     </row>
-    <row r="165" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A165" s="4">
         <v>43147</v>
       </c>
@@ -17065,7 +17938,7 @@
         <v>198.95873019999999</v>
       </c>
     </row>
-    <row r="166" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A166" s="4">
         <v>43154</v>
       </c>
@@ -17073,7 +17946,7 @@
         <v>197.24444439999999</v>
       </c>
     </row>
-    <row r="167" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A167" s="4">
         <v>43161</v>
       </c>
@@ -17081,7 +17954,7 @@
         <v>197.24444439999999</v>
       </c>
     </row>
-    <row r="168" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A168" s="4">
         <v>43168</v>
       </c>
@@ -17089,7 +17962,7 @@
         <v>197.24444439999999</v>
       </c>
     </row>
-    <row r="169" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A169" s="4">
         <v>43175</v>
       </c>
@@ -17097,7 +17970,7 @@
         <v>197.24444439999999</v>
       </c>
     </row>
-    <row r="170" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A170" s="4">
         <v>43182</v>
       </c>
@@ -17105,7 +17978,7 @@
         <v>197.24444439999999</v>
       </c>
     </row>
-    <row r="171" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A171" s="4">
         <v>43189</v>
       </c>
@@ -17113,7 +17986,7 @@
         <v>198.54406069999999</v>
       </c>
     </row>
-    <row r="172" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A172" s="4">
         <v>43196</v>
       </c>
@@ -17121,7 +17994,7 @@
         <v>194.34175819999999</v>
       </c>
     </row>
-    <row r="173" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A173" s="4">
         <v>43203</v>
       </c>
@@ -17129,7 +18002,7 @@
         <v>196.05604400000001</v>
       </c>
     </row>
-    <row r="174" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A174" s="4">
         <v>43210</v>
       </c>
@@ -17137,7 +18010,7 @@
         <v>197.34175819999999</v>
       </c>
     </row>
-    <row r="175" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A175" s="4">
         <v>43217</v>
       </c>
@@ -17145,7 +18018,7 @@
         <v>203.34175819999999</v>
       </c>
     </row>
-    <row r="176" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A176" s="4">
         <v>43224</v>
       </c>
@@ -17153,7 +18026,7 @@
         <v>203.34175819999999</v>
       </c>
     </row>
-    <row r="177" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A177" s="4">
         <v>43231</v>
       </c>
@@ -17161,7 +18034,7 @@
         <v>207.05604400000001</v>
       </c>
     </row>
-    <row r="178" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A178" s="4">
         <v>43238</v>
       </c>
@@ -17169,7 +18042,7 @@
         <v>213.05604400000001</v>
       </c>
     </row>
-    <row r="179" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A179" s="4">
         <v>43245</v>
       </c>
@@ -17177,7 +18050,7 @@
         <v>215.34175819999999</v>
       </c>
     </row>
-    <row r="180" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A180" s="4">
         <v>43252</v>
       </c>
@@ -17185,7 +18058,7 @@
         <v>215.34175819999999</v>
       </c>
     </row>
-    <row r="181" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A181" s="4">
         <v>43259</v>
       </c>
@@ -17193,7 +18066,7 @@
         <v>211.05604400000001</v>
       </c>
     </row>
-    <row r="182" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A182" s="4">
         <v>43266</v>
       </c>
@@ -17201,7 +18074,7 @@
         <v>209.34175819999999</v>
       </c>
     </row>
-    <row r="183" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A183" s="4">
         <v>43273</v>
       </c>
@@ -17209,7 +18082,7 @@
         <v>208.1989011</v>
       </c>
     </row>
-    <row r="184" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A184" s="4">
         <v>43280</v>
       </c>
@@ -17217,7 +18090,7 @@
         <v>207.72854369999999</v>
       </c>
     </row>
-    <row r="185" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A185" s="4">
         <v>43287</v>
       </c>
@@ -17225,7 +18098,7 @@
         <v>210.0492562</v>
       </c>
     </row>
-    <row r="186" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A186" s="4">
         <v>43294</v>
       </c>
@@ -17233,7 +18106,7 @@
         <v>210.0492562</v>
       </c>
     </row>
-    <row r="187" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A187" s="4">
         <v>43301</v>
       </c>
@@ -17241,7 +18114,7 @@
         <v>210.0492562</v>
       </c>
     </row>
-    <row r="188" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A188" s="4">
         <v>43308</v>
       </c>
@@ -17249,7 +18122,7 @@
         <v>211.77337900000001</v>
       </c>
     </row>
-    <row r="189" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A189" s="4">
         <v>43315</v>
       </c>
@@ -17257,7 +18130,7 @@
         <v>213.06647100000001</v>
       </c>
     </row>
-    <row r="190" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A190" s="4">
         <v>43322</v>
       </c>
@@ -17265,7 +18138,7 @@
         <v>214.79059380000001</v>
       </c>
     </row>
-    <row r="191" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A191" s="4">
         <v>43329</v>
       </c>
@@ -17273,7 +18146,7 @@
         <v>218.0951623</v>
       </c>
     </row>
-    <row r="192" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A192" s="4">
         <v>43336</v>
       </c>
@@ -17281,7 +18154,7 @@
         <v>218.0951623</v>
       </c>
     </row>
-    <row r="193" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A193" s="4">
         <v>43343</v>
       </c>
@@ -17289,7 +18162,7 @@
         <v>221.1123771</v>
       </c>
     </row>
-    <row r="194" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A194" s="4">
         <v>43350</v>
       </c>
@@ -17297,7 +18170,7 @@
         <v>222.83649980000001</v>
       </c>
     </row>
-    <row r="195" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A195" s="4">
         <v>43357</v>
       </c>
@@ -17305,7 +18178,7 @@
         <v>226.2847453</v>
       </c>
     </row>
-    <row r="196" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A196" s="4">
         <v>43364</v>
       </c>
@@ -17313,7 +18186,7 @@
         <v>227.14680659999999</v>
       </c>
     </row>
-    <row r="197" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A197" s="4">
         <v>43371</v>
       </c>
@@ -17321,7 +18194,7 @@
         <v>229.1582832</v>
       </c>
     </row>
-    <row r="198" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A198" s="4">
         <v>43378</v>
       </c>
@@ -17329,7 +18202,7 @@
         <v>240.4777005</v>
       </c>
     </row>
-    <row r="199" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A199" s="4">
         <v>43385</v>
       </c>
@@ -17337,7 +18210,7 @@
         <v>242.7844522</v>
       </c>
     </row>
-    <row r="200" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A200" s="4">
         <v>43392</v>
       </c>
@@ -17345,7 +18218,7 @@
         <v>238.89180870000001</v>
       </c>
     </row>
-    <row r="201" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A201" s="4">
         <v>43399</v>
       </c>
@@ -17353,7 +18226,7 @@
         <v>234.99916529999999</v>
       </c>
     </row>
-    <row r="202" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A202" s="4">
         <v>43406</v>
       </c>
@@ -17361,7 +18234,7 @@
         <v>228.79977020000001</v>
       </c>
     </row>
-    <row r="203" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A203" s="4">
         <v>43413</v>
       </c>
@@ -17369,7 +18242,7 @@
         <v>218.85190360000001</v>
       </c>
     </row>
-    <row r="204" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A204" s="4">
         <v>43420</v>
       </c>
@@ -17377,7 +18250,7 @@
         <v>210.4899288</v>
       </c>
     </row>
-    <row r="205" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A205" s="4">
         <v>43427</v>
       </c>
@@ -17385,7 +18258,7 @@
         <v>207.60648929999999</v>
       </c>
     </row>
-    <row r="206" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A206" s="4">
         <v>43434</v>
       </c>
@@ -17393,7 +18266,7 @@
         <v>202.99298590000001</v>
       </c>
     </row>
-    <row r="207" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A207" s="4">
         <v>43441</v>
       </c>
@@ -17401,7 +18274,7 @@
         <v>200.3978903</v>
       </c>
     </row>
-    <row r="208" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="208" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A208" s="4">
         <v>43448</v>
       </c>
@@ -17409,7 +18282,7 @@
         <v>198.66782649999999</v>
       </c>
     </row>
-    <row r="209" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A209" s="4">
         <v>43455</v>
       </c>
@@ -17417,7 +18290,7 @@
         <v>197.3702787</v>
       </c>
     </row>
-    <row r="210" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A210" s="4">
         <v>43462</v>
       </c>
@@ -17425,7 +18298,7 @@
         <v>196.5052469</v>
       </c>
     </row>
-    <row r="211" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A211" s="4">
         <v>43469</v>
       </c>
@@ -17433,7 +18306,7 @@
         <v>193.15929890000001</v>
       </c>
     </row>
-    <row r="212" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A212" s="4">
         <v>43476</v>
       </c>
@@ -17441,7 +18314,7 @@
         <v>192.79387019999999</v>
       </c>
     </row>
-    <row r="213" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A213" s="4">
         <v>43483</v>
       </c>
@@ -17449,7 +18322,7 @@
         <v>194.8113414</v>
       </c>
     </row>
-    <row r="214" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A214" s="4">
         <v>43490</v>
       </c>
@@ -17457,7 +18330,7 @@
         <v>196.8288125</v>
       </c>
     </row>
-    <row r="215" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A215" s="4">
         <v>43497</v>
       </c>
@@ -17465,7 +18338,7 @@
         <v>196.8288125</v>
       </c>
     </row>
-    <row r="216" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A216" s="4">
         <v>43504</v>
       </c>
@@ -17473,7 +18346,7 @@
         <v>196.8288125</v>
       </c>
     </row>
-    <row r="217" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A217" s="4">
         <v>43511</v>
       </c>
@@ -17481,7 +18354,7 @@
         <v>198.99038870000001</v>
       </c>
     </row>
-    <row r="218" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A218" s="4">
         <v>43518</v>
       </c>
@@ -17489,7 +18362,7 @@
         <v>204.3222768</v>
       </c>
     </row>
-    <row r="219" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A219" s="4">
         <v>43525</v>
       </c>
@@ -17497,7 +18370,7 @@
         <v>206.6279581</v>
       </c>
     </row>
-    <row r="220" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A220" s="4">
         <v>43532</v>
       </c>
@@ -17505,7 +18378,7 @@
         <v>206.91616830000001</v>
       </c>
     </row>
-    <row r="221" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A221" s="4">
         <v>43539</v>
       </c>
@@ -17513,7 +18386,7 @@
         <v>209.07774449999999</v>
       </c>
     </row>
-    <row r="222" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A222" s="4">
         <v>43546</v>
       </c>
@@ -17521,7 +18394,7 @@
         <v>206.91616830000001</v>
       </c>
     </row>
-    <row r="223" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A223" s="4">
         <v>43553</v>
       </c>
@@ -17529,7 +18402,7 @@
         <v>210.66290040000001</v>
       </c>
     </row>
-    <row r="224" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A224" s="4">
         <v>43560</v>
       </c>
@@ -17537,7 +18410,7 @@
         <v>209.4661466</v>
       </c>
     </row>
-    <row r="225" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A225" s="4">
         <v>43567</v>
       </c>
@@ -17545,7 +18418,7 @@
         <v>215.47852219999999</v>
       </c>
     </row>
-    <row r="226" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A226" s="4">
         <v>43574</v>
       </c>
@@ -17553,7 +18426,7 @@
         <v>217.053192</v>
       </c>
     </row>
-    <row r="227" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="227" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A227" s="4">
         <v>43581</v>
       </c>
@@ -17561,7 +18434,7 @@
         <v>220.48883520000001</v>
       </c>
     </row>
-    <row r="228" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A228" s="4">
         <v>43588</v>
       </c>
@@ -17569,7 +18442,7 @@
         <v>214.4764596</v>
       </c>
     </row>
-    <row r="229" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A229" s="4">
         <v>43595</v>
       </c>
@@ -17577,7 +18450,7 @@
         <v>211.6134236</v>
       </c>
     </row>
-    <row r="230" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A230" s="4">
         <v>43602</v>
       </c>
@@ -17585,7 +18458,7 @@
         <v>214.4764596</v>
       </c>
     </row>
-    <row r="231" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A231" s="4">
         <v>43609</v>
       </c>
@@ -17593,7 +18466,7 @@
         <v>220.34568340000001</v>
       </c>
     </row>
-    <row r="232" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A232" s="4">
         <v>43616</v>
       </c>
@@ -17601,7 +18474,7 @@
         <v>217.19634379999999</v>
       </c>
     </row>
-    <row r="233" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A233" s="4">
         <v>43623</v>
       </c>
@@ -17609,7 +18482,7 @@
         <v>208.60723580000001</v>
       </c>
     </row>
-    <row r="234" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A234" s="4">
         <v>43630</v>
       </c>
@@ -17617,7 +18490,7 @@
         <v>207.032566</v>
       </c>
     </row>
-    <row r="235" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A235" s="4">
         <v>43637</v>
       </c>
@@ -17625,7 +18498,7 @@
         <v>207.032566</v>
       </c>
     </row>
-    <row r="236" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A236" s="4">
         <v>43644</v>
       </c>
@@ -17633,7 +18506,7 @@
         <v>207.032566</v>
       </c>
     </row>
-    <row r="237" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A237" s="4">
         <v>43651</v>
       </c>
@@ -17641,7 +18514,7 @@
         <v>205.2073896</v>
       </c>
     </row>
-    <row r="238" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A238" s="4">
         <v>43658</v>
       </c>
@@ -17649,7 +18522,7 @@
         <v>207.35539019999999</v>
       </c>
     </row>
-    <row r="239" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A239" s="4">
         <v>43665</v>
       </c>
@@ -17657,7 +18530,7 @@
         <v>209.93299089999999</v>
       </c>
     </row>
-    <row r="240" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A240" s="4">
         <v>43672</v>
       </c>
@@ -17665,7 +18538,7 @@
         <v>210.219391</v>
       </c>
     </row>
-    <row r="241" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A241" s="4">
         <v>43679</v>
       </c>
@@ -17673,7 +18546,7 @@
         <v>210.219391</v>
       </c>
     </row>
-    <row r="242" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A242" s="4">
         <v>43686</v>
       </c>
@@ -17681,7 +18554,7 @@
         <v>210.219391</v>
       </c>
     </row>
-    <row r="243" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A243" s="4">
         <v>43693</v>
       </c>
@@ -17689,7 +18562,7 @@
         <v>210.219391</v>
       </c>
     </row>
-    <row r="244" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A244" s="4">
         <v>43700</v>
       </c>
@@ -17697,7 +18570,7 @@
         <v>210.219391</v>
       </c>
     </row>
-    <row r="245" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A245" s="4">
         <v>43707</v>
       </c>
@@ -17705,7 +18578,7 @@
         <v>211.50819139999999</v>
       </c>
     </row>
-    <row r="246" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A246" s="4">
         <v>43714</v>
       </c>
@@ -17713,7 +18586,7 @@
         <v>213.22659189999999</v>
       </c>
     </row>
-    <row r="247" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A247" s="4">
         <v>43721</v>
       </c>
@@ -17721,7 +18594,7 @@
         <v>213.22659189999999</v>
       </c>
     </row>
-    <row r="248" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A248" s="4">
         <v>43728</v>
       </c>
@@ -17729,7 +18602,7 @@
         <v>217.09299300000001</v>
       </c>
     </row>
-    <row r="249" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A249" s="4">
         <v>43735</v>
       </c>
@@ -17737,7 +18610,7 @@
         <v>216.23379270000001</v>
       </c>
     </row>
-    <row r="250" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A250" s="4">
         <v>43742</v>
       </c>
@@ -17745,7 +18618,7 @@
         <v>211.80014650000001</v>
       </c>
     </row>
-    <row r="251" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A251" s="4">
         <v>43749</v>
       </c>
@@ -17753,7 +18626,7 @@
         <v>211.0612055</v>
       </c>
     </row>
-    <row r="252" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A252" s="4">
         <v>43756</v>
       </c>
@@ -17761,7 +18634,7 @@
         <v>211.0612055</v>
       </c>
     </row>
-    <row r="253" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A253" s="4">
         <v>43763</v>
       </c>
@@ -17769,7 +18642,7 @@
         <v>211.0612055</v>
       </c>
     </row>
-    <row r="254" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A254" s="4">
         <v>43770</v>
       </c>
@@ -17777,7 +18650,7 @@
         <v>211.0612055</v>
       </c>
     </row>
-    <row r="255" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="255" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A255" s="4">
         <v>43777</v>
       </c>
@@ -17785,7 +18658,7 @@
         <v>212.3582854</v>
       </c>
     </row>
-    <row r="256" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="256" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A256" s="4">
         <v>43784</v>
       </c>
@@ -17793,7 +18666,7 @@
         <v>215.24068510000001</v>
       </c>
     </row>
-    <row r="257" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="257" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A257" s="4">
         <v>43791</v>
       </c>
@@ -17801,7 +18674,7 @@
         <v>216.10540499999999</v>
       </c>
     </row>
-    <row r="258" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="258" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A258" s="4">
         <v>43798</v>
       </c>
@@ -17809,7 +18682,7 @@
         <v>216.10540499999999</v>
       </c>
     </row>
-    <row r="259" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="259" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A259" s="4">
         <v>43805</v>
       </c>
@@ -17817,7 +18690,7 @@
         <v>216.10540499999999</v>
       </c>
     </row>
-    <row r="260" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A260" s="4">
         <v>43812</v>
       </c>
@@ -17825,7 +18698,7 @@
         <v>216.10540499999999</v>
       </c>
     </row>
-    <row r="261" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A261" s="4">
         <v>43819</v>
       </c>
@@ -17833,7 +18706,7 @@
         <v>216.10540499999999</v>
       </c>
     </row>
-    <row r="262" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="262" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A262" s="4">
         <v>43826</v>
       </c>
@@ -17841,7 +18714,7 @@
         <v>216.9701249</v>
       </c>
     </row>
-    <row r="263" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="263" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A263" s="4">
         <v>43833</v>
       </c>
@@ -17849,7 +18722,7 @@
         <v>223.05377910000001</v>
       </c>
     </row>
-    <row r="264" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="264" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A264" s="4">
         <v>43840</v>
       </c>
@@ -17857,7 +18730,7 @@
         <v>224.38956049999999</v>
       </c>
     </row>
-    <row r="265" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="265" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A265" s="4">
         <v>43847</v>
       </c>
@@ -17865,7 +18738,7 @@
         <v>222.94297800000001</v>
       </c>
     </row>
-    <row r="266" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="266" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A266" s="4">
         <v>43854</v>
       </c>
@@ -17873,7 +18746,7 @@
         <v>221.3517372</v>
       </c>
     </row>
-    <row r="267" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A267" s="4">
         <v>43861</v>
       </c>
@@ -17881,7 +18754,7 @@
         <v>216.4333566</v>
       </c>
     </row>
-    <row r="268" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A268" s="4">
         <v>43868</v>
       </c>
@@ -17889,7 +18762,7 @@
         <v>214.69745760000001</v>
       </c>
     </row>
-    <row r="269" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A269" s="4">
         <v>43875</v>
       </c>
@@ -17897,7 +18770,7 @@
         <v>214.69745760000001</v>
       </c>
     </row>
-    <row r="270" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A270" s="4">
         <v>43882</v>
       </c>
@@ -17905,7 +18778,7 @@
         <v>214.11882460000001</v>
       </c>
     </row>
-    <row r="271" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A271" s="4">
         <v>43889</v>
       </c>
@@ -17913,7 +18786,7 @@
         <v>213.2508751</v>
       </c>
     </row>
-    <row r="272" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A272" s="4">
         <v>43896</v>
       </c>
@@ -17921,7 +18794,7 @@
         <v>211.37031780000001</v>
       </c>
     </row>
-    <row r="273" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A273" s="4">
         <v>43903</v>
       </c>
@@ -17929,7 +18802,7 @@
         <v>191.98611210000001</v>
       </c>
     </row>
-    <row r="274" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A274" s="4">
         <v>43910</v>
       </c>
@@ -17937,7 +18810,7 @@
         <v>179.25618600000001</v>
       </c>
     </row>
-    <row r="275" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A275" s="4">
         <v>43917</v>
       </c>
@@ -17945,7 +18818,7 @@
         <v>179.25618600000001</v>
       </c>
     </row>
-    <row r="276" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="276" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A276" s="4">
         <v>43924</v>
       </c>
@@ -17953,7 +18826,7 @@
         <v>180.02010290000001</v>
       </c>
     </row>
-    <row r="277" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A277" s="4">
         <v>43931</v>
       </c>
@@ -17961,7 +18834,7 @@
         <v>180.3256696</v>
       </c>
     </row>
-    <row r="278" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A278" s="4">
         <v>43938</v>
       </c>
@@ -17969,7 +18842,7 @@
         <v>180.3256696</v>
       </c>
     </row>
-    <row r="279" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A279" s="4">
         <v>43945</v>
       </c>
@@ -17977,7 +18850,7 @@
         <v>180.3256696</v>
       </c>
     </row>
-    <row r="280" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A280" s="4">
         <v>43952</v>
       </c>
@@ -17985,7 +18858,7 @@
         <v>181.48454609999999</v>
       </c>
     </row>
-    <row r="281" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A281" s="4">
         <v>43959</v>
       </c>
@@ -17993,7 +18866,7 @@
         <v>182.35370349999999</v>
       </c>
     </row>
-    <row r="282" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A282" s="4">
         <v>43966</v>
       </c>
@@ -18001,7 +18874,7 @@
         <v>184.09201820000001</v>
       </c>
     </row>
-    <row r="283" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A283" s="4">
         <v>43973</v>
       </c>
@@ -18009,7 +18882,7 @@
         <v>183.51258000000001</v>
       </c>
     </row>
-    <row r="284" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A284" s="4">
         <v>43980</v>
       </c>
@@ -18017,7 +18890,7 @@
         <v>183.2228609</v>
       </c>
     </row>
-    <row r="285" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="285" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A285" s="4">
         <v>43987</v>
       </c>
@@ -18025,7 +18898,7 @@
         <v>185.39575429999999</v>
       </c>
     </row>
-    <row r="286" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A286" s="4">
         <v>43994</v>
       </c>
@@ -18033,7 +18906,7 @@
         <v>185.39575429999999</v>
       </c>
     </row>
-    <row r="287" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A287" s="4">
         <v>44001</v>
       </c>
@@ -18041,7 +18914,7 @@
         <v>185.39575429999999</v>
       </c>
     </row>
-    <row r="288" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A288" s="4">
         <v>44008</v>
       </c>
@@ -18049,7 +18922,7 @@
         <v>185.39575429999999</v>
       </c>
     </row>
-    <row r="289" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="289" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A289" s="4">
         <v>44015</v>
       </c>
@@ -18057,7 +18930,7 @@
         <v>185.95540750000001</v>
       </c>
     </row>
-    <row r="290" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A290" s="4">
         <v>44022</v>
       </c>
@@ -18065,7 +18938,7 @@
         <v>184.43864529999999</v>
       </c>
     </row>
-    <row r="291" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A291" s="4">
         <v>44029</v>
       </c>
@@ -18073,7 +18946,7 @@
         <v>185.0188531</v>
       </c>
     </row>
-    <row r="292" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A292" s="4">
         <v>44036</v>
       </c>
@@ -18081,7 +18954,7 @@
         <v>186.46937270000001</v>
       </c>
     </row>
-    <row r="293" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A293" s="4">
         <v>44043</v>
       </c>
@@ -18089,7 +18962,7 @@
         <v>188.20999620000001</v>
       </c>
     </row>
-    <row r="294" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A294" s="4">
         <v>44050</v>
       </c>
@@ -18097,7 +18970,7 @@
         <v>185.8891648</v>
       </c>
     </row>
-    <row r="295" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A295" s="4">
         <v>44057</v>
       </c>
@@ -18105,7 +18978,7 @@
         <v>185.0188531</v>
       </c>
     </row>
-    <row r="296" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A296" s="4">
         <v>44064</v>
       </c>
@@ -18113,7 +18986,7 @@
         <v>186.17926879999999</v>
       </c>
     </row>
-    <row r="297" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A297" s="4">
         <v>44071</v>
       </c>
@@ -18121,7 +18994,7 @@
         <v>189.08030790000001</v>
       </c>
     </row>
-    <row r="298" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A298" s="4">
         <v>44078</v>
       </c>
@@ -18129,7 +19002,7 @@
         <v>189.08030790000001</v>
       </c>
     </row>
-    <row r="299" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A299" s="4">
         <v>44085</v>
       </c>
@@ -18137,7 +19010,7 @@
         <v>187.33968440000001</v>
       </c>
     </row>
-    <row r="300" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A300" s="4">
         <v>44092</v>
       </c>
@@ -18145,7 +19018,7 @@
         <v>184.43864529999999</v>
       </c>
     </row>
-    <row r="301" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A301" s="4">
         <v>44099</v>
       </c>
@@ -18153,7 +19026,7 @@
         <v>185.8891648</v>
       </c>
     </row>
-    <row r="302" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="302" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A302" s="4">
         <v>44106</v>
       </c>
@@ -18161,7 +19034,7 @@
         <v>188.3545349</v>
       </c>
     </row>
-    <row r="303" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A303" s="4">
         <v>44113</v>
       </c>
@@ -18169,7 +19042,7 @@
         <v>185.3495345</v>
       </c>
     </row>
-    <row r="304" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="304" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A304" s="4">
         <v>44120</v>
       </c>
@@ -18177,7 +19050,7 @@
         <v>186.6535361</v>
       </c>
     </row>
-    <row r="305" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A305" s="4">
         <v>44127</v>
       </c>
@@ -18185,7 +19058,7 @@
         <v>186.9433142</v>
       </c>
     </row>
-    <row r="306" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A306" s="4">
         <v>44134</v>
       </c>
@@ -18193,7 +19066,7 @@
         <v>186.3637579</v>
       </c>
     </row>
-    <row r="307" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A307" s="4">
         <v>44141</v>
       </c>
@@ -18201,7 +19074,7 @@
         <v>185.92909069999999</v>
       </c>
     </row>
-    <row r="308" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A308" s="4">
         <v>44148</v>
       </c>
@@ -18209,7 +19082,7 @@
         <v>187.23309230000001</v>
       </c>
     </row>
-    <row r="309" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A309" s="4">
         <v>44155</v>
       </c>
@@ -18217,7 +19090,7 @@
         <v>185.92909069999999</v>
       </c>
     </row>
-    <row r="310" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A310" s="4">
         <v>44162</v>
       </c>
@@ -18225,7 +19098,7 @@
         <v>185.63931260000001</v>
       </c>
     </row>
-    <row r="311" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A311" s="4">
         <v>44169</v>
       </c>
@@ -18233,7 +19106,7 @@
         <v>187.95753759999999</v>
       </c>
     </row>
-    <row r="312" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A312" s="4">
         <v>44176</v>
       </c>
@@ -18241,7 +19114,7 @@
         <v>189.69620639999999</v>
       </c>
     </row>
-    <row r="313" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A313" s="4">
         <v>44183</v>
       </c>
@@ -18249,7 +19122,7 @@
         <v>188.2473157</v>
       </c>
     </row>
-    <row r="314" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A314" s="4">
         <v>44190</v>
       </c>
@@ -18257,7 +19130,7 @@
         <v>184.9148673</v>
       </c>
     </row>
-    <row r="315" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="315" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A315" s="4">
         <v>44197</v>
       </c>
@@ -18265,7 +19138,7 @@
         <v>186.3872006</v>
       </c>
     </row>
-    <row r="316" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A316" s="4">
         <v>44204</v>
       </c>
@@ -18273,7 +19146,7 @@
         <v>192.39724279999999</v>
       </c>
     </row>
-    <row r="317" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A317" s="4">
         <v>44211</v>
       </c>
@@ -18281,7 +19154,7 @@
         <v>197.1668402</v>
       </c>
     </row>
-    <row r="318" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A318" s="4">
         <v>44218</v>
       </c>
@@ -18289,7 +19162,7 @@
         <v>199.47937229999999</v>
       </c>
     </row>
-    <row r="319" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A319" s="4">
         <v>44225</v>
       </c>
@@ -18297,7 +19170,7 @@
         <v>195.57697440000001</v>
       </c>
     </row>
-    <row r="320" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A320" s="4">
         <v>44232</v>
       </c>
@@ -18305,7 +19178,7 @@
         <v>195.28790789999999</v>
       </c>
     </row>
-    <row r="321" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A321" s="4">
         <v>44239</v>
       </c>
@@ -18313,7 +19186,7 @@
         <v>200.0575053</v>
       </c>
     </row>
-    <row r="322" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A322" s="4">
         <v>44246</v>
       </c>
@@ -18321,7 +19194,7 @@
         <v>201.5028379</v>
       </c>
     </row>
-    <row r="323" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A323" s="4">
         <v>44253</v>
       </c>
@@ -18329,7 +19202,7 @@
         <v>202.94817040000001</v>
       </c>
     </row>
-    <row r="324" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A324" s="4">
         <v>44260</v>
       </c>
@@ -18337,7 +19210,7 @@
         <v>205.6943023</v>
       </c>
     </row>
-    <row r="325" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A325" s="4">
         <v>44267</v>
       </c>
@@ -18345,7 +19218,7 @@
         <v>207.13963480000001</v>
       </c>
     </row>
-    <row r="326" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A326" s="4">
         <v>44274</v>
       </c>
@@ -18353,7 +19226,7 @@
         <v>206.5615018</v>
       </c>
     </row>
-    <row r="327" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A327" s="4">
         <v>44281</v>
       </c>
@@ -18361,7 +19234,7 @@
         <v>203.52630350000001</v>
       </c>
     </row>
-    <row r="328" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A328" s="4">
         <v>44288</v>
       </c>
@@ -18369,7 +19242,7 @@
         <v>204.58969339999999</v>
       </c>
     </row>
-    <row r="329" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A329" s="4">
         <v>44295</v>
       </c>
@@ -18377,7 +19250,7 @@
         <v>205.38723580000001</v>
       </c>
     </row>
-    <row r="330" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A330" s="4">
         <v>44302</v>
       </c>
@@ -18385,7 +19258,7 @@
         <v>205.96514070000001</v>
       </c>
     </row>
-    <row r="331" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A331" s="4">
         <v>44309</v>
       </c>
@@ -18393,7 +19266,7 @@
         <v>208.9991417</v>
       </c>
     </row>
-    <row r="332" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A332" s="4">
         <v>44316</v>
       </c>
@@ -18401,7 +19274,7 @@
         <v>209.4325704</v>
       </c>
     </row>
-    <row r="333" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A333" s="4">
         <v>44323</v>
       </c>
@@ -18409,7 +19282,7 @@
         <v>210.58838019999999</v>
       </c>
     </row>
-    <row r="334" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A334" s="4">
         <v>44330</v>
       </c>
@@ -18417,7 +19290,7 @@
         <v>211.4552376</v>
       </c>
     </row>
-    <row r="335" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A335" s="4">
         <v>44337</v>
       </c>
@@ -18425,7 +19298,7 @@
         <v>211.4552376</v>
       </c>
     </row>
-    <row r="336" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A336" s="4">
         <v>44344</v>
       </c>
@@ -18433,7 +19306,7 @@
         <v>213.1889525</v>
       </c>
     </row>
-    <row r="337" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A337" s="4">
         <v>44351</v>
       </c>
@@ -18441,7 +19314,7 @@
         <v>215.50057219999999</v>
       </c>
     </row>
-    <row r="338" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A338" s="4">
         <v>44358</v>
       </c>
@@ -18449,7 +19322,7 @@
         <v>217.6677158</v>
       </c>
     </row>
-    <row r="339" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A339" s="4">
         <v>44365</v>
       </c>
@@ -18457,7 +19330,7 @@
         <v>220.70171669999999</v>
       </c>
     </row>
-    <row r="340" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="340" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A340" s="4">
         <v>44372</v>
       </c>
@@ -18465,7 +19338,7 @@
         <v>223.73571759999999</v>
       </c>
     </row>
-    <row r="341" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A341" s="4">
         <v>44379</v>
       </c>
@@ -18473,7 +19346,7 @@
         <v>223.5137599</v>
       </c>
     </row>
-    <row r="342" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="342" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A342" s="4">
         <v>44386</v>
       </c>
@@ -18481,7 +19354,7 @@
         <v>224.57014570000001</v>
       </c>
     </row>
-    <row r="343" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A343" s="4">
         <v>44393</v>
       </c>
@@ -18489,7 +19362,7 @@
         <v>224.85829910000001</v>
       </c>
     </row>
-    <row r="344" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A344" s="4">
         <v>44400</v>
       </c>
@@ -18497,7 +19370,7 @@
         <v>223.12937869999999</v>
       </c>
     </row>
-    <row r="345" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A345" s="4">
         <v>44407</v>
       </c>
@@ -18505,7 +19378,7 @@
         <v>224.71422240000001</v>
       </c>
     </row>
-    <row r="346" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A346" s="4">
         <v>44414</v>
       </c>
@@ -18513,7 +19386,7 @@
         <v>228.3161399</v>
       </c>
     </row>
-    <row r="347" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A347" s="4">
         <v>44421</v>
       </c>
@@ -18521,7 +19394,7 @@
         <v>227.307603</v>
       </c>
     </row>
-    <row r="348" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A348" s="4">
         <v>44428</v>
       </c>
@@ -18529,7 +19402,7 @@
         <v>226.7312962</v>
       </c>
     </row>
-    <row r="349" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A349" s="4">
         <v>44435</v>
       </c>
@@ -18537,7 +19410,7 @@
         <v>228.0279865</v>
       </c>
     </row>
-    <row r="350" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A350" s="4">
         <v>44442</v>
       </c>
@@ -18545,7 +19418,7 @@
         <v>229.75690689999999</v>
       </c>
     </row>
-    <row r="351" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A351" s="4">
         <v>44449</v>
       </c>
@@ -18553,7 +19426,7 @@
         <v>229.18060009999999</v>
       </c>
     </row>
-    <row r="352" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A352" s="4">
         <v>44456</v>
       </c>
@@ -18561,7 +19434,7 @@
         <v>230.04506029999999</v>
       </c>
     </row>
-    <row r="353" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A353" s="4">
         <v>44463</v>
       </c>
@@ -18569,7 +19442,7 @@
         <v>231.62990400000001</v>
       </c>
     </row>
-    <row r="354" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A354" s="4">
         <v>44470</v>
       </c>
@@ -18577,7 +19450,7 @@
         <v>231.485491</v>
       </c>
     </row>
-    <row r="355" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A355" s="4">
         <v>44477</v>
       </c>
@@ -18585,7 +19458,7 @@
         <v>234.73517810000001</v>
       </c>
     </row>
-    <row r="356" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A356" s="4">
         <v>44484</v>
       </c>
@@ -18593,7 +19466,7 @@
         <v>239.47579289999999</v>
       </c>
     </row>
-    <row r="357" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A357" s="4">
         <v>44491</v>
       </c>
@@ -18601,7 +19474,7 @@
         <v>244.36006280000001</v>
       </c>
     </row>
-    <row r="358" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A358" s="4">
         <v>44498</v>
       </c>
@@ -18609,7 +19482,7 @@
         <v>249.3879876</v>
       </c>
     </row>
-    <row r="359" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A359" s="4">
         <v>44505</v>
       </c>
@@ -18617,7 +19490,7 @@
         <v>251.5428125</v>
       </c>
     </row>
-    <row r="360" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A360" s="4">
         <v>44512</v>
       </c>
@@ -18625,7 +19498,7 @@
         <v>251.5428125</v>
       </c>
     </row>
-    <row r="361" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A361" s="4">
         <v>44519</v>
       </c>
@@ -18633,7 +19506,7 @@
         <v>251.5428125</v>
       </c>
     </row>
-    <row r="362" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A362" s="4">
         <v>44526</v>
       </c>
@@ -18641,7 +19514,7 @@
         <v>248.5260576</v>
       </c>
     </row>
-    <row r="363" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A363" s="4">
         <v>44533</v>
       </c>
@@ -18649,7 +19522,7 @@
         <v>248.5260576</v>
       </c>
     </row>
-    <row r="364" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A364" s="4">
         <v>44540</v>
       </c>
@@ -18657,7 +19530,7 @@
         <v>246.37123270000001</v>
       </c>
     </row>
-    <row r="365" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A365" s="4">
         <v>44547</v>
       </c>
@@ -18665,7 +19538,7 @@
         <v>243.49813280000001</v>
       </c>
     </row>
-    <row r="366" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A366" s="4">
         <v>44554</v>
       </c>
@@ -18673,7 +19546,7 @@
         <v>243.49813280000001</v>
       </c>
     </row>
-    <row r="367" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="367" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A367" s="4">
         <v>44561</v>
       </c>
@@ -18681,7 +19554,7 @@
         <v>244.76314500000001</v>
       </c>
     </row>
-    <row r="368" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="368" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A368" s="4">
         <v>44568</v>
       </c>
@@ -18689,7 +19562,7 @@
         <v>248.1949272</v>
       </c>
     </row>
-    <row r="369" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A369" s="4">
         <v>44575</v>
       </c>
@@ -18697,7 +19570,7 @@
         <v>250.11103080000001</v>
       </c>
     </row>
-    <row r="370" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A370" s="4">
         <v>44582</v>
       </c>
@@ -18705,7 +19578,7 @@
         <v>253.68428639999999</v>
       </c>
     </row>
-    <row r="371" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A371" s="4">
         <v>44589</v>
       </c>
@@ -18713,7 +19586,7 @@
         <v>257.0946131</v>
       </c>
     </row>
-    <row r="372" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A372" s="4">
         <v>44596</v>
       </c>
@@ -18721,7 +19594,7 @@
         <v>261.09927379999999</v>
       </c>
     </row>
-    <row r="373" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A373" s="4">
         <v>44603</v>
       </c>
@@ -18729,7 +19602,7 @@
         <v>265.04422219999998</v>
       </c>
     </row>
-    <row r="374" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A374" s="4">
         <v>44610</v>
       </c>
@@ -18737,7 +19610,7 @@
         <v>269.28846540000001</v>
       </c>
     </row>
-    <row r="375" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A375" s="4">
         <v>44617</v>
       </c>
@@ -18745,7 +19618,7 @@
         <v>272.79145390000002</v>
       </c>
     </row>
-    <row r="376" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A376" s="4">
         <v>44624</v>
       </c>
@@ -18753,7 +19626,7 @@
         <v>279.91749609999999</v>
       </c>
     </row>
-    <row r="377" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A377" s="4">
         <v>44631</v>
       </c>
@@ -18761,7 +19634,7 @@
         <v>298.78123049999999</v>
       </c>
     </row>
-    <row r="378" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A378" s="4">
         <v>44638</v>
       </c>
@@ -18769,7 +19642,7 @@
         <v>279.83095630000003</v>
       </c>
     </row>
-    <row r="379" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A379" s="4">
         <v>44645</v>
       </c>
@@ -18777,7 +19650,7 @@
         <v>269.5906956</v>
       </c>
     </row>
-    <row r="380" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A380" s="4">
         <v>44652</v>
       </c>
@@ -18785,7 +19658,7 @@
         <v>268.18248569999997</v>
       </c>
     </row>
-    <row r="381" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="381" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A381" s="4">
         <v>44659</v>
       </c>
@@ -18793,7 +19666,7 @@
         <v>263.00874069999998</v>
       </c>
     </row>
-    <row r="382" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="382" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A382" s="4">
         <v>44666</v>
       </c>
@@ -18801,7 +19674,7 @@
         <v>260.72666609999999</v>
       </c>
     </row>
-    <row r="383" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A383" s="4">
         <v>44673</v>
       </c>
@@ -18809,7 +19682,7 @@
         <v>262.00509929999998</v>
       </c>
     </row>
-    <row r="384" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A384" s="4">
         <v>44680</v>
       </c>
@@ -18817,7 +19690,7 @@
         <v>265.5409568</v>
       </c>
     </row>
-    <row r="385" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A385" s="4">
         <v>44687</v>
       </c>
@@ -18825,7 +19698,7 @@
         <v>273.5595075</v>
       </c>
     </row>
-    <row r="386" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A386" s="4">
         <v>44694</v>
       </c>
@@ -18833,7 +19706,7 @@
         <v>284.20828799999998</v>
       </c>
     </row>
-    <row r="387" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A387" s="4">
         <v>44701</v>
       </c>
@@ -18841,7 +19714,7 @@
         <v>291.4605439</v>
       </c>
     </row>
-    <row r="388" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A388" s="4">
         <v>44708</v>
       </c>
@@ -18849,7 +19722,7 @@
         <v>294.8444437</v>
       </c>
     </row>
-    <row r="389" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A389" s="4">
         <v>44715</v>
       </c>
@@ -18857,7 +19730,7 @@
         <v>294.18145060000001</v>
       </c>
     </row>
-    <row r="390" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A390" s="4">
         <v>44722</v>
       </c>
@@ -18865,7 +19738,7 @@
         <v>295.73487390000003</v>
       </c>
     </row>
-    <row r="391" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A391" s="4">
         <v>44729</v>
       </c>
@@ -18873,7 +19746,7 @@
         <v>303.65522659999999</v>
       </c>
     </row>
-    <row r="392" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A392" s="4">
         <v>44736</v>
       </c>
@@ -18881,7 +19754,7 @@
         <v>308.50244500000002</v>
       </c>
     </row>
-    <row r="393" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A393" s="4">
         <v>44743</v>
       </c>
@@ -18889,7 +19762,7 @@
         <v>308.9297353</v>
       </c>
     </row>
-    <row r="394" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A394" s="4">
         <v>44750</v>
       </c>
@@ -18897,7 +19770,7 @@
         <v>307.98289149999999</v>
       </c>
     </row>
-    <row r="395" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A395" s="4">
         <v>44757</v>
       </c>
@@ -18905,7 +19778,7 @@
         <v>303.49418120000001</v>
       </c>
     </row>
-    <row r="396" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="396" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A396" s="4">
         <v>44764</v>
       </c>
@@ -18913,7 +19786,7 @@
         <v>285.76360060000002</v>
       </c>
     </row>
-    <row r="397" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A397" s="4">
         <v>44771</v>
       </c>
@@ -18921,7 +19794,7 @@
         <v>269.54442030000001</v>
       </c>
     </row>
-    <row r="398" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A398" s="4">
         <v>44778</v>
       </c>
@@ -18929,7 +19802,7 @@
         <v>264.51088620000002</v>
       </c>
     </row>
-    <row r="399" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A399" s="4">
         <v>44785</v>
       </c>
@@ -18937,7 +19810,7 @@
         <v>261.25137999999998</v>
       </c>
     </row>
-    <row r="400" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A400" s="4">
         <v>44792</v>
       </c>
@@ -18945,7 +19818,7 @@
         <v>258.52456769999998</v>
       </c>
     </row>
-    <row r="401" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A401" s="4">
         <v>44799</v>
       </c>
@@ -18953,7 +19826,7 @@
         <v>258.6883373</v>
       </c>
     </row>
-    <row r="402" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A402" s="4">
         <v>44806</v>
       </c>
@@ -18961,7 +19834,7 @@
         <v>261.30671719999998</v>
       </c>
     </row>
-    <row r="403" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A403" s="4">
         <v>44813</v>
       </c>
@@ -18969,7 +19842,7 @@
         <v>261.83220110000002</v>
       </c>
     </row>
-    <row r="404" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A404" s="4">
         <v>44820</v>
       </c>
@@ -18977,7 +19850,7 @@
         <v>261.30040839999998</v>
       </c>
     </row>
-    <row r="405" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A405" s="4">
         <v>44827</v>
       </c>
@@ -18985,7 +19858,7 @@
         <v>261.02088070000002</v>
       </c>
     </row>
-    <row r="406" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A406" s="4">
         <v>44834</v>
       </c>
@@ -18993,7 +19866,7 @@
         <v>259.58808699999997</v>
       </c>
     </row>
-    <row r="407" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A407" s="4">
         <v>44841</v>
       </c>
@@ -19001,7 +19874,7 @@
         <v>257.17659650000002</v>
       </c>
     </row>
-    <row r="408" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A408" s="4">
         <v>44848</v>
       </c>
@@ -19009,7 +19882,7 @@
         <v>257.39425619999997</v>
       </c>
     </row>
-    <row r="409" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="409" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A409" s="4">
         <v>44855</v>
       </c>
@@ -19017,7 +19890,7 @@
         <v>257.56476759999998</v>
       </c>
     </row>
-    <row r="410" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A410" s="4">
         <v>44862</v>
       </c>
@@ -19025,7 +19898,7 @@
         <v>258.04264410000002</v>
       </c>
     </row>
-    <row r="411" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A411" s="4">
         <v>44869</v>
       </c>
@@ -19033,7 +19906,7 @@
         <v>257.1721235</v>
       </c>
     </row>
-    <row r="412" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A412" s="4">
         <v>44876</v>
       </c>
@@ -19041,7 +19914,7 @@
         <v>257.67942219999998</v>
       </c>
     </row>
-    <row r="413" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A413" s="4">
         <v>44883</v>
       </c>
@@ -19049,7 +19922,7 @@
         <v>257.61125029999999</v>
       </c>
     </row>
-    <row r="414" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A414" s="4">
         <v>44890</v>
       </c>
@@ -19057,7 +19930,7 @@
         <v>256.15321340000003</v>
       </c>
     </row>
-    <row r="415" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A415" s="4">
         <v>44897</v>
       </c>
@@ -19065,7 +19938,7 @@
         <v>252.7027133</v>
       </c>
     </row>
-    <row r="416" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A416" s="4">
         <v>44904</v>
       </c>
@@ -19073,7 +19946,7 @@
         <v>246.94869069999999</v>
       </c>
     </row>
-    <row r="417" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A417" s="4">
         <v>44911</v>
       </c>
@@ -19081,7 +19954,7 @@
         <v>240.20331669999999</v>
       </c>
     </row>
-    <row r="418" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A418" s="4">
         <v>44918</v>
       </c>
@@ -19089,7 +19962,7 @@
         <v>236.84588539999999</v>
       </c>
     </row>
-    <row r="419" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A419" s="4">
         <v>44925</v>
       </c>
@@ -19097,7 +19970,7 @@
         <v>238.81537650000001</v>
       </c>
     </row>
-    <row r="420" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A420" s="4">
         <v>44932</v>
       </c>
@@ -19105,7 +19978,7 @@
         <v>243.2337756</v>
       </c>
     </row>
-    <row r="421" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A421" s="4">
         <v>44939</v>
       </c>
@@ -19113,7 +19986,7 @@
         <v>242.88477449999999</v>
       </c>
     </row>
-    <row r="422" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A422" s="4">
         <v>44946</v>
       </c>
@@ -19121,7 +19994,7 @@
         <v>242.9840662</v>
       </c>
     </row>
-    <row r="423" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A423" s="4">
         <v>44953</v>
       </c>
@@ -19129,7 +20002,7 @@
         <v>247.95092779999999</v>
       </c>
     </row>
-    <row r="424" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A424" s="4">
         <v>44960</v>
       </c>
@@ -19137,7 +20010,7 @@
         <v>247.97214880000001</v>
       </c>
     </row>
-    <row r="425" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A425" s="4">
         <v>44967</v>
       </c>
@@ -19145,7 +20018,7 @@
         <v>246.8799731</v>
       </c>
     </row>
-    <row r="426" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A426" s="4">
         <v>44974</v>
       </c>
@@ -19153,7 +20026,7 @@
         <v>247.1915626</v>
       </c>
     </row>
-    <row r="427" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A427" s="4">
         <v>44981</v>
       </c>
@@ -19161,7 +20034,7 @@
         <v>245.26399520000001</v>
       </c>
     </row>
-    <row r="428" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A428" s="4">
         <v>44988</v>
       </c>
@@ -19169,7 +20042,7 @@
         <v>245.98254539999999</v>
       </c>
     </row>
-    <row r="429" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A429" s="4">
         <v>44995</v>
       </c>
@@ -19177,7 +20050,7 @@
         <v>245.68445399999999</v>
       </c>
     </row>
-    <row r="430" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A430" s="4">
         <v>45002</v>
       </c>
@@ -19185,7 +20058,7 @@
         <v>244.81362089999999</v>
       </c>
     </row>
-    <row r="431" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A431" s="4">
         <v>45009</v>
       </c>
@@ -19193,7 +20066,7 @@
         <v>243.06928300000001</v>
       </c>
     </row>
-    <row r="432" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A432" s="4">
         <v>45016</v>
       </c>
@@ -19201,7 +20074,7 @@
         <v>241.82912110000001</v>
       </c>
     </row>
-    <row r="433" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A433" s="4">
         <v>45023</v>
       </c>
@@ -19209,7 +20082,7 @@
         <v>246.19009589999999</v>
       </c>
     </row>
-    <row r="434" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A434" s="4">
         <v>45030</v>
       </c>
@@ -19217,7 +20090,7 @@
         <v>248.76394099999999</v>
       </c>
     </row>
-    <row r="435" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A435" s="4">
         <v>45037</v>
       </c>
@@ -19225,7 +20098,7 @@
         <v>249.3106157</v>
       </c>
     </row>
-    <row r="436" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A436" s="4">
         <v>45044</v>
       </c>
@@ -19233,7 +20106,7 @@
         <v>248.90071370000001</v>
       </c>
     </row>
-    <row r="437" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A437" s="4">
         <v>45051</v>
       </c>
@@ -19241,7 +20114,7 @@
         <v>245.37753420000001</v>
       </c>
     </row>
-    <row r="438" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A438" s="4">
         <v>45058</v>
       </c>
@@ -19249,7 +20122,7 @@
         <v>239.63877189999999</v>
       </c>
     </row>
-    <row r="439" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A439" s="4">
         <v>45065</v>
       </c>
@@ -19257,7 +20130,7 @@
         <v>235.75663729999999</v>
       </c>
     </row>
-    <row r="440" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A440" s="4">
         <v>45072</v>
       </c>
@@ -19265,7 +20138,7 @@
         <v>236.32711029999999</v>
       </c>
     </row>
-    <row r="441" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A441" s="4">
         <v>45079</v>
       </c>
@@ -19273,7 +20146,7 @@
         <v>239.2969861</v>
       </c>
     </row>
-    <row r="442" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A442" s="4">
         <v>45086</v>
       </c>
@@ -19281,7 +20154,7 @@
         <v>238.78242059999999</v>
       </c>
     </row>
-    <row r="443" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A443" s="4">
         <v>45093</v>
       </c>
@@ -19289,7 +20162,7 @@
         <v>238.5626288</v>
       </c>
     </row>
-    <row r="444" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A444" s="4">
         <v>45100</v>
       </c>
@@ -19297,7 +20170,7 @@
         <v>238.62232900000001</v>
       </c>
     </row>
-    <row r="445" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A445" s="4">
         <v>45107</v>
       </c>
@@ -19305,7 +20178,7 @@
         <v>243.49078900000001</v>
       </c>
     </row>
-    <row r="446" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A446" s="4">
         <v>45114</v>
       </c>
@@ -19313,7 +20186,7 @@
         <v>264.64432640000001</v>
       </c>
     </row>
-    <row r="447" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A447" s="4">
         <v>45121</v>
       </c>
@@ -19321,7 +20194,7 @@
         <v>264.28787560000001</v>
       </c>
     </row>
-    <row r="448" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A448" s="4">
         <v>45128</v>
       </c>
@@ -19329,7 +20202,7 @@
         <v>266.78185259999998</v>
       </c>
     </row>
-    <row r="449" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A449" s="4">
         <v>45135</v>
       </c>
@@ -19337,7 +20210,7 @@
         <v>272.374798</v>
       </c>
     </row>
-    <row r="450" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A450" s="4">
         <v>45142</v>
       </c>
@@ -19345,7 +20218,7 @@
         <v>277.76442739999999</v>
       </c>
     </row>
-    <row r="451" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A451" s="4">
         <v>45149</v>
       </c>
@@ -19353,7 +20226,7 @@
         <v>281.27566789999997</v>
       </c>
     </row>
-    <row r="452" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A452" s="4">
         <v>45156</v>
       </c>
@@ -19361,7 +20234,7 @@
         <v>286.40290950000002</v>
       </c>
     </row>
-    <row r="453" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A453" s="4">
         <v>45163</v>
       </c>
@@ -19369,7 +20242,7 @@
         <v>288.64616799999999</v>
       </c>
     </row>
-    <row r="454" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A454" s="4">
         <v>45170</v>
       </c>
@@ -19377,7 +20250,7 @@
         <v>290.93826280000002</v>
       </c>
     </row>
-    <row r="455" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A455" s="4">
         <v>45177</v>
       </c>
@@ -19385,7 +20258,7 @@
         <v>293.43467920000001</v>
       </c>
     </row>
-    <row r="456" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A456" s="4">
         <v>45184</v>
       </c>
@@ -19393,7 +20266,7 @@
         <v>296.53593660000001</v>
       </c>
     </row>
-    <row r="457" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A457" s="4">
         <v>45191</v>
       </c>
@@ -19401,7 +20274,7 @@
         <v>301.00098309999998</v>
       </c>
     </row>
-    <row r="458" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="458" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A458" s="4">
         <v>45198</v>
       </c>
@@ -19409,7 +20282,7 @@
         <v>301.93506430000002</v>
       </c>
     </row>
-    <row r="459" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A459" s="4">
         <v>45205</v>
       </c>
@@ -19417,7 +20290,7 @@
         <v>296.72163069999999</v>
       </c>
     </row>
-    <row r="460" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A460" s="4">
         <v>45212</v>
       </c>
@@ -19425,7 +20298,7 @@
         <v>292.43642139999997</v>
       </c>
     </row>
-    <row r="461" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A461" s="4">
         <v>45219</v>
       </c>
@@ -19433,7 +20306,7 @@
         <v>289.36485520000002</v>
       </c>
     </row>
-    <row r="462" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A462" s="4">
         <v>45226</v>
       </c>
@@ -19441,7 +20314,7 @@
         <v>287.62794070000001</v>
       </c>
     </row>
-    <row r="463" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A463" s="4">
         <v>45233</v>
       </c>
@@ -19449,7 +20322,7 @@
         <v>286.79197429999999</v>
       </c>
     </row>
-    <row r="464" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A464" s="4">
         <v>45240</v>
       </c>
@@ -19457,7 +20330,7 @@
         <v>285.5771848</v>
       </c>
     </row>
-    <row r="465" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A465" s="4">
         <v>45247</v>
       </c>
@@ -19465,7 +20338,7 @@
         <v>282.63599570000002</v>
       </c>
     </row>
-    <row r="466" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A466" s="4">
         <v>45254</v>
       </c>
@@ -19473,7 +20346,7 @@
         <v>279.73079469999999</v>
       </c>
     </row>
-    <row r="467" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A467" s="4">
         <v>45261</v>
       </c>
@@ -19481,7 +20354,7 @@
         <v>276.71581229999998</v>
       </c>
     </row>
-    <row r="468" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A468" s="4">
         <v>45268</v>
       </c>
@@ -19489,7 +20362,7 @@
         <v>272.97806919999999</v>
       </c>
     </row>
-    <row r="469" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="469" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A469" s="4">
         <v>45275</v>
       </c>
@@ -19497,7 +20370,7 @@
         <v>268.07097060000001</v>
       </c>
     </row>
-    <row r="470" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="470" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A470" s="4">
         <v>45282</v>
       </c>
@@ -19505,7 +20378,7 @@
         <v>266.05018360000003</v>
       </c>
     </row>
-    <row r="471" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A471" s="4">
         <v>45289</v>
       </c>
@@ -19513,7 +20386,7 @@
         <v>265.76198449999998</v>
       </c>
     </row>
-    <row r="472" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A472" s="4">
         <v>45296</v>
       </c>
@@ -19521,7 +20394,7 @@
         <v>265.7174574</v>
       </c>
     </row>
-    <row r="473" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A473" s="4">
         <v>45303</v>
       </c>
@@ -19529,7 +20402,7 @@
         <v>265.3049054</v>
       </c>
     </row>
-    <row r="474" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A474" s="4">
         <v>45310</v>
       </c>
@@ -19537,7 +20410,7 @@
         <v>265.05007430000001</v>
       </c>
     </row>
-    <row r="475" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A475" s="4">
         <v>45317</v>
       </c>
@@ -19545,7 +20418,7 @@
         <v>266.54534100000001</v>
       </c>
     </row>
-    <row r="476" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A476" s="4">
         <v>45324</v>
       </c>
@@ -19553,7 +20426,7 @@
         <v>272.1266885</v>
       </c>
     </row>
-    <row r="477" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A477" s="4">
         <v>45331</v>
       </c>
@@ -19561,7 +20434,7 @@
         <v>275.58411630000001</v>
       </c>
     </row>
-    <row r="478" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A478" s="4">
         <v>45338</v>
       </c>
@@ -19569,7 +20442,7 @@
         <v>277.82113989999999</v>
       </c>
     </row>
-    <row r="479" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A479" s="4">
         <v>45345</v>
       </c>
@@ -19577,7 +20450,7 @@
         <v>279.24328509999998</v>
       </c>
     </row>
-    <row r="480" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A480" s="4">
         <v>45352</v>
       </c>
@@ -19585,7 +20458,7 @@
         <v>279.32440580000002</v>
       </c>
     </row>
-    <row r="481" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="481" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A481" s="4">
         <v>45359</v>
       </c>
@@ -19593,7 +20466,7 @@
         <v>280.16422399999999</v>
       </c>
     </row>
-    <row r="482" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A482" s="4">
         <v>45366</v>
       </c>
@@ -19601,7 +20474,7 @@
         <v>279.50204439999999</v>
       </c>
     </row>
-    <row r="483" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A483" s="4">
         <v>45373</v>
       </c>
@@ -19609,7 +20482,7 @@
         <v>279.84370130000002</v>
       </c>
     </row>
-    <row r="484" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="484" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A484" s="4">
         <v>45380</v>
       </c>
@@ -19617,7 +20490,7 @@
         <v>282.27261659999999</v>
       </c>
     </row>
-    <row r="485" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A485" s="4">
         <v>45387</v>
       </c>
@@ -19625,7 +20498,7 @@
         <v>283.56304640000002</v>
       </c>
     </row>
-    <row r="486" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A486" s="4">
         <v>45394</v>
       </c>
@@ -19633,7 +20506,7 @@
         <v>284.86303859999998</v>
       </c>
     </row>
-    <row r="487" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A487" s="4">
         <v>45401</v>
       </c>
@@ -19641,7 +20514,7 @@
         <v>285.19454189999999</v>
       </c>
     </row>
-    <row r="488" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A488" s="4">
         <v>45408</v>
       </c>
@@ -19649,7 +20522,7 @@
         <v>284.59299549999997</v>
       </c>
     </row>
-    <row r="489" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A489" s="4">
         <v>45415</v>
       </c>
@@ -19657,7 +20530,7 @@
         <v>283.61880880000001</v>
       </c>
     </row>
-    <row r="490" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A490" s="4">
         <v>45422</v>
       </c>
@@ -19665,7 +20538,7 @@
         <v>281.86104419999998</v>
       </c>
     </row>
-    <row r="491" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A491" s="4">
         <v>45429</v>
       </c>
@@ -19673,7 +20546,7 @@
         <v>278.70979670000003</v>
       </c>
     </row>
-    <row r="492" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A492" s="4">
         <v>45436</v>
       </c>
@@ -19681,7 +20554,7 @@
         <v>275.94843550000002</v>
       </c>
     </row>
-    <row r="493" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A493" s="4">
         <v>45443</v>
       </c>
@@ -19689,7 +20562,7 @@
         <v>273.23884850000002</v>
       </c>
     </row>
-    <row r="494" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A494" s="4">
         <v>45450</v>
       </c>
@@ -19697,7 +20570,7 @@
         <v>268.67537090000002</v>
       </c>
     </row>
-    <row r="495" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="495" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A495" s="4">
         <v>45457</v>
       </c>
@@ -19705,7 +20578,7 @@
         <v>264.30792220000001</v>
       </c>
     </row>
-    <row r="496" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A496" s="4">
         <v>45464</v>
       </c>
@@ -19713,7 +20586,7 @@
         <v>263.13433659999998</v>
       </c>
     </row>
-    <row r="497" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A497" s="4">
         <v>45471</v>
       </c>
@@ -19721,7 +20594,7 @@
         <v>265.49181420000002</v>
       </c>
     </row>
-    <row r="498" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A498" s="4">
         <v>45478</v>
       </c>
@@ -19729,7 +20602,7 @@
         <v>262.13687579999998</v>
       </c>
     </row>
-    <row r="499" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A499" s="4">
         <v>45485</v>
       </c>
@@ -19737,7 +20610,7 @@
         <v>264.27202169999998</v>
       </c>
     </row>
-    <row r="500" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A500" s="4">
         <v>45492</v>
       </c>
@@ -19745,7 +20618,7 @@
         <v>264.63758100000001</v>
       </c>
     </row>
-    <row r="501" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A501" s="4">
         <v>45499</v>
       </c>
@@ -19753,7 +20626,7 @@
         <v>264.28085329999999</v>
       </c>
     </row>
-    <row r="502" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A502" s="4">
         <v>45506</v>
       </c>
@@ -19761,7 +20634,7 @@
         <v>263.49845119999998</v>
       </c>
     </row>
-    <row r="503" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A503" s="4">
         <v>45513</v>
       </c>
@@ -19769,7 +20642,7 @@
         <v>262.51468549999998</v>
       </c>
     </row>
-    <row r="504" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A504" s="4">
         <v>45520</v>
       </c>
@@ -19777,7 +20650,7 @@
         <v>260.56074799999999</v>
       </c>
     </row>
-    <row r="505" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A505" s="4">
         <v>45527</v>
       </c>
@@ -19785,7 +20658,7 @@
         <v>258.82574519999997</v>
       </c>
     </row>
-    <row r="506" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A506" s="4">
         <v>45534</v>
       </c>
@@ -19793,7 +20666,7 @@
         <v>256.43474670000001</v>
       </c>
     </row>
-    <row r="507" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A507" s="4">
         <v>45541</v>
       </c>
@@ -19801,7 +20674,7 @@
         <v>254.4328812</v>
       </c>
     </row>
-    <row r="508" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A508" s="4">
         <v>45548</v>
       </c>
@@ -19809,7 +20682,7 @@
         <v>251.69259450000001</v>
       </c>
     </row>
-    <row r="509" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A509" s="4">
         <v>45555</v>
       </c>
@@ -19817,7 +20690,7 @@
         <v>249.01809610000001</v>
       </c>
     </row>
-    <row r="510" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A510" s="4">
         <v>45562</v>
       </c>
@@ -19825,7 +20698,7 @@
         <v>247.26206189999999</v>
       </c>
     </row>
-    <row r="511" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A511" s="4">
         <v>45569</v>
       </c>
@@ -19833,7 +20706,7 @@
         <v>246.79487750000001</v>
       </c>
     </row>
-    <row r="512" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A512" s="4">
         <v>45576</v>
       </c>
@@ -19841,7 +20714,7 @@
         <v>249.43657540000001</v>
       </c>
     </row>
-    <row r="513" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A513" s="4">
         <v>45583</v>
       </c>
@@ -19849,7 +20722,7 @@
         <v>252.26114899999999</v>
       </c>
     </row>
-    <row r="514" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A514" s="4">
         <v>45590</v>
       </c>
@@ -19857,7 +20730,7 @@
         <v>253.18533740000001</v>
       </c>
     </row>
-    <row r="515" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A515" s="4">
         <v>45597</v>
       </c>
@@ -19865,7 +20738,7 @@
         <v>252.33932129999999</v>
       </c>
     </row>
-    <row r="516" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A516" s="4">
         <v>45604</v>
       </c>
@@ -19873,7 +20746,7 @@
         <v>253.76761680000001</v>
       </c>
     </row>
-    <row r="517" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="517" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A517" s="4">
         <v>45611</v>
       </c>
@@ -19881,7 +20754,7 @@
         <v>255.8128596</v>
       </c>
     </row>
-    <row r="518" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A518" s="4">
         <v>45618</v>
       </c>
@@ -19889,7 +20762,7 @@
         <v>255.972995</v>
       </c>
     </row>
-    <row r="519" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A519" s="4">
         <v>45625</v>
       </c>
@@ -19897,7 +20770,7 @@
         <v>255.8713042</v>
       </c>
     </row>
-    <row r="520" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A520" s="4">
         <v>45632</v>
       </c>
@@ -19905,7 +20778,7 @@
         <v>255.46482409999999</v>
       </c>
     </row>
-    <row r="521" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A521" s="4">
         <v>45639</v>
       </c>
@@ -19913,7 +20786,7 @@
         <v>255.64667940000001</v>
       </c>
     </row>
-    <row r="522" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A522" s="4">
         <v>45646</v>
       </c>
@@ -19921,7 +20794,7 @@
         <v>258.50677100000001</v>
       </c>
     </row>
-    <row r="523" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A523" s="4">
         <v>45653</v>
       </c>
@@ -19929,7 +20802,7 @@
         <v>262.34053280000001</v>
       </c>
     </row>
-    <row r="524" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A524" s="4">
         <v>45660</v>
       </c>
@@ -19937,7 +20810,7 @@
         <v>264.73920479999998</v>
       </c>
     </row>
-    <row r="525" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A525" s="4">
         <v>45667</v>
       </c>
@@ -19945,7 +20818,7 @@
         <v>265.70118530000002</v>
       </c>
     </row>
-    <row r="526" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A526" s="4">
         <v>45674</v>
       </c>
@@ -19953,7 +20826,7 @@
         <v>268.18693949999999</v>
       </c>
     </row>
-    <row r="527" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A527" s="4">
         <v>45681</v>
       </c>
@@ -19961,7 +20834,7 @@
         <v>270.64791930000001</v>
       </c>
     </row>
-    <row r="528" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="528" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A528" s="4">
         <v>45688</v>
       </c>
@@ -19969,7 +20842,7 @@
         <v>270.3937717</v>
       </c>
     </row>
-    <row r="529" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A529" s="4">
         <v>45695</v>
       </c>
@@ -19977,7 +20850,7 @@
         <v>269.39890939999998</v>
       </c>
     </row>
-    <row r="530" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A530" s="4">
         <v>45702</v>
       </c>
@@ -19985,7 +20858,7 @@
         <v>268.81659209999998</v>
       </c>
     </row>
-    <row r="531" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A531" s="4">
         <v>45709</v>
       </c>
@@ -19993,7 +20866,7 @@
         <v>268.37462240000002</v>
       </c>
     </row>
-    <row r="532" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A532" s="4">
         <v>45716</v>
       </c>
@@ -20001,7 +20874,7 @@
         <v>267.70196540000001</v>
       </c>
     </row>
-    <row r="533" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A533" s="4">
         <v>45723</v>
       </c>
@@ -20009,7 +20882,7 @@
         <v>266.34197719999997</v>
       </c>
     </row>
-    <row r="534" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A534" s="4">
         <v>45730</v>
       </c>
@@ -20017,7 +20890,7 @@
         <v>263.86124319999999</v>
       </c>
     </row>
-    <row r="535" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A535" s="4">
         <v>45737</v>
       </c>
@@ -20025,7 +20898,7 @@
         <v>261.66781559999998</v>
       </c>
     </row>
-    <row r="536" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A536" s="4">
         <v>45744</v>
       </c>
@@ -20033,7 +20906,7 @@
         <v>261.21330460000001</v>
       </c>
     </row>
-    <row r="537" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A537" s="4">
         <v>45751</v>
       </c>
@@ -20041,7 +20914,7 @@
         <v>261.21368589999997</v>
       </c>
     </row>
-    <row r="538" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A538" s="4">
         <v>45758</v>
       </c>
@@ -20049,7 +20922,7 @@
         <v>260.0092148</v>
       </c>
     </row>
-    <row r="539" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A539" s="4">
         <v>45765</v>
       </c>
@@ -20057,7 +20930,7 @@
         <v>257.33806229999999</v>
       </c>
     </row>
-    <row r="540" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A540" s="4">
         <v>45772</v>
       </c>
@@ -20065,7 +20938,7 @@
         <v>255.48949189999999</v>
       </c>
     </row>
-    <row r="541" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A541" s="4">
         <v>45779</v>
       </c>
@@ -20073,7 +20946,7 @@
         <v>254.23606939999999</v>
       </c>
     </row>
-    <row r="542" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A542" s="4">
         <v>45786</v>
       </c>
@@ -20081,7 +20954,7 @@
         <v>252.97837659999999</v>
       </c>
     </row>
-    <row r="543" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A543" s="4">
         <v>45793</v>
       </c>
@@ -20089,7 +20962,7 @@
         <v>251.68383589999999</v>
       </c>
     </row>
-    <row r="544" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A544" s="4">
         <v>45800</v>
       </c>
@@ -20097,7 +20970,7 @@
         <v>251.15133839999999</v>
       </c>
     </row>
-    <row r="545" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A545" s="4">
         <v>45807</v>
       </c>
@@ -20105,7 +20978,7 @@
         <v>250.36283169999999</v>
       </c>
     </row>
-    <row r="546" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A546" s="4">
         <v>45814</v>
       </c>
@@ -20113,7 +20986,7 @@
         <v>248.86195839999999</v>
       </c>
     </row>
-    <row r="547" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A547" s="4">
         <v>45821</v>
       </c>
@@ -20121,7 +20994,7 @@
         <v>248.3089774</v>
       </c>
     </row>
-    <row r="548" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A548" s="4">
         <v>45828</v>
       </c>
@@ -20129,7 +21002,7 @@
         <v>250.71980880000001</v>
       </c>
     </row>
-    <row r="549" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A549" s="4">
         <v>45835</v>
       </c>
@@ -20137,7 +21010,7 @@
         <v>255.178076</v>
       </c>
     </row>
-    <row r="550" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A550" s="4">
         <v>45842</v>
       </c>
@@ -20145,7 +21018,7 @@
         <v>256.09046960000001</v>
       </c>
     </row>
-    <row r="551" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A551" s="4">
         <v>45849</v>
       </c>
@@ -20153,7 +21026,7 @@
         <v>254.87867739999999</v>
       </c>
     </row>
-    <row r="552" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A552" s="4">
         <v>45856</v>
       </c>
@@ -20161,7 +21034,7 @@
         <v>253.89432149999999</v>
       </c>
     </row>
-    <row r="553" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A553" s="4">
         <v>45863</v>
       </c>
@@ -20169,7 +21042,7 @@
         <v>254.1245538</v>
       </c>
     </row>
-    <row r="554" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="554" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A554" s="4">
         <v>45870</v>
       </c>
@@ -20177,7 +21050,7 @@
         <v>253.9131763</v>
       </c>
     </row>
-    <row r="555" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A555" s="4">
         <v>45877</v>
       </c>
@@ -20185,7 +21058,7 @@
         <v>254.14235149999999</v>
       </c>
     </row>
-    <row r="556" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A556" s="4">
         <v>45884</v>
       </c>
@@ -20193,7 +21066,7 @@
         <v>252.74203700000001</v>
       </c>
     </row>
-    <row r="557" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A557" s="4">
         <v>45891</v>
       </c>
@@ -20201,7 +21074,7 @@
         <v>251.6431882</v>
       </c>
     </row>
-    <row r="558" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A558" s="4">
         <v>45898</v>
       </c>
@@ -20209,7 +21082,7 @@
         <v>252.58462359999999</v>
       </c>
     </row>
-    <row r="559" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A559" s="4">
         <v>45905</v>
       </c>
@@ -20217,7 +21090,7 @@
         <v>253.45306959999999</v>
       </c>
     </row>
-    <row r="560" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A560" s="4">
         <v>45912</v>
       </c>
@@ -20225,7 +21098,7 @@
         <v>254.7162792</v>
       </c>
     </row>
-    <row r="561" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A561" s="4">
         <v>45919</v>
       </c>
@@ -20233,7 +21106,7 @@
         <v>254.94850439999999</v>
       </c>
     </row>
-    <row r="562" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A562" s="4">
         <v>45926</v>
       </c>
@@ -20241,7 +21114,7 @@
         <v>254.88564550000001</v>
       </c>
     </row>
-    <row r="563" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A563" s="4">
         <v>45933</v>
       </c>
@@ -20249,7 +21122,7 @@
         <v>256.79284209999997</v>
       </c>
     </row>
-    <row r="564" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A564" s="4">
         <v>45940</v>
       </c>
@@ -20257,7 +21130,7 @@
         <v>257.77437040000001</v>
       </c>
     </row>
-    <row r="565" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A565" s="4">
         <v>45947</v>
       </c>
@@ -20265,7 +21138,7 @@
         <v>257.92833419999999</v>
       </c>
     </row>
-    <row r="566" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A566" s="4">
         <v>45954</v>
       </c>
@@ -20273,7 +21146,7 @@
         <v>258.02821</v>
       </c>
     </row>
-    <row r="567" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A567" s="4">
         <v>45961</v>
       </c>
@@ -20281,7 +21154,7 @@
         <v>258.19403729999999</v>
       </c>
     </row>
-    <row r="568" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A568" s="4">
         <v>45968</v>
       </c>
@@ -20289,7 +21162,7 @@
         <v>259.9795168</v>
       </c>
     </row>
-    <row r="569" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A569" s="4">
         <v>45975</v>
       </c>
@@ -20297,7 +21170,7 @@
         <v>261.09767190000002</v>
       </c>
     </row>
-    <row r="570" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A570" s="4">
         <v>45982</v>
       </c>
@@ -20305,7 +21178,7 @@
         <v>262.71388400000001</v>
       </c>
     </row>
-    <row r="571" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A571" s="4">
         <v>45989</v>
       </c>
@@ -20313,7 +21186,7 @@
         <v>263.6667521</v>
       </c>
     </row>
-    <row r="572" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A572" s="4">
         <v>45996</v>
       </c>
@@ -20321,7 +21194,7 @@
         <v>263.29859740000001</v>
       </c>
     </row>
-    <row r="573" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A573" s="4">
         <v>46003</v>
       </c>
@@ -20329,7 +21202,7 @@
         <v>263.55805559999999</v>
       </c>
     </row>
-    <row r="574" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A574" s="4">
         <v>46010</v>
       </c>
@@ -20337,7 +21210,7 @@
         <v>262.68088180000001</v>
       </c>
     </row>
-    <row r="575" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A575" s="4">
         <v>46017</v>
       </c>
@@ -20345,7 +21218,7 @@
         <v>260.87594039999999</v>
       </c>
     </row>
-    <row r="576" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A576" s="4">
         <v>46024</v>
       </c>
@@ -20353,7 +21226,7 @@
         <v>259.34794870000002</v>
       </c>
     </row>
-    <row r="577" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A577" s="4">
         <v>46031</v>
       </c>
@@ -20361,7 +21234,7 @@
         <v>257.89418749999999</v>
       </c>
     </row>
-    <row r="578" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="578" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A578" s="4">
         <v>46038</v>
       </c>
@@ -20369,7 +21242,7 @@
         <v>255.8569047</v>
       </c>
     </row>
-    <row r="579" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A579" s="4">
         <v>46045</v>
       </c>
@@ -20377,7 +21250,7 @@
         <v>254.82883749999999</v>
       </c>
     </row>
-    <row r="580" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A580" s="4">
         <v>46052</v>
       </c>
@@ -20385,7 +21258,7 @@
         <v>254.2878493</v>
       </c>
     </row>
-    <row r="581" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A581" s="4">
         <v>46059</v>
       </c>
@@ -20393,7 +21266,7 @@
         <v>253.69099979999999</v>
       </c>
     </row>
-    <row r="582" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A582" s="4">
         <v>46066</v>
       </c>
@@ -20401,7 +21274,7 @@
         <v>252.8266606</v>
       </c>
     </row>
-    <row r="583" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A583" s="4">
         <v>46073</v>
       </c>
@@ -20409,7 +21282,7 @@
         <v>252.3097181</v>
       </c>
     </row>
-    <row r="584" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A584" s="4">
         <v>46080</v>
       </c>
@@ -20417,7 +21290,7 @@
         <v>252.9454796</v>
       </c>
     </row>
-    <row r="585" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A585" s="4">
         <v>46087</v>
       </c>
@@ -20425,7 +21298,7 @@
         <v>258.0163786</v>
       </c>
     </row>
-    <row r="586" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A586" s="4">
         <v>46094</v>
       </c>
@@ -20433,7 +21306,7 @@
         <v>282.0612648</v>
       </c>
     </row>
-    <row r="587" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A587" s="4">
         <v>46101</v>
       </c>
@@ -20441,7 +21314,7 @@
         <v>313.91989310000002</v>
       </c>
     </row>
-    <row r="588" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A588" s="4">
         <v>46108</v>
       </c>
@@ -20449,7 +21322,7 @@
         <v>335.24787889999999</v>
       </c>
     </row>
-    <row r="589" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A589" s="4">
         <v>46115</v>
       </c>
@@ -20457,7 +21330,7 @@
         <v>340.24394469999999</v>
       </c>
     </row>
-    <row r="590" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="590" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A590" s="4">
         <v>46122</v>
       </c>
@@ -20465,7 +21338,7 @@
         <v>346.8315159</v>
       </c>
     </row>
-    <row r="591" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="591" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A591" s="4">
         <v>46129</v>
       </c>
@@ -20473,7 +21346,7 @@
         <v>342.1280625</v>
       </c>
     </row>
-    <row r="592" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="592" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A592" s="4">
         <v>46136</v>
       </c>
@@ -20481,7 +21354,7 @@
         <v>330.34025170000001</v>
       </c>
     </row>
-    <row r="593" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A593" s="4">
         <v>46143</v>
       </c>
@@ -20489,7 +21362,7 @@
         <v>322.47753130000001</v>
       </c>
     </row>
-    <row r="594" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A594" s="4">
         <v>46150</v>
       </c>
@@ -20497,7 +21370,7 @@
         <v>323.04009719999999</v>
       </c>
     </row>
-    <row r="595" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A595" s="4">
         <v>46157</v>
       </c>
@@ -20505,7 +21378,7 @@
         <v>322.1773541</v>
       </c>
     </row>
-    <row r="596" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="596" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A596" s="4">
         <v>46164</v>
       </c>
@@ -20513,7 +21386,7 @@
         <v>324.40253189999999</v>
       </c>
     </row>
-    <row r="597" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A597" s="4">
         <v>46171</v>
       </c>
@@ -20521,7 +21394,7 @@
         <v>324.84309610000003</v>
       </c>
     </row>
-    <row r="598" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A598" s="4">
         <v>46178</v>
       </c>
@@ -20529,7 +21402,7 @@
         <v>322.24647850000002</v>
       </c>
     </row>
-    <row r="599" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A599" s="4">
         <v>46185</v>
       </c>
@@ -20537,7 +21410,7 @@
         <v>317.13150569999999</v>
       </c>
     </row>
-    <row r="600" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A600" s="4">
         <v>46192</v>
       </c>
@@ -20545,7 +21418,7 @@
         <v>309.7663948</v>
       </c>
     </row>
-    <row r="601" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A601" s="4">
         <v>46199</v>
       </c>
@@ -20553,7 +21426,7 @@
         <v>301.0267073</v>
       </c>
     </row>
-    <row r="602" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="602" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A602" s="4">
         <v>46206</v>
       </c>
@@ -20561,7 +21434,7 @@
         <v>296.10165360000002</v>
       </c>
     </row>
-    <row r="603" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A603" s="4">
         <v>46213</v>
       </c>
@@ -20569,7 +21442,7 @@
         <v>292.66670069999998</v>
       </c>
     </row>
-    <row r="604" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A604" s="4">
         <v>46220</v>
       </c>
@@ -20577,7 +21450,7 @@
         <v>290.50132930000001</v>
       </c>
     </row>
-    <row r="605" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A605" s="4">
         <v>46227</v>
       </c>
@@ -20585,7 +21458,7 @@
         <v>291.9867855</v>
       </c>
     </row>
-    <row r="606" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A606" s="4">
         <v>46234</v>
       </c>
@@ -20593,7 +21466,7 @@
         <v>298.54918620000001</v>
       </c>
     </row>
-    <row r="607" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A607" s="4">
         <v>46241</v>
       </c>
@@ -20601,7 +21474,7 @@
         <v>300.83523769999999</v>
       </c>
     </row>
-    <row r="608" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A608" s="4">
         <v>46248</v>
       </c>
@@ -20609,7 +21482,7 @@
         <v>298.81317960000001</v>
       </c>
     </row>
-    <row r="609" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A609" s="4">
         <v>46255</v>
       </c>
@@ -20617,7 +21490,7 @@
         <v>298.03322309999999</v>
       </c>
     </row>
-    <row r="610" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A610" s="4">
         <v>46262</v>
       </c>
@@ -20625,7 +21498,7 @@
         <v>297.88171610000001</v>
       </c>
     </row>
-    <row r="611" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A611" s="4">
         <v>46269</v>
       </c>
@@ -20633,7 +21506,7 @@
         <v>296.71102450000001</v>
       </c>
     </row>
-    <row r="612" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:2" x14ac:dyDescent="0.35">
       <c r="A612" s="4">
         <v>46276</v>
       </c>
